--- a/data/proteomics/ecGEM_volume_size_across_compartment.xlsx
+++ b/data/proteomics/ecGEM_volume_size_across_compartment.xlsx
@@ -828,40 +828,40 @@
         <v>1.049987227663292</v>
       </c>
       <c r="D2" t="n">
-        <v>1.256144698163694</v>
+        <v>1.256144698163695</v>
       </c>
       <c r="E2" t="n">
         <v>1.126161559236469</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8591535621148843</v>
+        <v>0.8591535621148844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5177522722082555</v>
+        <v>0.5177522722082551</v>
       </c>
       <c r="H2" t="n">
-        <v>0.466681941357798</v>
+        <v>0.4666819413577978</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4777860406857834</v>
+        <v>0.477786040685783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6330785040863717</v>
+        <v>0.6330785040863716</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6613640442646158</v>
+        <v>0.6613640442646163</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5660421895011397</v>
+        <v>0.5660421895011404</v>
       </c>
       <c r="M2" t="n">
         <v>0.360263035528362</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3749143332130896</v>
+        <v>0.3749143332130898</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5276593890769895</v>
+        <v>0.5276593890769891</v>
       </c>
       <c r="P2" t="n">
         <v>0.5202648195530772</v>
@@ -870,109 +870,109 @@
         <v>0.4498247096478478</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4554912368158403</v>
+        <v>0.4554912368158401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.453916338440971</v>
+        <v>0.4539163384409709</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4538914170691596</v>
+        <v>0.4538914170691597</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4675886634707168</v>
+        <v>0.4675886634707169</v>
       </c>
       <c r="V2" t="n">
         <v>0.6834746554681825</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6922160338100319</v>
+        <v>0.6922160338100314</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6425355055851453</v>
+        <v>0.6425355055851452</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7890243023013779</v>
+        <v>0.7890243023013782</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8378464312370536</v>
+        <v>0.8378464312370537</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8377193499862395</v>
+        <v>0.8377193499862392</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8231267106010237</v>
+        <v>0.8231267106010238</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9476955356448304</v>
+        <v>0.9476955356448307</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9728897876467881</v>
+        <v>0.9728897876467884</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9139430839228619</v>
+        <v>0.9139430839228608</v>
       </c>
       <c r="AF2" t="n">
         <v>0.5829530587726548</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.7268751833027055</v>
+        <v>0.7268751833027058</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3935434142391812</v>
+        <v>0.3935434142391808</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.65157580083922</v>
+        <v>0.6515758008392198</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.6242473643339935</v>
+        <v>0.6242473643339939</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7431975111596302</v>
+        <v>0.7431975111596303</v>
       </c>
       <c r="AL2" t="n">
         <v>0.9145002333868393</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.7826390134633693</v>
+        <v>0.7826390134633697</v>
       </c>
       <c r="AN2" t="n">
         <v>0.710959504014204</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6721743395151181</v>
+        <v>0.6721743395151187</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6932823629116794</v>
+        <v>0.6932823629116796</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6040513471139124</v>
+        <v>0.6040513471139125</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7408238220066251</v>
+        <v>0.7408238220066246</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6954901855513765</v>
+        <v>0.6954901855513763</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.936522089064719</v>
+        <v>0.9365220890647193</v>
       </c>
       <c r="AU2" t="n">
         <v>0.8595203523287716</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8717060833677144</v>
+        <v>0.8717060833677142</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9743975669753345</v>
+        <v>0.9743975669753336</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.8412655522800155</v>
+        <v>0.8412655522800151</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.8231790574142374</v>
+        <v>0.8231790574142378</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.092944924043126</v>
+        <v>1.092944924043125</v>
       </c>
       <c r="BA2" t="n">
         <v>1.048336875220488</v>
@@ -984,10 +984,10 @@
         <v>1.032373365445709</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.827235261012491</v>
+        <v>1.82723526101249</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.81266655094274</v>
+        <v>0.8126665509427405</v>
       </c>
       <c r="BF2" t="n">
         <v>1.040625959103209</v>
@@ -996,37 +996,37 @@
         <v>1.000141129523174</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.119381185529754</v>
+        <v>1.119381185529753</v>
       </c>
       <c r="BI2" t="n">
         <v>1.083459858394292</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9734894186343686</v>
+        <v>0.9734894186343692</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5501383651094053</v>
+        <v>0.5501383651094054</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.4870335389535336</v>
+        <v>0.4870335389535334</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5608789831753042</v>
+        <v>0.5608789831753038</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.5394131063841409</v>
+        <v>0.5394131063841405</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.7756569235411139</v>
+        <v>0.775656923541114</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.6802600342673158</v>
+        <v>0.6802600342673161</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.4241860246430977</v>
+        <v>0.4241860246430975</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.9775864692441001</v>
+        <v>0.9775864692441003</v>
       </c>
       <c r="BS2" t="n">
         <v>1.040537443180722</v>
@@ -1035,19 +1035,19 @@
         <v>1.082974163833796</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.152478924546475</v>
+        <v>1.152478924546474</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.8246314982360723</v>
+        <v>0.8246314982360731</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9228255200030691</v>
+        <v>0.9228255200030694</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9289614786933188</v>
+        <v>0.9289614786933184</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.8682631427090884</v>
+        <v>0.8682631427090874</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.7340393413746037</v>
@@ -1284,7 +1284,7 @@
         <v>0.0003322398597394922</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000377225941049047</v>
+        <v>0.0003772259410490469</v>
       </c>
       <c r="E4" t="n">
         <v>0.0003583614413244079</v>
@@ -1302,7 +1302,7 @@
         <v>0.0001179810423484579</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001322384458017878</v>
+        <v>0.0001322384458017879</v>
       </c>
       <c r="K4" t="n">
         <v>0.0001589428251550112</v>
@@ -1329,10 +1329,10 @@
         <v>0.000158748551935655</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001663830337042047</v>
+        <v>0.0001663830337042046</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001627185802885623</v>
+        <v>0.0001627185802885622</v>
       </c>
       <c r="U4" t="n">
         <v>0.0001727746616229145</v>
@@ -1368,10 +1368,10 @@
         <v>0.0001774014398450595</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.000132398637882487</v>
+        <v>0.0001323986378824871</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0001555840090512109</v>
+        <v>0.000155584009051211</v>
       </c>
       <c r="AH4" t="n">
         <v>0.000123808698491444</v>
@@ -1383,7 +1383,7 @@
         <v>0.0001753803888314101</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0001739955399859589</v>
+        <v>0.000173995539985959</v>
       </c>
       <c r="AL4" t="n">
         <v>0.0001967807888337744</v>
@@ -1437,13 +1437,13 @@
         <v>0.001325319950023928</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.00125557288588742</v>
+        <v>0.001255572885887421</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.002162014369514076</v>
+        <v>0.002162014369514075</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.00109536436248489</v>
+        <v>0.001095364362484891</v>
       </c>
       <c r="BF4" t="n">
         <v>0.0009090216311288476</v>
@@ -1461,7 +1461,7 @@
         <v>0.0027146145554712</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002191342156808939</v>
+        <v>0.002191342156808938</v>
       </c>
       <c r="BL4" t="n">
         <v>0.0004860406399360256</v>
@@ -1479,7 +1479,7 @@
         <v>0.002714725365014473</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.002569892358410914</v>
+        <v>0.002569892358410915</v>
       </c>
       <c r="BR4" t="n">
         <v>0.0005900622026359213</v>
@@ -1488,7 +1488,7 @@
         <v>0.0006457381892774908</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0008656412027750572</v>
+        <v>0.0008656412027750573</v>
       </c>
       <c r="BU4" t="n">
         <v>0.0009501970979753655</v>
@@ -1500,7 +1500,7 @@
         <v>0.0008128982079587995</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0008208661226804845</v>
+        <v>0.0008208661226804844</v>
       </c>
       <c r="BY4" t="n">
         <v>0.0008323106787265849</v>
@@ -1760,25 +1760,25 @@
         <v>0.5143080793185156</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3103516766423365</v>
+        <v>0.3103516766423366</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2750735048448867</v>
+        <v>0.2750735048448869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.381090845346047</v>
+        <v>0.3810908453460468</v>
       </c>
       <c r="G6" t="n">
         <v>0.1861148882390055</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1648777314475548</v>
+        <v>0.164877731447555</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1749548708358682</v>
+        <v>0.1749548708358681</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2094000186918243</v>
+        <v>0.2094000186918242</v>
       </c>
       <c r="K6" t="n">
         <v>0.2292392539856247</v>
@@ -1793,10 +1793,10 @@
         <v>0.1451808310036761</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1824883645118464</v>
+        <v>0.1824883645118466</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1997833623260608</v>
+        <v>0.1997833623260609</v>
       </c>
       <c r="Q6" t="n">
         <v>0.178256221927974</v>
@@ -1805,28 +1805,28 @@
         <v>0.1729613283317465</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1669621900372409</v>
+        <v>0.1669621900372411</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1722945217167197</v>
+        <v>0.1722945217167198</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1770942343863647</v>
+        <v>0.1770942343863648</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2586446737302971</v>
+        <v>0.258644673730297</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2594294011896114</v>
+        <v>0.2594294011896115</v>
       </c>
       <c r="X6" t="n">
         <v>0.2514658596404651</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.319757746760134</v>
+        <v>0.3197577467601339</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3520426017975075</v>
+        <v>0.3520426017975076</v>
       </c>
       <c r="AA6" t="n">
         <v>0.3206257421465145</v>
@@ -1835,10 +1835,10 @@
         <v>0.2583891258671711</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3272905187455605</v>
+        <v>0.3272905187455606</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3457428317054136</v>
+        <v>0.3457428317054132</v>
       </c>
       <c r="AE6" t="n">
         <v>0.3333422184760381</v>
@@ -1850,7 +1850,7 @@
         <v>0.2277272586538105</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1332400412292829</v>
+        <v>0.1332400412292828</v>
       </c>
       <c r="AI6" t="n">
         <v>0.2267851652768534</v>
@@ -1865,43 +1865,43 @@
         <v>0.3218798731255537</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.255967097282311</v>
+        <v>0.2559670972823109</v>
       </c>
       <c r="AN6" t="n">
         <v>0.2664625562288911</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2320396131717256</v>
+        <v>0.2320396131717255</v>
       </c>
       <c r="AP6" t="n">
         <v>0.2343507032601449</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.181939571844525</v>
+        <v>0.1819395718445251</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.2550896352623453</v>
+        <v>0.2550896352623452</v>
       </c>
       <c r="AS6" t="n">
         <v>0.1940588353039499</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.3024855845165622</v>
+        <v>0.3024855845165623</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2839890668609884</v>
+        <v>0.2839890668609882</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2905573828441333</v>
+        <v>0.2905573828441335</v>
       </c>
       <c r="AW6" t="n">
         <v>0.3707407690831376</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2138100831920558</v>
+        <v>0.213810083192056</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.187775908782773</v>
+        <v>0.1877759087827729</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.2453654563908972</v>
@@ -1910,76 +1910,76 @@
         <v>0.2170785297149514</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.5144229908985455</v>
+        <v>0.5144229908985453</v>
       </c>
       <c r="BC6" t="n">
         <v>0.42265632896176</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.6190479563544693</v>
+        <v>0.6190479563544694</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.3659437161054303</v>
+        <v>0.36594371610543</v>
       </c>
       <c r="BF6" t="n">
         <v>0.3878414958836536</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.3852939404380495</v>
+        <v>0.3852939404380494</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.3902524848553716</v>
+        <v>0.3902524848553712</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.3823566278171411</v>
+        <v>0.3823566278171409</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.3971948382237462</v>
+        <v>0.3971948382237463</v>
       </c>
       <c r="BK6" t="n">
         <v>0.2109365797046015</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.2580131952448713</v>
+        <v>0.2580131952448715</v>
       </c>
       <c r="BM6" t="n">
         <v>0.2196026808143791</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.151648249767702</v>
+        <v>0.1516482497677021</v>
       </c>
       <c r="BO6" t="n">
         <v>0.1836149940633889</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.3147745456503826</v>
+        <v>0.3147745456503823</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1785599988289096</v>
+        <v>0.1785599988289098</v>
       </c>
       <c r="BR6" t="n">
         <v>0.2785013426686078</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.2851564490299612</v>
+        <v>0.285156449029961</v>
       </c>
       <c r="BT6" t="n">
         <v>0.3020976186530686</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.321698226518469</v>
+        <v>0.3216982265184689</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2305155942339973</v>
+        <v>0.2305155942339972</v>
       </c>
       <c r="BW6" t="n">
         <v>0.2554124485781185</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.268445258079544</v>
+        <v>0.2684452580795441</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.2763762960769901</v>
+        <v>0.27637629607699</v>
       </c>
       <c r="BZ6" t="n">
         <v>0.2569175824963994</v>
@@ -1995,157 +1995,157 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.227702900574953</v>
+        <v>1.227702900574952</v>
       </c>
       <c r="D7" t="n">
         <v>1.107817742152018</v>
       </c>
       <c r="E7" t="n">
-        <v>1.166235345688814</v>
+        <v>1.166235345688813</v>
       </c>
       <c r="F7" t="n">
-        <v>1.288541085963576</v>
+        <v>1.288541085963575</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4493567617922102</v>
+        <v>0.4493567617922103</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4038511183931702</v>
+        <v>0.4038511183931698</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4158391074185473</v>
+        <v>0.4158391074185478</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7506920834617155</v>
+        <v>0.7506920834617156</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7827808561125245</v>
+        <v>0.7827808561125238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6761619508185629</v>
+        <v>0.6761619508185628</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3274162882041733</v>
+        <v>0.3274162882041731</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3454188670451776</v>
+        <v>0.3454188670451778</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4675497487232159</v>
+        <v>0.467549748723216</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4652831266977561</v>
+        <v>0.4652831266977556</v>
       </c>
       <c r="Q7" t="n">
         <v>0.3950000762617641</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4048519269576958</v>
+        <v>0.4048519269576955</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4339307388466834</v>
+        <v>0.4339307388466827</v>
       </c>
       <c r="T7" t="n">
         <v>0.4220583719045811</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4261446592363546</v>
+        <v>0.426144659236355</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6741873226844031</v>
+        <v>0.674187322684403</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6815970976960152</v>
+        <v>0.6815970976960154</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6646391909939914</v>
+        <v>0.6646391909939912</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.821398090842348</v>
+        <v>0.8213980908423483</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8441529395581461</v>
+        <v>0.8441529395581465</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.8582885339151145</v>
+        <v>0.8582885339151144</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.076929476043777</v>
+        <v>1.076929476043778</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.299972964871671</v>
+        <v>1.299972964871672</v>
       </c>
       <c r="AD7" t="n">
         <v>1.289230897111436</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9815952440526073</v>
+        <v>0.9815952440526076</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5366674650241225</v>
+        <v>0.5366674650241221</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.6464002313312956</v>
+        <v>0.6464002313312951</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.3152085494247799</v>
+        <v>0.3152085494247798</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.546577466770802</v>
+        <v>0.5465774667708021</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.5493768416962731</v>
+        <v>0.5493768416962733</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.6873973619525936</v>
+        <v>0.687397361952594</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.8614857902621359</v>
+        <v>0.861485790262135</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.7182248758041916</v>
+        <v>0.7182248758041915</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.6236792409363761</v>
+        <v>0.6236792409363762</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5552088172173947</v>
+        <v>0.5552088172173946</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.5958182796999963</v>
+        <v>0.5958182796999952</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.581897322835178</v>
+        <v>0.5818973228351779</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.8080113656938168</v>
+        <v>0.8080113656938166</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.627943450058617</v>
+        <v>0.6279434500586174</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.8146671509830211</v>
+        <v>0.814667150983021</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.7295714607737497</v>
+        <v>0.7295714607737496</v>
       </c>
       <c r="AV7" t="n">
         <v>0.7288609611279501</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.9015501718970114</v>
+        <v>0.9015501718970115</v>
       </c>
       <c r="AX7" t="n">
         <v>1.155577028741131</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.8933718282368671</v>
+        <v>0.8933718282368677</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.495515052882004</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.26137999223781</v>
+        <v>1.261379992237812</v>
       </c>
       <c r="BB7" t="n">
         <v>1.56437021790089</v>
@@ -2154,13 +2154,13 @@
         <v>1.081264416173102</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.634685651839968</v>
+        <v>1.634685651839967</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.9198683368265117</v>
+        <v>0.9198683368265115</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.097489586968307</v>
+        <v>1.097489586968306</v>
       </c>
       <c r="BG7" t="n">
         <v>1.080850846096522</v>
@@ -2169,58 +2169,58 @@
         <v>1.1146951940471</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.113360493497042</v>
+        <v>1.113360493497043</v>
       </c>
       <c r="BJ7" t="n">
         <v>1.118596374007212</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5141265167424509</v>
+        <v>0.5141265167424507</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5848631786052083</v>
+        <v>0.5848631786052085</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6879163558332752</v>
+        <v>0.6879163558332755</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.4993418889399708</v>
+        <v>0.4993418889399707</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.6235051106462604</v>
+        <v>0.6235051106462602</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.7908840580962716</v>
+        <v>0.7908840580962712</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.4817974991180228</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.7694632132794632</v>
+        <v>0.7694632132794637</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.7986595779968454</v>
+        <v>0.7986595779968452</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.8497655618256695</v>
+        <v>0.8497655618256694</v>
       </c>
       <c r="BU7" t="n">
         <v>0.9129961750019356</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.6495737684084243</v>
+        <v>0.6495737684084248</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7344637977690031</v>
+        <v>0.7344637977690033</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.7637157314283931</v>
+        <v>0.7637157314283928</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.7684553469714387</v>
+        <v>0.7684553469714386</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.7054232521858326</v>
+        <v>0.7054232521858324</v>
       </c>
     </row>
     <row r="8">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7982390795516948</v>
+        <v>0.7982390795516946</v>
       </c>
       <c r="D8" t="n">
         <v>0.7393193884560378</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6193452912589789</v>
+        <v>0.619345291258979</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6492396050707753</v>
+        <v>0.6492396050707752</v>
       </c>
       <c r="G8" t="n">
-        <v>0.27376022840418</v>
+        <v>0.2737602284041801</v>
       </c>
       <c r="H8" t="n">
         <v>0.2339410648605333</v>
@@ -2254,103 +2254,103 @@
         <v>0.2375708946283366</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3004151312184634</v>
+        <v>0.3004151312184635</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3153455907196531</v>
+        <v>0.315345590719653</v>
       </c>
       <c r="L8" t="n">
         <v>0.267092117313193</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1924005285432477</v>
+        <v>0.1924005285432476</v>
       </c>
       <c r="N8" t="n">
         <v>0.1951699541240396</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3132463399142199</v>
+        <v>0.31324633991422</v>
       </c>
       <c r="P8" t="n">
         <v>0.2920746868538087</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2535805437228612</v>
+        <v>0.2535805437228613</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2463827402016978</v>
+        <v>0.2463827402016977</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2291750694235068</v>
+        <v>0.2291750694235067</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2384137940499196</v>
+        <v>0.2384137940499195</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2405395568922332</v>
+        <v>0.2405395568922333</v>
       </c>
       <c r="V8" t="n">
         <v>0.3807334814021336</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3825101421392366</v>
+        <v>0.3825101421392363</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3690861992735718</v>
+        <v>0.3690861992735719</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.487245201003645</v>
+        <v>0.4872452010036449</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5450115984420972</v>
+        <v>0.5450115984420971</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5080470018680143</v>
+        <v>0.5080470018680144</v>
       </c>
       <c r="AB8" t="n">
         <v>0.3730032996525984</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.4132297238610653</v>
+        <v>0.4132297238610655</v>
       </c>
       <c r="AD8" t="n">
         <v>0.4554396717984956</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4081776155867545</v>
+        <v>0.4081776155867542</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2965613066312804</v>
+        <v>0.2965613066312803</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3777935023335457</v>
+        <v>0.3777935023335459</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2164781838518625</v>
+        <v>0.2164781838518626</v>
       </c>
       <c r="AI8" t="n">
         <v>0.3416887363714</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3123780421662212</v>
+        <v>0.3123780421662213</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.2999350908331838</v>
+        <v>0.2999350908331839</v>
       </c>
       <c r="AL8" t="n">
         <v>0.3601947066162626</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.3101394654783235</v>
+        <v>0.3101394654783234</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.3658831692751932</v>
+        <v>0.3658831692751931</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.3379828789614061</v>
+        <v>0.337982878961406</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.3374959607947396</v>
+        <v>0.3374959607947395</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.2793935115354628</v>
@@ -2359,13 +2359,13 @@
         <v>0.3208014193879415</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.365610949218778</v>
+        <v>0.3656109492187782</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5445909124963615</v>
+        <v>0.5445909124963613</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4720523219880314</v>
+        <v>0.4720523219880313</v>
       </c>
       <c r="AV8" t="n">
         <v>0.5054987189717977</v>
@@ -2377,16 +2377,16 @@
         <v>0.4219282797917098</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.4239808901691193</v>
+        <v>0.4239808901691192</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.5598553049354345</v>
+        <v>0.5598553049354346</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.5413711884785152</v>
+        <v>0.5413711884785151</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.011244370521979</v>
+        <v>1.011244370521978</v>
       </c>
       <c r="BC8" t="n">
         <v>0.6964196231699886</v>
@@ -2395,67 +2395,67 @@
         <v>1.076919298804062</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.5778488099953575</v>
+        <v>0.5778488099953577</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.6151288257897004</v>
+        <v>0.6151288257897005</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.5998841874225798</v>
+        <v>0.5998841874225795</v>
       </c>
       <c r="BH8" t="n">
         <v>0.6446558572924046</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.6338407708263951</v>
+        <v>0.6338407708263952</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7077017395046324</v>
+        <v>0.7077017395046326</v>
       </c>
       <c r="BK8" t="n">
         <v>0.3646051222595128</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.3815704345047607</v>
+        <v>0.3815704345047605</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.4144117842042943</v>
+        <v>0.4144117842042941</v>
       </c>
       <c r="BN8" t="n">
         <v>0.3114400057037329</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.4369001270508289</v>
+        <v>0.436900127050829</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.5376150754495201</v>
+        <v>0.53761507544952</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.3081988538513358</v>
+        <v>0.3081988538513361</v>
       </c>
       <c r="BR8" t="n">
         <v>0.5707863453682297</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.6093192567295521</v>
+        <v>0.6093192567295522</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.6015885015292086</v>
+        <v>0.6015885015292085</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.6165239432800271</v>
+        <v>0.6165239432800269</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.4083067263904819</v>
+        <v>0.4083067263904818</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.4385310140322547</v>
+        <v>0.4385310140322546</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.4662428397181791</v>
+        <v>0.4662428397181792</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.4582802526142649</v>
+        <v>0.4582802526142648</v>
       </c>
       <c r="BZ8" t="n">
         <v>0.4104237161057965</v>
@@ -2840,7 +2840,7 @@
         <v>0.06157716676391219</v>
       </c>
       <c r="R11" t="n">
-        <v>0.05771475927931039</v>
+        <v>0.05771475927931041</v>
       </c>
       <c r="S11" t="n">
         <v>0.04871636611428785</v>
@@ -2900,7 +2900,7 @@
         <v>0.05572766770626596</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.059769052139576</v>
+        <v>0.05976905213957599</v>
       </c>
       <c r="AM11" t="n">
         <v>0.05571853850209376</v>
@@ -2909,7 +2909,7 @@
         <v>0.08247918168038001</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.08534858842759589</v>
+        <v>0.08534858842759588</v>
       </c>
       <c r="AP11" t="n">
         <v>0.08805876923953554</v>
@@ -2933,13 +2933,13 @@
         <v>0.1471682092617092</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1393609109815632</v>
+        <v>0.1393609109815633</v>
       </c>
       <c r="AX11" t="n">
         <v>0.01001596512491797</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.009076797027001862</v>
+        <v>0.009076797027001864</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.02798295840196091</v>
@@ -2960,7 +2960,7 @@
         <v>0.08880729001545486</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.08739275401290554</v>
+        <v>0.08739275401290553</v>
       </c>
       <c r="BG11" t="n">
         <v>0.08501895718879579</v>
@@ -2990,10 +2990,10 @@
         <v>0.022162660041695</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.07639364114680341</v>
+        <v>0.07639364114680339</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04238247931725551</v>
+        <v>0.04238247931725552</v>
       </c>
       <c r="BR11" t="n">
         <v>0.09644484929134946</v>
@@ -3002,7 +3002,7 @@
         <v>0.09541030931478837</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.07585307604587258</v>
+        <v>0.07585307604587255</v>
       </c>
       <c r="BU11" t="n">
         <v>0.0696862829730249</v>
@@ -3057,22 +3057,22 @@
         <v>0.02309432970726709</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02497715567570376</v>
+        <v>0.02497715567570374</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02080467048728495</v>
+        <v>0.02080467048728496</v>
       </c>
       <c r="M12" t="n">
         <v>0.01558937166865422</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01766055861697168</v>
+        <v>0.01766055861697167</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01840606919011976</v>
+        <v>0.01840606919011975</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02689027045874542</v>
+        <v>0.02689027045874541</v>
       </c>
       <c r="Q12" t="n">
         <v>0.02296376585644248</v>
@@ -3093,28 +3093,28 @@
         <v>0.0313206049997131</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03211237389962543</v>
+        <v>0.03211237389962544</v>
       </c>
       <c r="X12" t="n">
         <v>0.03171876961288196</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.032885117943838</v>
+        <v>0.03288511794383801</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.03399075750222565</v>
+        <v>0.03399075750222566</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0358840029791237</v>
+        <v>0.03588400297912371</v>
       </c>
       <c r="AB12" t="n">
         <v>0.02950446607677986</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0380833261623321</v>
+        <v>0.03808332616233212</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.03406270465241798</v>
+        <v>0.03406270465241797</v>
       </c>
       <c r="AE12" t="n">
         <v>0.02854469534692618</v>
@@ -3123,16 +3123,16 @@
         <v>0.01740077907179848</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.02065593738677496</v>
+        <v>0.02065593738677497</v>
       </c>
       <c r="AH12" t="n">
         <v>0.01854040570897606</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03038580545176779</v>
+        <v>0.0303858054517678</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.03057261998519872</v>
+        <v>0.03057261998519871</v>
       </c>
       <c r="AK12" t="n">
         <v>0.02647517203616514</v>
@@ -3141,13 +3141,13 @@
         <v>0.02807863178441878</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.02445647431249598</v>
+        <v>0.02445647431249599</v>
       </c>
       <c r="AN12" t="n">
         <v>0.03563125512395165</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03248034163721466</v>
+        <v>0.03248034163721467</v>
       </c>
       <c r="AP12" t="n">
         <v>0.03486475110574932</v>
@@ -3159,7 +3159,7 @@
         <v>0.02695778819819575</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.01997099923935497</v>
+        <v>0.01997099923935498</v>
       </c>
       <c r="AT12" t="n">
         <v>0.03250913189512489</v>
@@ -3168,25 +3168,25 @@
         <v>0.03111070355504049</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.03272613865220683</v>
+        <v>0.03272613865220685</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02977312935865723</v>
+        <v>0.02977312935865722</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03810297418119101</v>
+        <v>0.038102974181191</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.05264942286469059</v>
+        <v>0.05264942286469058</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.03744019642051501</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.04004923612835316</v>
+        <v>0.04004923612835318</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.06073519467565327</v>
+        <v>0.06073519467565329</v>
       </c>
       <c r="BC12" t="n">
         <v>0.05875149224500057</v>
@@ -3198,13 +3198,13 @@
         <v>0.04779410468314452</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.03218256796543859</v>
+        <v>0.0321825679654386</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.03063281704566329</v>
+        <v>0.03063281704566328</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.03643799999227416</v>
+        <v>0.03643799999227415</v>
       </c>
       <c r="BI12" t="n">
         <v>0.04054942679106745</v>
@@ -3216,7 +3216,7 @@
         <v>0.07530277780062522</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.02391613228651356</v>
+        <v>0.02391613228651358</v>
       </c>
       <c r="BM12" t="n">
         <v>0.03366601921925902</v>
@@ -3228,10 +3228,10 @@
         <v>0.028088550008779</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.06374698490179785</v>
+        <v>0.06374698490179787</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.04717947072476982</v>
+        <v>0.04717947072476981</v>
       </c>
       <c r="BR12" t="n">
         <v>0.02738103477203083</v>
@@ -3240,13 +3240,13 @@
         <v>0.03365105264998251</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.04915377444081241</v>
+        <v>0.04915377444081242</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.05232710193669214</v>
+        <v>0.05232710193669216</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0345502029948212</v>
+        <v>0.03455020299482121</v>
       </c>
       <c r="BW12" t="n">
         <v>0.03297990757152342</v>
@@ -3255,7 +3255,7 @@
         <v>0.02867831836361502</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02688058534524349</v>
+        <v>0.02688058534524348</v>
       </c>
       <c r="BZ12" t="n">
         <v>0.02335473576866817</v>
@@ -3485,10 +3485,10 @@
         <v>0.01152972927726868</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01816457818509659</v>
+        <v>0.0181645781850966</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009039985626760325</v>
+        <v>0.009039985626760323</v>
       </c>
       <c r="G14" t="n">
         <v>0.008849888610613548</v>
@@ -3503,7 +3503,7 @@
         <v>0.01407331298334914</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01418015712387645</v>
+        <v>0.01418015712387644</v>
       </c>
       <c r="L14" t="n">
         <v>0.01211468273141171</v>
@@ -3512,25 +3512,25 @@
         <v>0.005664886637643952</v>
       </c>
       <c r="N14" t="n">
-        <v>0.00637147679833992</v>
+        <v>0.006371476798339921</v>
       </c>
       <c r="O14" t="n">
         <v>0.008057841190896831</v>
       </c>
       <c r="P14" t="n">
-        <v>0.009598145047686508</v>
+        <v>0.009598145047686506</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007903687573520559</v>
+        <v>0.007903687573520562</v>
       </c>
       <c r="R14" t="n">
         <v>0.00827676131353856</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008998042866794289</v>
+        <v>0.00899804286679429</v>
       </c>
       <c r="T14" t="n">
-        <v>0.008896080946413854</v>
+        <v>0.008896080946413852</v>
       </c>
       <c r="U14" t="n">
         <v>0.008952079256406321</v>
@@ -3557,7 +3557,7 @@
         <v>0.01529555918447747</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01841472599730317</v>
+        <v>0.01841472599730318</v>
       </c>
       <c r="AD14" t="n">
         <v>0.01763407539551822</v>
@@ -3569,7 +3569,7 @@
         <v>0.009689784133443647</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01150420343091632</v>
+        <v>0.01150420343091633</v>
       </c>
       <c r="AH14" t="n">
         <v>0.006822422829576734</v>
@@ -3578,7 +3578,7 @@
         <v>0.01155994513074424</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01132277207784168</v>
+        <v>0.01132277207784167</v>
       </c>
       <c r="AK14" t="n">
         <v>0.01859208082221883</v>
@@ -3587,19 +3587,19 @@
         <v>0.02063305439972827</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.01863683620436579</v>
+        <v>0.01863683620436578</v>
       </c>
       <c r="AN14" t="n">
         <v>0.01302123278754891</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.01212092176337463</v>
+        <v>0.01212092176337464</v>
       </c>
       <c r="AP14" t="n">
         <v>0.01201232559268637</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.01020897842337819</v>
+        <v>0.0102089784233782</v>
       </c>
       <c r="AR14" t="n">
         <v>0.01321350647877024</v>
@@ -3617,7 +3617,7 @@
         <v>0.01166374136172977</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02968646776051986</v>
+        <v>0.02968646776051985</v>
       </c>
       <c r="AX14" t="n">
         <v>0.0124455990861893</v>
@@ -3632,7 +3632,7 @@
         <v>0.01369702863110732</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.04804157555099176</v>
+        <v>0.04804157555099178</v>
       </c>
       <c r="BC14" t="n">
         <v>0.02974563798119256</v>
@@ -3662,7 +3662,7 @@
         <v>0.01475217002920228</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.01224283383017587</v>
+        <v>0.01224283383017588</v>
       </c>
       <c r="BM14" t="n">
         <v>0.01615292056137</v>
@@ -3674,22 +3674,22 @@
         <v>0.01932621244695</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01478509281969276</v>
+        <v>0.01478509281969277</v>
       </c>
       <c r="BQ14" t="n">
         <v>0.01152011254863777</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.02489255885371965</v>
+        <v>0.02489255885371966</v>
       </c>
       <c r="BS14" t="n">
         <v>0.02762798312756579</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.03407933714016373</v>
+        <v>0.03407933714016372</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.03653309637381603</v>
+        <v>0.03653309637381602</v>
       </c>
       <c r="BV14" t="n">
         <v>0.02584852485115112</v>
@@ -3701,10 +3701,10 @@
         <v>0.02318878861811598</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.01898939651890569</v>
+        <v>0.01898939651890568</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.01553410251685019</v>
+        <v>0.01553410251685018</v>
       </c>
     </row>
     <row r="15">
@@ -3726,7 +3726,7 @@
         <v>0.002789251802392839</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001424053347866577</v>
+        <v>0.001424053347866576</v>
       </c>
       <c r="G15" t="n">
         <v>0.001287688428877839</v>
@@ -3792,7 +3792,7 @@
         <v>0.001072068682216801</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.00257336615069711</v>
+        <v>0.002573366150697109</v>
       </c>
       <c r="AC15" t="n">
         <v>0.00301348041238518</v>
@@ -3831,7 +3831,7 @@
         <v>0.00195086416647219</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.001870760399723949</v>
+        <v>0.001870760399723948</v>
       </c>
       <c r="AP15" t="n">
         <v>0.00197036281230378</v>
@@ -3903,13 +3903,13 @@
         <v>0.001929482841776176</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.002387077189694001</v>
+        <v>0.002387077189694</v>
       </c>
       <c r="BN15" t="n">
         <v>0.005119034197691</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.009393609170035001</v>
+        <v>0.009393609170034999</v>
       </c>
       <c r="BP15" t="n">
         <v>0.003240514650959302</v>
@@ -3988,19 +3988,19 @@
         <v>0.003247820223645693</v>
       </c>
       <c r="N16" t="n">
-        <v>0.003354895189327943</v>
+        <v>0.003354895189327942</v>
       </c>
       <c r="O16" t="n">
-        <v>0.003338003396389624</v>
+        <v>0.003338003396389623</v>
       </c>
       <c r="P16" t="n">
-        <v>0.005162171060867453</v>
+        <v>0.005162171060867454</v>
       </c>
       <c r="Q16" t="n">
         <v>0.004496117447621103</v>
       </c>
       <c r="R16" t="n">
-        <v>0.004490435384083299</v>
+        <v>0.0044904353840833</v>
       </c>
       <c r="S16" t="n">
         <v>0.005346889227240285</v>
@@ -4009,7 +4009,7 @@
         <v>0.005247856527636872</v>
       </c>
       <c r="U16" t="n">
-        <v>0.005416735100837085</v>
+        <v>0.005416735100837084</v>
       </c>
       <c r="V16" t="n">
         <v>0.007611885369904682</v>
@@ -4021,7 +4021,7 @@
         <v>0.007203536429031572</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.008938696106021151</v>
+        <v>0.00893869610602115</v>
       </c>
       <c r="Z16" t="n">
         <v>0.009146993071343677</v>
@@ -4030,7 +4030,7 @@
         <v>0.008968994337012584</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.005422962468700085</v>
+        <v>0.005422962468700086</v>
       </c>
       <c r="AC16" t="n">
         <v>0.006224276987326405</v>
@@ -4057,31 +4057,31 @@
         <v>0.005624115577661517</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.005213387741831672</v>
+        <v>0.005213387741831671</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0062836146194494</v>
+        <v>0.006283614619449401</v>
       </c>
       <c r="AM16" t="n">
         <v>0.005694958801448964</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.006453204476343261</v>
+        <v>0.006453204476343259</v>
       </c>
       <c r="AO16" t="n">
         <v>0.005759135321769804</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.006400209839168391</v>
+        <v>0.00640020983916839</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.005656731966255237</v>
+        <v>0.005656731966255236</v>
       </c>
       <c r="AR16" t="n">
         <v>0.006344586382157897</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.007092283504571138</v>
+        <v>0.007092283504571139</v>
       </c>
       <c r="AT16" t="n">
         <v>0.005541470214676141</v>
@@ -4111,7 +4111,7 @@
         <v>0.01823958132046985</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.01828296714659694</v>
+        <v>0.01828296714659693</v>
       </c>
       <c r="BD16" t="n">
         <v>0.02719043249572705</v>
@@ -4159,7 +4159,7 @@
         <v>0.01162200263156081</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.01234017236084642</v>
+        <v>0.01234017236084643</v>
       </c>
       <c r="BT16" t="n">
         <v>0.01512646632469355</v>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008159739594521925</v>
+        <v>0.0008159739594521924</v>
       </c>
       <c r="D17" t="n">
         <v>0.0008634171827324289</v>
@@ -4211,7 +4211,7 @@
         <v>0.004868841633299267</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005029862057562129</v>
+        <v>0.005029862057562127</v>
       </c>
       <c r="J17" t="n">
         <v>0.00198585124022714</v>
@@ -4226,7 +4226,7 @@
         <v>0.004645613469944895</v>
       </c>
       <c r="N17" t="n">
-        <v>0.005578596670677016</v>
+        <v>0.005578596670677017</v>
       </c>
       <c r="O17" t="n">
         <v>0.004101773396949581</v>
@@ -4235,7 +4235,7 @@
         <v>0.008070560677375349</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.006437775204262387</v>
+        <v>0.006437775204262388</v>
       </c>
       <c r="R17" t="n">
         <v>0.007197415462550327</v>
@@ -4256,16 +4256,16 @@
         <v>0.007123166912644055</v>
       </c>
       <c r="X17" t="n">
-        <v>0.007111428002245542</v>
+        <v>0.007111428002245543</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.005926124171595332</v>
+        <v>0.005926124171595333</v>
       </c>
       <c r="Z17" t="n">
         <v>0.005612990712043483</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.007157702640699007</v>
+        <v>0.007157702640699005</v>
       </c>
       <c r="AB17" t="n">
         <v>0.002934104051035908</v>
@@ -4283,7 +4283,7 @@
         <v>0.001362887562829491</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001741313954561996</v>
+        <v>0.001741313954561995</v>
       </c>
       <c r="AH17" t="n">
         <v>0.005419844078309601</v>
@@ -4310,10 +4310,10 @@
         <v>0.009796613677345089</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.01062433590079606</v>
+        <v>0.01062433590079605</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.002014962215701794</v>
+        <v>0.002014962215701793</v>
       </c>
       <c r="AR17" t="n">
         <v>0.003183303781061957</v>
@@ -4334,7 +4334,7 @@
         <v>0.001220480129089584</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0007371045464355392</v>
+        <v>0.0007371045464355394</v>
       </c>
       <c r="AY17" t="n">
         <v>0.0005177653413473382</v>
@@ -4343,7 +4343,7 @@
         <v>0.0007108715591008039</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0006227901185917688</v>
+        <v>0.0006227901185917689</v>
       </c>
       <c r="BB17" t="n">
         <v>0.0009791253014351526</v>
@@ -4355,7 +4355,7 @@
         <v>0.01128635018459437</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.004470396099516054</v>
+        <v>0.004470396099516055</v>
       </c>
       <c r="BF17" t="n">
         <v>0.0002176435358098873</v>
@@ -4379,7 +4379,7 @@
         <v>0.0003929773392787147</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0004429581834160001</v>
+        <v>0.000442958183416</v>
       </c>
       <c r="BN17" t="n">
         <v>0.000457820122875</v>
@@ -4676,7 +4676,7 @@
         <v>0.003215403887863355</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004742899048256368</v>
+        <v>0.004742899048256369</v>
       </c>
       <c r="G19" t="n">
         <v>0.001750539528713412</v>
@@ -4691,10 +4691,10 @@
         <v>0.002430217446407068</v>
       </c>
       <c r="K19" t="n">
-        <v>0.002606957933354005</v>
+        <v>0.002606957933354004</v>
       </c>
       <c r="L19" t="n">
-        <v>0.002386815804212287</v>
+        <v>0.002386815804212286</v>
       </c>
       <c r="M19" t="n">
         <v>0.001733754052076915</v>
@@ -4715,7 +4715,7 @@
         <v>0.002243938519125376</v>
       </c>
       <c r="S19" t="n">
-        <v>0.002655706627529777</v>
+        <v>0.002655706627529778</v>
       </c>
       <c r="T19" t="n">
         <v>0.002523644150561539</v>
@@ -4748,7 +4748,7 @@
         <v>0.004375406429050402</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.004874025240612481</v>
+        <v>0.00487402524061248</v>
       </c>
       <c r="AE19" t="n">
         <v>0.003829236991667895</v>
@@ -4766,10 +4766,10 @@
         <v>0.002403552426095056</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.002671349825555876</v>
+        <v>0.002671349825555877</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.002726537900688475</v>
+        <v>0.002726537900688476</v>
       </c>
       <c r="AL19" t="n">
         <v>0.0033240920573011</v>
@@ -4781,13 +4781,13 @@
         <v>0.00315260346429906</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.002650679614276084</v>
+        <v>0.002650679614276083</v>
       </c>
       <c r="AP19" t="n">
         <v>0.003047425970347553</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.002132792450222454</v>
+        <v>0.002132792450222453</v>
       </c>
       <c r="AR19" t="n">
         <v>0.003217690965632633</v>
@@ -4817,7 +4817,7 @@
         <v>0.003000040143569708</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.003708091798110701</v>
+        <v>0.0037080917981107</v>
       </c>
       <c r="BB19" t="n">
         <v>0.001984118795059495</v>
@@ -4844,7 +4844,7 @@
         <v>0.002849897416201045</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.009628026023779199</v>
+        <v>0.0096280260237792</v>
       </c>
       <c r="BK19" t="n">
         <v>0.001838421768791798</v>
@@ -4856,7 +4856,7 @@
         <v>0.00142917498414</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.0008474442649570001</v>
+        <v>0.0008474442649570002</v>
       </c>
       <c r="BO19" t="n">
         <v>0.00066217543239</v>
@@ -5459,16 +5459,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3208443565005761</v>
+        <v>0.320844356500576</v>
       </c>
       <c r="D23" t="n">
-        <v>0.215413419605969</v>
+        <v>0.2154134196059691</v>
       </c>
       <c r="E23" t="n">
         <v>0.1172059667990647</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1240586287985129</v>
+        <v>0.1240586287985128</v>
       </c>
       <c r="G23" t="n">
         <v>0.08033604112801793</v>
@@ -5483,7 +5483,7 @@
         <v>0.06833077096710122</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06595237488752562</v>
+        <v>0.0659523748875256</v>
       </c>
       <c r="L23" t="n">
         <v>0.06230820651610022</v>
@@ -5498,22 +5498,22 @@
         <v>0.1129252539909291</v>
       </c>
       <c r="P23" t="n">
-        <v>0.08759610263059396</v>
+        <v>0.08759610263059395</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.07362879711331712</v>
+        <v>0.07362879711331709</v>
       </c>
       <c r="R23" t="n">
         <v>0.06978160240857775</v>
       </c>
       <c r="S23" t="n">
-        <v>0.06042675313456904</v>
+        <v>0.06042675313456905</v>
       </c>
       <c r="T23" t="n">
         <v>0.06686733958958141</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0597770431094692</v>
+        <v>0.05977704310946918</v>
       </c>
       <c r="V23" t="n">
         <v>0.109385414784206</v>
@@ -5525,7 +5525,7 @@
         <v>0.1070315867905702</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1411918591773611</v>
+        <v>0.141191859177361</v>
       </c>
       <c r="Z23" t="n">
         <v>0.182078861526926</v>
@@ -5534,16 +5534,16 @@
         <v>0.1515535902351397</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.0614400675855466</v>
+        <v>0.06144006758554661</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.08069804681241305</v>
+        <v>0.08069804681241308</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.09411322477836871</v>
+        <v>0.0941132247783687</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.09860842451415358</v>
+        <v>0.09860842451415357</v>
       </c>
       <c r="AF23" t="n">
         <v>0.08630253927132216</v>
@@ -5558,13 +5558,13 @@
         <v>0.1120454278327464</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.09292284668962844</v>
+        <v>0.09292284668962843</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.07270384745513229</v>
+        <v>0.07270384745513231</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.07797248884702555</v>
+        <v>0.0779724888470256</v>
       </c>
       <c r="AM23" t="n">
         <v>0.07297809008226636</v>
@@ -5579,43 +5579,43 @@
         <v>0.105704253334346</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.07033708006300016</v>
+        <v>0.07033708006300014</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.08142261483391738</v>
+        <v>0.08142261483391736</v>
       </c>
       <c r="AS23" t="n">
         <v>0.1069155275501203</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.1909554274358723</v>
+        <v>0.1909554274358722</v>
       </c>
       <c r="AU23" t="n">
         <v>0.1460380544540667</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.1635543759349877</v>
+        <v>0.1635543759349876</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.1814993039898484</v>
+        <v>0.1814993039898483</v>
       </c>
       <c r="AX23" t="n">
         <v>0.0324367975315425</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.04033436197878466</v>
+        <v>0.04033436197878468</v>
       </c>
       <c r="AZ23" t="n">
         <v>0.05479659139434438</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.05844035338240643</v>
+        <v>0.05844035338240644</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.2160020461209928</v>
+        <v>0.2160020461209927</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.1579754972674479</v>
+        <v>0.157975497267448</v>
       </c>
       <c r="BD23" t="n">
         <v>0.2525535527142941</v>
@@ -5627,7 +5627,7 @@
         <v>0.1109962392514576</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.1070317337930672</v>
+        <v>0.1070317337930671</v>
       </c>
       <c r="BH23" t="n">
         <v>0.119752938236844</v>
@@ -5636,16 +5636,16 @@
         <v>0.11941165516026</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.1237277784287433</v>
+        <v>0.1237277784287432</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.05559217365756216</v>
+        <v>0.05559217365756217</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.09400224249534252</v>
+        <v>0.09400224249534254</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.04789394533640898</v>
+        <v>0.047893945336409</v>
       </c>
       <c r="BN23" t="n">
         <v>0.037330012613686</v>
@@ -5654,10 +5654,10 @@
         <v>0.05254259205315603</v>
       </c>
       <c r="BP23" t="n">
-        <v>0.1103461544049838</v>
+        <v>0.1103461544049839</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0.0710374797112331</v>
+        <v>0.07103747971123307</v>
       </c>
       <c r="BR23" t="n">
         <v>0.1234938918115044</v>
@@ -5672,16 +5672,16 @@
         <v>0.1232200346835067</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.07333342537727426</v>
+        <v>0.07333342537727428</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.07130783250283869</v>
+        <v>0.07130783250283872</v>
       </c>
       <c r="BX23" t="n">
         <v>0.07185162988965116</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.07219776544156689</v>
+        <v>0.07219776544156691</v>
       </c>
       <c r="BZ23" t="n">
         <v>0.06478227947930569</v>
@@ -5986,10 +5986,10 @@
         <v>0.001428537332036</v>
       </c>
       <c r="BP25" t="n">
-        <v>0.0005168459556694666</v>
+        <v>0.0005168459556694665</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0.0002135653240629082</v>
+        <v>0.0002135653240629081</v>
       </c>
       <c r="BR25" t="n">
         <v>0.0006827299461645387</v>
@@ -6509,7 +6509,7 @@
         <v>0.0001431027383132618</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0001424154180331319</v>
+        <v>0.0001424154180331318</v>
       </c>
       <c r="F28" t="n">
         <v>0.0003973274949688903</v>
@@ -6518,10 +6518,10 @@
         <v>7.635726773272987e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>7.597369700000186e-05</v>
+        <v>7.597369700000188e-05</v>
       </c>
       <c r="I28" t="n">
-        <v>7.373327542965275e-05</v>
+        <v>7.373327542965274e-05</v>
       </c>
       <c r="J28" t="n">
         <v>8.881127008107037e-05</v>
@@ -6530,13 +6530,13 @@
         <v>0.0001046082256921506</v>
       </c>
       <c r="L28" t="n">
-        <v>7.967315415650923e-05</v>
+        <v>7.967315415650922e-05</v>
       </c>
       <c r="M28" t="n">
         <v>5.618634889925427e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>6.414504086288746e-05</v>
+        <v>6.414504086288747e-05</v>
       </c>
       <c r="O28" t="n">
         <v>5.633089106026419e-05</v>
@@ -6557,13 +6557,13 @@
         <v>7.125894810714698e-05</v>
       </c>
       <c r="U28" t="n">
-        <v>7.634154197983183e-05</v>
+        <v>7.634154197983184e-05</v>
       </c>
       <c r="V28" t="n">
-        <v>9.859975614865238e-05</v>
+        <v>9.859975614865237e-05</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0001001929622898236</v>
+        <v>0.0001001929622898237</v>
       </c>
       <c r="X28" t="n">
         <v>0.0001000835438451899</v>
@@ -6584,7 +6584,7 @@
         <v>0.0001716267580413807</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.0001704994905255065</v>
+        <v>0.0001704994905255064</v>
       </c>
       <c r="AE28" t="n">
         <v>0.0001369681469169641</v>
@@ -6593,10 +6593,10 @@
         <v>6.872431815464377e-05</v>
       </c>
       <c r="AG28" t="n">
-        <v>8.404978525415754e-05</v>
+        <v>8.404978525415752e-05</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.954890279870983e-05</v>
+        <v>4.954890279870984e-05</v>
       </c>
       <c r="AI28" t="n">
         <v>8.890916871926854e-05</v>
@@ -6611,7 +6611,7 @@
         <v>0.0001094062472141895</v>
       </c>
       <c r="AM28" t="n">
-        <v>8.860482057296082e-05</v>
+        <v>8.860482057296081e-05</v>
       </c>
       <c r="AN28" t="n">
         <v>0.0001058221839047486</v>
@@ -6623,7 +6623,7 @@
         <v>9.809880779258885e-05</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.9108146980436e-05</v>
+        <v>7.910814698043599e-05</v>
       </c>
       <c r="AR28" t="n">
         <v>0.0001247359282645608</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.05161323425854673</v>
+        <v>0.05161323425854674</v>
       </c>
       <c r="D29" t="n">
         <v>0.1937396268530673</v>
@@ -6744,13 +6744,13 @@
         <v>0.02378115517528512</v>
       </c>
       <c r="H29" t="n">
-        <v>0.02255584114044653</v>
+        <v>0.02255584114044652</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02216740808002087</v>
+        <v>0.02216740808002086</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0214037771682923</v>
+        <v>0.02140377716829229</v>
       </c>
       <c r="K29" t="n">
         <v>0.02194534480352572</v>
@@ -6780,37 +6780,37 @@
         <v>0.02540862232349336</v>
       </c>
       <c r="T29" t="n">
-        <v>0.02397932275204744</v>
+        <v>0.02397932275204743</v>
       </c>
       <c r="U29" t="n">
         <v>0.02515250984944163</v>
       </c>
       <c r="V29" t="n">
-        <v>0.03345971988071914</v>
+        <v>0.03345971988071913</v>
       </c>
       <c r="W29" t="n">
         <v>0.03438158862292283</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0342512372240825</v>
+        <v>0.03425123722408251</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.03727066623986038</v>
+        <v>0.0372706662398604</v>
       </c>
       <c r="Z29" t="n">
         <v>0.03240772667304067</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03939649915032469</v>
+        <v>0.03939649915032468</v>
       </c>
       <c r="AB29" t="n">
         <v>0.03448207072675304</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.04320495019843537</v>
+        <v>0.04320495019843536</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.04162821690534636</v>
+        <v>0.04162821690534637</v>
       </c>
       <c r="AE29" t="n">
         <v>0.0243468380180186</v>
@@ -6834,7 +6834,7 @@
         <v>0.02783720424625108</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.0323658203825892</v>
+        <v>0.03236582038258921</v>
       </c>
       <c r="AM29" t="n">
         <v>0.03043246743680176</v>
@@ -6861,7 +6861,7 @@
         <v>0.02683934551725007</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.03298613030227199</v>
+        <v>0.03298613030227198</v>
       </c>
       <c r="AV29" t="n">
         <v>0.03240068340601739</v>
@@ -6870,19 +6870,19 @@
         <v>0.03063182322043375</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.0326722073698164</v>
+        <v>0.03267220736981639</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.02791484395844428</v>
+        <v>0.02791484395844429</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.03750664736686245</v>
+        <v>0.03750664736686246</v>
       </c>
       <c r="BA29" t="n">
         <v>0.02721354355892404</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.03653610696846718</v>
+        <v>0.03653610696846721</v>
       </c>
       <c r="BC29" t="n">
         <v>0.02324129773551014</v>
@@ -6891,10 +6891,10 @@
         <v>0.04092063236908518</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.01868147422090423</v>
+        <v>0.01868147422090424</v>
       </c>
       <c r="BF29" t="n">
-        <v>0.03801720547165044</v>
+        <v>0.03801720547165045</v>
       </c>
       <c r="BG29" t="n">
         <v>0.03409570703078039</v>
@@ -6912,7 +6912,7 @@
         <v>0.01538440339292617</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.02045685533812562</v>
+        <v>0.02045685533812561</v>
       </c>
       <c r="BM29" t="n">
         <v>0.010037854482453</v>
@@ -6924,10 +6924,10 @@
         <v>0.010499729625048</v>
       </c>
       <c r="BP29" t="n">
-        <v>0.04420767907804682</v>
+        <v>0.04420767907804683</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0.03123757337228381</v>
+        <v>0.03123757337228382</v>
       </c>
       <c r="BR29" t="n">
         <v>0.01637024842820569</v>
@@ -6945,16 +6945,16 @@
         <v>0.01788163400250088</v>
       </c>
       <c r="BW29" t="n">
-        <v>0.02061711381252879</v>
+        <v>0.02061711381252878</v>
       </c>
       <c r="BX29" t="n">
         <v>0.02161097345913124</v>
       </c>
       <c r="BY29" t="n">
-        <v>0.02152030137081877</v>
+        <v>0.02152030137081878</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0.01991878073985018</v>
+        <v>0.01991878073985019</v>
       </c>
     </row>
     <row r="30">
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.08086852804088832</v>
+        <v>0.08086852804088834</v>
       </c>
       <c r="D32" t="n">
         <v>0.05886591207445761</v>
@@ -7148,19 +7148,19 @@
         <v>0.04868706948254356</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07818868369134901</v>
+        <v>0.07818868369134903</v>
       </c>
       <c r="G32" t="n">
         <v>0.02708367543860904</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02483430944492418</v>
+        <v>0.02483430944492417</v>
       </c>
       <c r="I32" t="n">
         <v>0.0287397415751385</v>
       </c>
       <c r="J32" t="n">
-        <v>0.04679776255671783</v>
+        <v>0.04679776255671784</v>
       </c>
       <c r="K32" t="n">
         <v>0.05566713871239079</v>
@@ -7169,7 +7169,7 @@
         <v>0.04469200901876304</v>
       </c>
       <c r="M32" t="n">
-        <v>0.02398989770695372</v>
+        <v>0.02398989770695373</v>
       </c>
       <c r="N32" t="n">
         <v>0.02663936832914213</v>
@@ -7178,25 +7178,25 @@
         <v>0.031472793471658</v>
       </c>
       <c r="P32" t="n">
-        <v>0.03284324049720027</v>
+        <v>0.03284324049720026</v>
       </c>
       <c r="Q32" t="n">
         <v>0.02834317017862426</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0285322820723574</v>
+        <v>0.02853228207235741</v>
       </c>
       <c r="S32" t="n">
-        <v>0.03160296600545338</v>
+        <v>0.03160296600545336</v>
       </c>
       <c r="T32" t="n">
         <v>0.0324982281224343</v>
       </c>
       <c r="U32" t="n">
-        <v>0.03244257526840127</v>
+        <v>0.03244257526840126</v>
       </c>
       <c r="V32" t="n">
-        <v>0.05292336557912808</v>
+        <v>0.05292336557912806</v>
       </c>
       <c r="W32" t="n">
         <v>0.05344823099832626</v>
@@ -7205,16 +7205,16 @@
         <v>0.05058714268957816</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.06303303006753989</v>
+        <v>0.06303303006753991</v>
       </c>
       <c r="Z32" t="n">
         <v>0.07193984764387817</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.06477655687572759</v>
+        <v>0.0647765568757276</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.09467621544861476</v>
+        <v>0.09467621544861475</v>
       </c>
       <c r="AC32" t="n">
         <v>0.1138394648529392</v>
@@ -7223,31 +7223,31 @@
         <v>0.122297606979586</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.07469786113848789</v>
+        <v>0.07469786113848792</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.03466042981410484</v>
+        <v>0.03466042981410483</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.04389141545237907</v>
+        <v>0.04389141545237906</v>
       </c>
       <c r="AH32" t="n">
         <v>0.02383243706744505</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.04244746430668318</v>
+        <v>0.04244746430668317</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.04362588052895775</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.0518093963902479</v>
+        <v>0.05180939639024791</v>
       </c>
       <c r="AL32" t="n">
         <v>0.06855816054235099</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.05311053098252219</v>
+        <v>0.05311053098252221</v>
       </c>
       <c r="AN32" t="n">
         <v>0.05462487752569137</v>
@@ -7256,19 +7256,19 @@
         <v>0.04594706306382935</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.05045294725558196</v>
+        <v>0.05045294725558195</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.03865157369949904</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.05563368875797649</v>
+        <v>0.0556336887579765</v>
       </c>
       <c r="AS32" t="n">
         <v>0.03590754810357977</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.05747159825095004</v>
+        <v>0.05747159825095003</v>
       </c>
       <c r="AU32" t="n">
         <v>0.05453921005105521</v>
@@ -7277,19 +7277,19 @@
         <v>0.05210259347751038</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.08833676256473279</v>
+        <v>0.08833676256473276</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.0535619603934601</v>
+        <v>0.05356196039346009</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.03899530468943127</v>
+        <v>0.03899530468943128</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.05403604247833303</v>
+        <v>0.05403604247833305</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.04166558846217791</v>
+        <v>0.0416655884621779</v>
       </c>
       <c r="BB32" t="n">
         <v>0.1169477761025242</v>
@@ -7298,7 +7298,7 @@
         <v>0.09082137555628469</v>
       </c>
       <c r="BD32" t="n">
-        <v>0.1187487819921037</v>
+        <v>0.1187487819921036</v>
       </c>
       <c r="BE32" t="n">
         <v>0.07596562812882994</v>
@@ -7313,19 +7313,19 @@
         <v>0.1133944924508619</v>
       </c>
       <c r="BI32" t="n">
-        <v>0.1122283732574563</v>
+        <v>0.1122283732574564</v>
       </c>
       <c r="BJ32" t="n">
         <v>0.09167672850950241</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.0470833188650631</v>
+        <v>0.04708331886506311</v>
       </c>
       <c r="BL32" t="n">
         <v>0.04561000418221187</v>
       </c>
       <c r="BM32" t="n">
-        <v>0.04989081382694398</v>
+        <v>0.04989081382694399</v>
       </c>
       <c r="BN32" t="n">
         <v>0.037495175044443</v>
@@ -7334,13 +7334,13 @@
         <v>0.03563583985321801</v>
       </c>
       <c r="BP32" t="n">
-        <v>0.04706036281811711</v>
+        <v>0.04706036281811712</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0.0371130348445746</v>
+        <v>0.03711303484457459</v>
       </c>
       <c r="BR32" t="n">
-        <v>0.04433766819588678</v>
+        <v>0.04433766819588677</v>
       </c>
       <c r="BS32" t="n">
         <v>0.04855434551309767</v>
@@ -7355,16 +7355,16 @@
         <v>0.06478428738358505</v>
       </c>
       <c r="BW32" t="n">
-        <v>0.08017531720107633</v>
+        <v>0.08017531720107636</v>
       </c>
       <c r="BX32" t="n">
-        <v>0.08738916479359571</v>
+        <v>0.08738916479359572</v>
       </c>
       <c r="BY32" t="n">
-        <v>0.09064716467558577</v>
+        <v>0.09064716467558576</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0.08169141273813735</v>
+        <v>0.08169141273813736</v>
       </c>
     </row>
     <row r="33">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.04089209820732145</v>
+        <v>0.04089209820732146</v>
       </c>
       <c r="D33" t="n">
         <v>0.04869644744851479</v>
       </c>
       <c r="E33" t="n">
-        <v>0.04284633029455416</v>
+        <v>0.04284633029455417</v>
       </c>
       <c r="F33" t="n">
         <v>0.04293598422744917</v>
@@ -7392,13 +7392,13 @@
         <v>0.04243411313614217</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03702500226432195</v>
+        <v>0.03702500226432194</v>
       </c>
       <c r="I33" t="n">
         <v>0.04558721617390476</v>
       </c>
       <c r="J33" t="n">
-        <v>0.06084112248586105</v>
+        <v>0.06084112248586104</v>
       </c>
       <c r="K33" t="n">
         <v>0.07057969914834493</v>
@@ -7419,7 +7419,7 @@
         <v>0.04659274640204927</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04496333527704748</v>
+        <v>0.04496333527704749</v>
       </c>
       <c r="R33" t="n">
         <v>0.04134974583883249</v>
@@ -7467,13 +7467,13 @@
         <v>0.04226519334357057</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.06031999047012186</v>
+        <v>0.06031999047012187</v>
       </c>
       <c r="AH33" t="n">
         <v>0.0288317979652771</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.04671167800472805</v>
+        <v>0.04671167800472804</v>
       </c>
       <c r="AJ33" t="n">
         <v>0.04874171946891495</v>
@@ -7482,7 +7482,7 @@
         <v>0.05688212275661492</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.08205635108287225</v>
+        <v>0.08205635108287228</v>
       </c>
       <c r="AM33" t="n">
         <v>0.05915471133627643</v>
@@ -7491,10 +7491,10 @@
         <v>0.07104464472032312</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.05557523906232009</v>
+        <v>0.0555752390623201</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.05030053932858596</v>
+        <v>0.05030053932858595</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.04181736931071485</v>
@@ -7503,13 +7503,13 @@
         <v>0.05524950659870086</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.04394923845949143</v>
+        <v>0.04394923845949144</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.06021951537336685</v>
+        <v>0.06021951537336686</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.07346421660992238</v>
+        <v>0.07346421660992236</v>
       </c>
       <c r="AV33" t="n">
         <v>0.06582061040767601</v>
@@ -7530,7 +7530,7 @@
         <v>0.08202339666101434</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.09451494580100037</v>
+        <v>0.09451494580100035</v>
       </c>
       <c r="BC33" t="n">
         <v>0.06043341082748839</v>
@@ -7548,19 +7548,19 @@
         <v>0.05007890426394854</v>
       </c>
       <c r="BH33" t="n">
-        <v>0.05632238108095817</v>
+        <v>0.05632238108095818</v>
       </c>
       <c r="BI33" t="n">
         <v>0.05189771094910962</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.04019823998648881</v>
+        <v>0.0401982399864888</v>
       </c>
       <c r="BK33" t="n">
         <v>0.02985399441560724</v>
       </c>
       <c r="BL33" t="n">
-        <v>0.03145374251808077</v>
+        <v>0.03145374251808076</v>
       </c>
       <c r="BM33" t="n">
         <v>0.04303102293794</v>
@@ -7575,7 +7575,7 @@
         <v>0.0222370933549469</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0.01368654628570524</v>
+        <v>0.01368654628570525</v>
       </c>
       <c r="BR33" t="n">
         <v>0.05784118532753057</v>
@@ -7584,22 +7584,22 @@
         <v>0.06142019140693977</v>
       </c>
       <c r="BT33" t="n">
-        <v>0.05581740568900412</v>
+        <v>0.05581740568900411</v>
       </c>
       <c r="BU33" t="n">
-        <v>0.05604399904367948</v>
+        <v>0.05604399904367947</v>
       </c>
       <c r="BV33" t="n">
         <v>0.03784011924159795</v>
       </c>
       <c r="BW33" t="n">
-        <v>0.04224395451994685</v>
+        <v>0.04224395451994687</v>
       </c>
       <c r="BX33" t="n">
         <v>0.04607442704742617</v>
       </c>
       <c r="BY33" t="n">
-        <v>0.04424284720338581</v>
+        <v>0.04424284720338582</v>
       </c>
       <c r="BZ33" t="n">
         <v>0.03733737455734325</v>
@@ -7986,7 +7986,7 @@
         <v>0.0001106098665233601</v>
       </c>
       <c r="H36" t="n">
-        <v>9.254065795979337e-05</v>
+        <v>9.254065795979336e-05</v>
       </c>
       <c r="I36" t="n">
         <v>0.0001251323354108479</v>
@@ -8034,7 +8034,7 @@
         <v>0.0002186046756592321</v>
       </c>
       <c r="X36" t="n">
-        <v>0.0002433823741195339</v>
+        <v>0.0002433823741195338</v>
       </c>
       <c r="Y36" t="n">
         <v>0.0002481671319361806</v>
@@ -8043,19 +8043,19 @@
         <v>0.0002988978181169974</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.0002779223686611941</v>
+        <v>0.0002779223686611942</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.0003052112361814047</v>
+        <v>0.0003052112361814046</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.0003683190789044036</v>
+        <v>0.0003683190789044037</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.0004446422269929932</v>
+        <v>0.0004446422269929933</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0003296000848543016</v>
+        <v>0.0003296000848543017</v>
       </c>
       <c r="AF36" t="n">
         <v>0.0001440898028391932</v>
@@ -8064,10 +8064,10 @@
         <v>0.0001732108415616983</v>
       </c>
       <c r="AH36" t="n">
-        <v>9.765879293583725e-05</v>
+        <v>9.765879293583726e-05</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.0001732311734174352</v>
+        <v>0.0001732311734174351</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.0001771685696752035</v>
@@ -8085,7 +8085,7 @@
         <v>0.0002105813372908991</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.0001911422558714877</v>
+        <v>0.0001911422558714876</v>
       </c>
       <c r="AP36" t="n">
         <v>0.0002089516211224321</v>
@@ -8100,13 +8100,13 @@
         <v>0.0001508589053250189</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.000205624264845709</v>
+        <v>0.0002056242648457089</v>
       </c>
       <c r="AU36" t="n">
         <v>0.0002293602579536671</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.0002111462161482678</v>
+        <v>0.0002111462161482677</v>
       </c>
       <c r="AW36" t="n">
         <v>0.001015356009300522</v>
@@ -8148,10 +8148,10 @@
         <v>0.002458798478157503</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.004713026961410081</v>
+        <v>0.00471302696141008</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.004487094390929371</v>
+        <v>0.00448709439092937</v>
       </c>
       <c r="BL36" t="n">
         <v>0.001057737081655551</v>
@@ -8163,7 +8163,7 @@
         <v>0.0009424503514140002</v>
       </c>
       <c r="BO36" t="n">
-        <v>0.000860235194566</v>
+        <v>0.0008602351945660001</v>
       </c>
       <c r="BP36" t="n">
         <v>0.002963040577218874</v>
@@ -8212,10 +8212,10 @@
         <v>0.02934521426469704</v>
       </c>
       <c r="D37" t="n">
-        <v>0.04343818644612286</v>
+        <v>0.04343818644612287</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07297885831143225</v>
+        <v>0.07297885831143226</v>
       </c>
       <c r="F37" t="n">
         <v>0.02635010312095915</v>
@@ -8230,13 +8230,13 @@
         <v>0.01858033932724784</v>
       </c>
       <c r="J37" t="n">
-        <v>0.03286443085799679</v>
+        <v>0.0328644308579968</v>
       </c>
       <c r="K37" t="n">
         <v>0.03726538659635743</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02949412060044298</v>
+        <v>0.02949412060044297</v>
       </c>
       <c r="M37" t="n">
         <v>0.01559721797243444</v>
@@ -8245,37 +8245,37 @@
         <v>0.0162822100584973</v>
       </c>
       <c r="O37" t="n">
-        <v>0.02622883664725226</v>
+        <v>0.02622883664725227</v>
       </c>
       <c r="P37" t="n">
         <v>0.0278793476619497</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.02476757353196356</v>
+        <v>0.02476757353196357</v>
       </c>
       <c r="R37" t="n">
         <v>0.02519416158484606</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02636640082250944</v>
+        <v>0.02636640082250943</v>
       </c>
       <c r="T37" t="n">
         <v>0.02560750285425682</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02516793213286805</v>
+        <v>0.02516793213286804</v>
       </c>
       <c r="V37" t="n">
-        <v>0.03239108414581088</v>
+        <v>0.03239108414581089</v>
       </c>
       <c r="W37" t="n">
         <v>0.03409211359631</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02931941689248587</v>
+        <v>0.02931941689248586</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.03398600246477874</v>
+        <v>0.03398600246477875</v>
       </c>
       <c r="Z37" t="n">
         <v>0.03074976640514909</v>
@@ -8284,13 +8284,13 @@
         <v>0.03585340637327934</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.04039701160416454</v>
+        <v>0.04039701160416453</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.05847134603605859</v>
+        <v>0.05847134603605858</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.0570484250734734</v>
+        <v>0.05704842507347341</v>
       </c>
       <c r="AE37" t="n">
         <v>0.04000306438492565</v>
@@ -8308,19 +8308,19 @@
         <v>0.03294369766672366</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.0327466098274993</v>
+        <v>0.03274660982749929</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.04496425894551351</v>
+        <v>0.0449642589455135</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.05403739661488218</v>
+        <v>0.05403739661488217</v>
       </c>
       <c r="AM37" t="n">
         <v>0.04786718509221028</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.03679094726826665</v>
+        <v>0.03679094726826666</v>
       </c>
       <c r="AO37" t="n">
         <v>0.03342043480887056</v>
@@ -8329,22 +8329,22 @@
         <v>0.03540696115093275</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.02516198454024637</v>
+        <v>0.02516198454024638</v>
       </c>
       <c r="AR37" t="n">
         <v>0.03437784634721471</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.02412704330925888</v>
+        <v>0.02412704330925889</v>
       </c>
       <c r="AT37" t="n">
         <v>0.04779499643609249</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.04124543242418707</v>
+        <v>0.04124543242418705</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.04188455795239149</v>
+        <v>0.0418845579523915</v>
       </c>
       <c r="AW37" t="n">
         <v>0.07367890065650859</v>
@@ -8359,55 +8359,55 @@
         <v>0.03481863917339705</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.01581704935022681</v>
+        <v>0.01581704935022682</v>
       </c>
       <c r="BB37" t="n">
         <v>0.09622095526240426</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.06930708318250661</v>
+        <v>0.06930708318250663</v>
       </c>
       <c r="BD37" t="n">
-        <v>0.09379006199189099</v>
+        <v>0.09379006199189097</v>
       </c>
       <c r="BE37" t="n">
-        <v>0.04842426997584361</v>
+        <v>0.04842426997584363</v>
       </c>
       <c r="BF37" t="n">
         <v>0.08992084610598554</v>
       </c>
       <c r="BG37" t="n">
-        <v>0.08536591983287181</v>
+        <v>0.08536591983287185</v>
       </c>
       <c r="BH37" t="n">
         <v>0.1032704525868096</v>
       </c>
       <c r="BI37" t="n">
-        <v>0.09606870729184852</v>
+        <v>0.09606870729184853</v>
       </c>
       <c r="BJ37" t="n">
         <v>0.0425119185698856</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.02246844458742796</v>
+        <v>0.02246844458742795</v>
       </c>
       <c r="BL37" t="n">
-        <v>0.01657309084914641</v>
+        <v>0.0165730908491464</v>
       </c>
       <c r="BM37" t="n">
         <v>0.028960050873293</v>
       </c>
       <c r="BN37" t="n">
-        <v>0.04993478638636301</v>
+        <v>0.049934786386363</v>
       </c>
       <c r="BO37" t="n">
         <v>0.056057411931915</v>
       </c>
       <c r="BP37" t="n">
-        <v>0.02723644291398002</v>
+        <v>0.02723644291398003</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0.01662809308079343</v>
+        <v>0.01662809308079342</v>
       </c>
       <c r="BR37" t="n">
         <v>0.04695853858380743</v>
@@ -8419,22 +8419,22 @@
         <v>0.06920118763140928</v>
       </c>
       <c r="BU37" t="n">
-        <v>0.08080280687936595</v>
+        <v>0.08080280687936596</v>
       </c>
       <c r="BV37" t="n">
         <v>0.06648571959135273</v>
       </c>
       <c r="BW37" t="n">
-        <v>0.08197961675108625</v>
+        <v>0.08197961675108624</v>
       </c>
       <c r="BX37" t="n">
-        <v>0.0937173861192357</v>
+        <v>0.09371738611923568</v>
       </c>
       <c r="BY37" t="n">
         <v>0.09175604787608491</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0.07093717299439817</v>
+        <v>0.07093717299439814</v>
       </c>
     </row>
     <row r="38">
@@ -9061,7 +9061,7 @@
         <v>0.0007113280793163522</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.0005359830752737136</v>
+        <v>0.0005359830752737137</v>
       </c>
       <c r="AT43" t="n">
         <v>0.0005696189588042548</v>
@@ -9100,7 +9100,7 @@
         <v>0.001180751148836009</v>
       </c>
       <c r="BF43" t="n">
-        <v>0.0009423304235904468</v>
+        <v>0.0009423304235904469</v>
       </c>
       <c r="BG43" t="n">
         <v>0.0009079313824777999</v>
@@ -9176,7 +9176,7 @@
         <v>0.0006906517668779341</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007345179282229173</v>
+        <v>0.0007345179282229171</v>
       </c>
       <c r="E44" t="n">
         <v>0.0007286813554939124</v>
@@ -9185,7 +9185,7 @@
         <v>0.002379482114004293</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0002821969126536191</v>
+        <v>0.0002821969126536192</v>
       </c>
       <c r="H44" t="n">
         <v>0.0002610352202974439</v>
@@ -9200,10 +9200,10 @@
         <v>0.0004041036214240926</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0003495284171693681</v>
+        <v>0.0003495284171693682</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0002280000290082294</v>
+        <v>0.0002280000290082293</v>
       </c>
       <c r="N44" t="n">
         <v>0.0002393808770803761</v>
@@ -9212,7 +9212,7 @@
         <v>0.0002368320178932056</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0003399769539449598</v>
+        <v>0.0003399769539449599</v>
       </c>
       <c r="Q44" t="n">
         <v>0.0002922773131445313</v>
@@ -9230,28 +9230,28 @@
         <v>0.0003475492910157886</v>
       </c>
       <c r="V44" t="n">
-        <v>0.0004919386222872488</v>
+        <v>0.0004919386222872489</v>
       </c>
       <c r="W44" t="n">
-        <v>0.000515755860070786</v>
+        <v>0.0005157558600707861</v>
       </c>
       <c r="X44" t="n">
         <v>0.0005167573614099408</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.000590886392691412</v>
+        <v>0.0005908863926914122</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0005942913913028622</v>
+        <v>0.0005942913913028623</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0006267347194173037</v>
+        <v>0.0006267347194173036</v>
       </c>
       <c r="AB44" t="n">
         <v>0.0005890309195216571</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.0007305339073841655</v>
+        <v>0.0007305339073841656</v>
       </c>
       <c r="AD44" t="n">
         <v>0.0007376936958756999</v>
@@ -9260,10 +9260,10 @@
         <v>0.0005726945388758923</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0003229679957901762</v>
+        <v>0.0003229679957901761</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.0003611304658216217</v>
+        <v>0.0003611304658216216</v>
       </c>
       <c r="AH44" t="n">
         <v>0.0002132367680783868</v>
@@ -9278,13 +9278,13 @@
         <v>0.0004480992691228183</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.0005374784804561731</v>
+        <v>0.0005374784804561732</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.0004786566148071365</v>
+        <v>0.0004786566148071366</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.0004615607869486243</v>
+        <v>0.0004615607869486244</v>
       </c>
       <c r="AO44" t="n">
         <v>0.0004252867320855558</v>
@@ -9293,10 +9293,10 @@
         <v>0.0004651055058316485</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.000338484222180278</v>
+        <v>0.0003384842221802779</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.0004951571500580523</v>
+        <v>0.0004951571500580522</v>
       </c>
       <c r="AS44" t="n">
         <v>0.0003777417139028418</v>
@@ -9305,7 +9305,7 @@
         <v>0.0004714341830339178</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.0005173207261191078</v>
+        <v>0.0005173207261191077</v>
       </c>
       <c r="AV44" t="n">
         <v>0.0004629762008944935</v>
@@ -9323,10 +9323,10 @@
         <v>0.001382544250516152</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.001579200131754119</v>
+        <v>0.00157920013175412</v>
       </c>
       <c r="BB44" t="n">
-        <v>0.0009443297037733911</v>
+        <v>0.0009443297037733912</v>
       </c>
       <c r="BC44" t="n">
         <v>0.001314854107271866</v>
@@ -9347,10 +9347,10 @@
         <v>0.0006893138320887157</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.0007275797199780115</v>
+        <v>0.0007275797199780114</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0.007224539722094399</v>
+        <v>0.0072245397220944</v>
       </c>
       <c r="BK44" t="n">
         <v>0.00440553236045924</v>
@@ -9362,13 +9362,13 @@
         <v>0.001182919180961</v>
       </c>
       <c r="BN44" t="n">
-        <v>0.000669496491954</v>
+        <v>0.0006694964919540001</v>
       </c>
       <c r="BO44" t="n">
-        <v>0.000711518812859</v>
+        <v>0.0007115188128589999</v>
       </c>
       <c r="BP44" t="n">
-        <v>0.004724845716358262</v>
+        <v>0.004724845716358263</v>
       </c>
       <c r="BQ44" t="n">
         <v>0.004336316512052163</v>
@@ -9398,7 +9398,7 @@
         <v>0.0006417251121315134</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0.0006026146934179853</v>
+        <v>0.0006026146934179852</v>
       </c>
     </row>
     <row r="45">
@@ -9846,7 +9846,7 @@
         <v>0.0004446083939889183</v>
       </c>
       <c r="T48" t="n">
-        <v>0.0004166316851689866</v>
+        <v>0.0004166316851689865</v>
       </c>
       <c r="U48" t="n">
         <v>0.0004098688069242123</v>
@@ -9975,10 +9975,10 @@
         <v>0.00231110502760416</v>
       </c>
       <c r="BK48" t="n">
-        <v>0.0008824134723302296</v>
+        <v>0.0008824134723302295</v>
       </c>
       <c r="BL48" t="n">
-        <v>0.0006148918004782671</v>
+        <v>0.000614891800478267</v>
       </c>
       <c r="BM48" t="n">
         <v>0.000232051630946</v>
@@ -10011,7 +10011,7 @@
         <v>0.001290300764296935</v>
       </c>
       <c r="BW48" t="n">
-        <v>0.001274879345697322</v>
+        <v>0.001274879345697321</v>
       </c>
       <c r="BX48" t="n">
         <v>0.001267427498851738</v>
@@ -10579,7 +10579,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.1807384230839094</v>
+        <v>0.1807384230839093</v>
       </c>
       <c r="D54" t="n">
         <v>0.2244083061616104</v>
@@ -10588,55 +10588,55 @@
         <v>0.1458989347463394</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1898655784976917</v>
+        <v>0.1898655784976916</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05963823269816271</v>
+        <v>0.0596382326981627</v>
       </c>
       <c r="H54" t="n">
-        <v>0.05423711469210914</v>
+        <v>0.05423711469210915</v>
       </c>
       <c r="I54" t="n">
-        <v>0.05143403927058113</v>
+        <v>0.05143403927058116</v>
       </c>
       <c r="J54" t="n">
-        <v>0.08861473051631438</v>
+        <v>0.08861473051631437</v>
       </c>
       <c r="K54" t="n">
-        <v>0.08769148706878986</v>
+        <v>0.08769148706878988</v>
       </c>
       <c r="L54" t="n">
-        <v>0.07506259669369784</v>
+        <v>0.07506259669369787</v>
       </c>
       <c r="M54" t="n">
         <v>0.03471172123205261</v>
       </c>
       <c r="N54" t="n">
-        <v>0.03859265357287902</v>
+        <v>0.03859265357287901</v>
       </c>
       <c r="O54" t="n">
-        <v>0.05026485321385041</v>
+        <v>0.05026485321385039</v>
       </c>
       <c r="P54" t="n">
-        <v>0.04611349091886325</v>
+        <v>0.04611349091886324</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.03780440914502886</v>
+        <v>0.03780440914502887</v>
       </c>
       <c r="R54" t="n">
-        <v>0.03777021782216379</v>
+        <v>0.03777021782216378</v>
       </c>
       <c r="S54" t="n">
-        <v>0.03605587487352712</v>
+        <v>0.03605587487352713</v>
       </c>
       <c r="T54" t="n">
-        <v>0.03627619837979568</v>
+        <v>0.0362761983797957</v>
       </c>
       <c r="U54" t="n">
-        <v>0.03720019811091785</v>
+        <v>0.03720019811091784</v>
       </c>
       <c r="V54" t="n">
-        <v>0.07322204500963804</v>
+        <v>0.07322204500963803</v>
       </c>
       <c r="W54" t="n">
         <v>0.07057214768454775</v>
@@ -10651,7 +10651,7 @@
         <v>0.1103447653373937</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.109256420011514</v>
+        <v>0.1092564200115141</v>
       </c>
       <c r="AB54" t="n">
         <v>0.1264198169598664</v>
@@ -10666,16 +10666,16 @@
         <v>0.09654706807146193</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.07353994020113495</v>
+        <v>0.07353994020113497</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.09737573171378552</v>
+        <v>0.0973757317137855</v>
       </c>
       <c r="AH54" t="n">
         <v>0.03076713243742725</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.05027060696264869</v>
+        <v>0.05027060696264871</v>
       </c>
       <c r="AJ54" t="n">
         <v>0.04924378088719029</v>
@@ -10684,37 +10684,37 @@
         <v>0.04272843111430607</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.05085816043419401</v>
+        <v>0.05085816043419402</v>
       </c>
       <c r="AM54" t="n">
         <v>0.04604362386664201</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.05730555382432562</v>
+        <v>0.05730555382432563</v>
       </c>
       <c r="AO54" t="n">
         <v>0.05010150926536122</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.04961182374342312</v>
+        <v>0.04961182374342313</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.06772861854584568</v>
+        <v>0.06772861854584572</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.07085209812095616</v>
+        <v>0.07085209812095618</v>
       </c>
       <c r="AS54" t="n">
         <v>0.09910904869469508</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.09955425678155344</v>
+        <v>0.09955425678155341</v>
       </c>
       <c r="AU54" t="n">
         <v>0.08926911643136358</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.09369546929625119</v>
+        <v>0.09369546929625121</v>
       </c>
       <c r="AW54" t="n">
         <v>0.04099871512080958</v>
@@ -10744,7 +10744,7 @@
         <v>0.1189475308681322</v>
       </c>
       <c r="BF54" t="n">
-        <v>0.1204250549594659</v>
+        <v>0.1204250549594658</v>
       </c>
       <c r="BG54" t="n">
         <v>0.1197336566305247</v>
@@ -10759,22 +10759,22 @@
         <v>0.1315240313754536</v>
       </c>
       <c r="BK54" t="n">
-        <v>0.0451899448434914</v>
+        <v>0.04518994484349141</v>
       </c>
       <c r="BL54" t="n">
-        <v>0.06710901670523278</v>
+        <v>0.06710901670523277</v>
       </c>
       <c r="BM54" t="n">
         <v>0.06831464925758098</v>
       </c>
       <c r="BN54" t="n">
-        <v>0.03407159117696101</v>
+        <v>0.03407159117696099</v>
       </c>
       <c r="BO54" t="n">
         <v>0.05660769668922399</v>
       </c>
       <c r="BP54" t="n">
-        <v>0.1229658241254422</v>
+        <v>0.1229658241254421</v>
       </c>
       <c r="BQ54" t="n">
         <v>0.06302358751104499</v>
@@ -10795,16 +10795,16 @@
         <v>0.05000832036309062</v>
       </c>
       <c r="BW54" t="n">
-        <v>0.0528760446472828</v>
+        <v>0.05287604464728281</v>
       </c>
       <c r="BX54" t="n">
         <v>0.05759318504522874</v>
       </c>
       <c r="BY54" t="n">
-        <v>0.0633991187997464</v>
+        <v>0.06339911879974638</v>
       </c>
       <c r="BZ54" t="n">
-        <v>0.06229786134273683</v>
+        <v>0.06229786134273684</v>
       </c>
     </row>
     <row r="55">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.009888210564539172</v>
+        <v>0.009888210564539174</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01081454757929514</v>
+        <v>0.01081454757929513</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01303629366939746</v>
+        <v>0.01303629366939747</v>
       </c>
       <c r="F55" t="n">
         <v>0.01360351201504055</v>
@@ -10832,13 +10832,13 @@
         <v>0.005360424324383288</v>
       </c>
       <c r="H55" t="n">
-        <v>0.004783724941028615</v>
+        <v>0.004783724941028616</v>
       </c>
       <c r="I55" t="n">
-        <v>0.004595890915348866</v>
+        <v>0.004595890915348867</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00706578578802686</v>
+        <v>0.007065785788026859</v>
       </c>
       <c r="K55" t="n">
         <v>0.007457180080699568</v>
@@ -10853,19 +10853,19 @@
         <v>0.005059785854830556</v>
       </c>
       <c r="O55" t="n">
-        <v>0.006253634020039598</v>
+        <v>0.006253634020039597</v>
       </c>
       <c r="P55" t="n">
         <v>0.007090215170729595</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.006232395903747291</v>
+        <v>0.006232395903747292</v>
       </c>
       <c r="R55" t="n">
         <v>0.00616788113007639</v>
       </c>
       <c r="S55" t="n">
-        <v>0.005715615182465754</v>
+        <v>0.005715615182465753</v>
       </c>
       <c r="T55" t="n">
         <v>0.005927267186481355</v>
@@ -10874,10 +10874,10 @@
         <v>0.005842778035022208</v>
       </c>
       <c r="V55" t="n">
-        <v>0.007146787951147838</v>
+        <v>0.007146787951147837</v>
       </c>
       <c r="W55" t="n">
-        <v>0.007059463625383835</v>
+        <v>0.007059463625383834</v>
       </c>
       <c r="X55" t="n">
         <v>0.007067113781883744</v>
@@ -10895,13 +10895,13 @@
         <v>0.008371258037462088</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.008970740126326905</v>
+        <v>0.008970740126326903</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.009602932346261929</v>
+        <v>0.009602932346261925</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.009828621292482194</v>
+        <v>0.009828621292482192</v>
       </c>
       <c r="AF55" t="n">
         <v>0.006887409785626681</v>
@@ -10919,13 +10919,13 @@
         <v>0.007984239077775344</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.007744541766948132</v>
+        <v>0.007744541766948131</v>
       </c>
       <c r="AL55" t="n">
         <v>0.008803280989721005</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.007853631838898808</v>
+        <v>0.00785363183889881</v>
       </c>
       <c r="AN55" t="n">
         <v>0.009294941133990065</v>
@@ -10934,16 +10934,16 @@
         <v>0.008181841985693768</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.008550480714436242</v>
+        <v>0.00855048071443624</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.006809123503029727</v>
+        <v>0.006809123503029726</v>
       </c>
       <c r="AR55" t="n">
-        <v>0.008141255506984219</v>
+        <v>0.00814125550698422</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.007785504755174551</v>
+        <v>0.007785504755174552</v>
       </c>
       <c r="AT55" t="n">
         <v>0.008963274165000711</v>
@@ -10952,7 +10952,7 @@
         <v>0.009271411238595864</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.009916605387099427</v>
+        <v>0.009916605387099429</v>
       </c>
       <c r="AW55" t="n">
         <v>0.01956425432332298</v>
@@ -10970,7 +10970,7 @@
         <v>0.01941219761128539</v>
       </c>
       <c r="BB55" t="n">
-        <v>0.02210354675805213</v>
+        <v>0.02210354675805214</v>
       </c>
       <c r="BC55" t="n">
         <v>0.02018148766768143</v>
@@ -11000,7 +11000,7 @@
         <v>0.01494671302825335</v>
       </c>
       <c r="BL55" t="n">
-        <v>0.008904227662864698</v>
+        <v>0.008904227662864696</v>
       </c>
       <c r="BM55" t="n">
         <v>0.012015721235052</v>
@@ -11012,13 +11012,13 @@
         <v>0.015401437783094</v>
       </c>
       <c r="BP55" t="n">
-        <v>0.0188761799559792</v>
+        <v>0.01887617995597921</v>
       </c>
       <c r="BQ55" t="n">
         <v>0.01563435555220082</v>
       </c>
       <c r="BR55" t="n">
-        <v>0.02509471645712165</v>
+        <v>0.02509471645712164</v>
       </c>
       <c r="BS55" t="n">
         <v>0.02627942382317437</v>
@@ -11058,28 +11058,28 @@
         <v>0.02445946242487982</v>
       </c>
       <c r="D56" t="n">
-        <v>0.04591343296125254</v>
+        <v>0.04591343296125255</v>
       </c>
       <c r="E56" t="n">
-        <v>0.06835196440235</v>
+        <v>0.06835196440235006</v>
       </c>
       <c r="F56" t="n">
-        <v>0.016307590955216</v>
+        <v>0.01630759095521601</v>
       </c>
       <c r="G56" t="n">
         <v>0.03066455957333849</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02716422965099678</v>
+        <v>0.02716422965099677</v>
       </c>
       <c r="I56" t="n">
         <v>0.02838142976457154</v>
       </c>
       <c r="J56" t="n">
-        <v>0.04322255549696288</v>
+        <v>0.04322255549696287</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04312714406293539</v>
+        <v>0.0431271440629354</v>
       </c>
       <c r="L56" t="n">
         <v>0.04275304951864205</v>
@@ -11094,19 +11094,19 @@
         <v>0.03090427932153013</v>
       </c>
       <c r="P56" t="n">
-        <v>0.04813034937772578</v>
+        <v>0.0481303493777258</v>
       </c>
       <c r="Q56" t="n">
         <v>0.04071491673379893</v>
       </c>
       <c r="R56" t="n">
-        <v>0.04364996720761422</v>
+        <v>0.04364996720761423</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04870327175299429</v>
+        <v>0.04870327175299428</v>
       </c>
       <c r="T56" t="n">
-        <v>0.04655934913633558</v>
+        <v>0.04655934913633557</v>
       </c>
       <c r="U56" t="n">
         <v>0.04999325036413325</v>
@@ -11115,7 +11115,7 @@
         <v>0.06448379347575399</v>
       </c>
       <c r="W56" t="n">
-        <v>0.06158527827109766</v>
+        <v>0.06158527827109765</v>
       </c>
       <c r="X56" t="n">
         <v>0.05537270755326205</v>
@@ -11127,7 +11127,7 @@
         <v>0.06582734282117071</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.07167697759378795</v>
+        <v>0.07167697759378799</v>
       </c>
       <c r="AB56" t="n">
         <v>0.06501752004711467</v>
@@ -11142,7 +11142,7 @@
         <v>0.07587328173838839</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.03946071040200335</v>
+        <v>0.03946071040200334</v>
       </c>
       <c r="AG56" t="n">
         <v>0.04711417263990938</v>
@@ -11154,19 +11154,19 @@
         <v>0.05960629010330606</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.05993861671442254</v>
+        <v>0.05993861671442256</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.06178990670852414</v>
+        <v>0.06178990670852413</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.07695179329973226</v>
+        <v>0.07695179329973223</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.06702473603587307</v>
+        <v>0.06702473603587308</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.06778832530265991</v>
+        <v>0.06778832530265994</v>
       </c>
       <c r="AO56" t="n">
         <v>0.06424328918390118</v>
@@ -11178,16 +11178,16 @@
         <v>0.05200978641053879</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.06300433602865832</v>
+        <v>0.06300433602865831</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.04486678471419335</v>
+        <v>0.04486678471419334</v>
       </c>
       <c r="AT56" t="n">
         <v>0.06431954771474285</v>
       </c>
       <c r="AU56" t="n">
-        <v>0.07135948344390254</v>
+        <v>0.07135948344390257</v>
       </c>
       <c r="AV56" t="n">
         <v>0.06365730817176012</v>
@@ -11196,7 +11196,7 @@
         <v>0.01862126995701937</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.01756192938709862</v>
+        <v>0.01756192938709863</v>
       </c>
       <c r="AY56" t="n">
         <v>0.01694594673049786</v>
@@ -11205,7 +11205,7 @@
         <v>0.005985132258225338</v>
       </c>
       <c r="BA56" t="n">
-        <v>0.003903863431020501</v>
+        <v>0.003903863431020502</v>
       </c>
       <c r="BB56" t="n">
         <v>0.008568820750290666</v>
@@ -11214,7 +11214,7 @@
         <v>0.003378906085344885</v>
       </c>
       <c r="BD56" t="n">
-        <v>0.005165016903268298</v>
+        <v>0.005165016903268299</v>
       </c>
       <c r="BE56" t="n">
         <v>0.00319563864441662</v>
@@ -11223,25 +11223,25 @@
         <v>0.005748131008486537</v>
       </c>
       <c r="BG56" t="n">
-        <v>0.005516747101004369</v>
+        <v>0.00551674710100437</v>
       </c>
       <c r="BH56" t="n">
-        <v>0.007156683085491686</v>
+        <v>0.007156683085491687</v>
       </c>
       <c r="BI56" t="n">
-        <v>0.005459503637301602</v>
+        <v>0.005459503637301601</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.00766601461850256</v>
+        <v>0.007666014618502558</v>
       </c>
       <c r="BK56" t="n">
         <v>0.003496545827132832</v>
       </c>
       <c r="BL56" t="n">
-        <v>0.003781662807793284</v>
+        <v>0.003781662807793282</v>
       </c>
       <c r="BM56" t="n">
-        <v>0.005640112044796</v>
+        <v>0.005640112044796002</v>
       </c>
       <c r="BN56" t="n">
         <v>0.010211438888226</v>
@@ -11250,10 +11250,10 @@
         <v>0.01195859948303</v>
       </c>
       <c r="BP56" t="n">
-        <v>0.006929935827152901</v>
+        <v>0.006929935827152902</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0.005079851383037975</v>
+        <v>0.005079851383037976</v>
       </c>
       <c r="BR56" t="n">
         <v>0.01005309630287698</v>
@@ -11262,7 +11262,7 @@
         <v>0.01284990036110044</v>
       </c>
       <c r="BT56" t="n">
-        <v>0.01822980336708246</v>
+        <v>0.01822980336708245</v>
       </c>
       <c r="BU56" t="n">
         <v>0.02102460113097052</v>
@@ -11274,7 +11274,7 @@
         <v>0.019070155061954</v>
       </c>
       <c r="BX56" t="n">
-        <v>0.02095497457295136</v>
+        <v>0.02095497457295137</v>
       </c>
       <c r="BY56" t="n">
         <v>0.01886996370724664</v>
@@ -11714,16 +11714,16 @@
         <v>0.05295435564391827</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0505905788552138</v>
+        <v>0.05059057885521379</v>
       </c>
       <c r="E60" t="n">
-        <v>0.04128636135723638</v>
+        <v>0.04128636135723639</v>
       </c>
       <c r="F60" t="n">
         <v>0.04948523388856117</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01923450235223113</v>
+        <v>0.01923450235223112</v>
       </c>
       <c r="H60" t="n">
         <v>0.01653647501397063</v>
@@ -11756,7 +11756,7 @@
         <v>0.02814563363255421</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02804108539696285</v>
+        <v>0.02804108539696286</v>
       </c>
       <c r="S60" t="n">
         <v>0.02868018458426515</v>
@@ -11774,7 +11774,7 @@
         <v>0.03451643422008279</v>
       </c>
       <c r="X60" t="n">
-        <v>0.03692718769015446</v>
+        <v>0.03692718769015445</v>
       </c>
       <c r="Y60" t="n">
         <v>0.0416164647357115</v>
@@ -11783,10 +11783,10 @@
         <v>0.04242034841473503</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.04434394821778874</v>
+        <v>0.04434394821778875</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.02164211481213934</v>
+        <v>0.02164211481213933</v>
       </c>
       <c r="AC60" t="n">
         <v>0.02894114796002764</v>
@@ -11876,13 +11876,13 @@
         <v>0.01303254598234851</v>
       </c>
       <c r="BF60" t="n">
-        <v>0.009790355083658307</v>
+        <v>0.009790355083658305</v>
       </c>
       <c r="BG60" t="n">
         <v>0.009721797314128932</v>
       </c>
       <c r="BH60" t="n">
-        <v>0.009690445117482311</v>
+        <v>0.009690445117482313</v>
       </c>
       <c r="BI60" t="n">
         <v>0.009793674799354028</v>
@@ -11891,7 +11891,7 @@
         <v>0.107500576814692</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.1526371184323834</v>
+        <v>0.1526371184323835</v>
       </c>
       <c r="BL60" t="n">
         <v>0.02076117777001004</v>
@@ -11909,7 +11909,7 @@
         <v>0.02559098342961993</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0.01339224923373295</v>
+        <v>0.01339224923373296</v>
       </c>
       <c r="BR60" t="n">
         <v>0.02038598425293594</v>
@@ -11924,7 +11924,7 @@
         <v>0.03167046687841677</v>
       </c>
       <c r="BV60" t="n">
-        <v>0.02064190854061581</v>
+        <v>0.0206419085406158</v>
       </c>
       <c r="BW60" t="n">
         <v>0.02133175198706542</v>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.00847182349795921</v>
+        <v>0.008471823497959208</v>
       </c>
       <c r="D63" t="n">
         <v>0.01279448374917614</v>
@@ -12296,7 +12296,7 @@
         <v>0.00687817216704303</v>
       </c>
       <c r="L63" t="n">
-        <v>0.005777465565244611</v>
+        <v>0.005777465565244612</v>
       </c>
       <c r="M63" t="n">
         <v>0.01059716192462796</v>
@@ -12311,16 +12311,16 @@
         <v>0.01482050348809692</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.01427792720100105</v>
+        <v>0.01427792720100104</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0134791459156779</v>
+        <v>0.01347914591567789</v>
       </c>
       <c r="S63" t="n">
         <v>0.0116560017532111</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01255993121653118</v>
+        <v>0.01255993121653117</v>
       </c>
       <c r="U63" t="n">
         <v>0.0150012582058068</v>
@@ -12341,7 +12341,7 @@
         <v>0.01540401926148166</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01243700555081249</v>
+        <v>0.0124370055508125</v>
       </c>
       <c r="AB63" t="n">
         <v>0.008627813080616591</v>
@@ -12374,13 +12374,13 @@
         <v>0.03534642402757376</v>
       </c>
       <c r="AL63" t="n">
-        <v>0.04946203211417961</v>
+        <v>0.0494620321141796</v>
       </c>
       <c r="AM63" t="n">
         <v>0.03931935007139734</v>
       </c>
       <c r="AN63" t="n">
-        <v>0.02511262690813034</v>
+        <v>0.02511262690813035</v>
       </c>
       <c r="AO63" t="n">
         <v>0.02076384457930367</v>
@@ -12410,25 +12410,25 @@
         <v>0.003596173743162529</v>
       </c>
       <c r="AX63" t="n">
-        <v>0.007850846041321852</v>
+        <v>0.007850846041321854</v>
       </c>
       <c r="AY63" t="n">
-        <v>0.005774768069212782</v>
+        <v>0.005774768069212781</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0.009788718710840191</v>
+        <v>0.009788718710840192</v>
       </c>
       <c r="BA63" t="n">
         <v>0.006904869628408825</v>
       </c>
       <c r="BB63" t="n">
-        <v>0.008081167614974702</v>
+        <v>0.008081167614974703</v>
       </c>
       <c r="BC63" t="n">
         <v>0.01030101705854174</v>
       </c>
       <c r="BD63" t="n">
-        <v>0.01869805173261529</v>
+        <v>0.0186980517326153</v>
       </c>
       <c r="BE63" t="n">
         <v>0.008222561582154501</v>
@@ -12470,7 +12470,7 @@
         <v>0.003824188556281412</v>
       </c>
       <c r="BR63" t="n">
-        <v>0.003546064010778688</v>
+        <v>0.003546064010778687</v>
       </c>
       <c r="BS63" t="n">
         <v>0.004118114398045986</v>
@@ -12488,7 +12488,7 @@
         <v>0.005371868292407976</v>
       </c>
       <c r="BX63" t="n">
-        <v>0.005684500182179035</v>
+        <v>0.005684500182179034</v>
       </c>
       <c r="BY63" t="n">
         <v>0.005992729534612658</v>
@@ -12726,19 +12726,19 @@
         <v>0.05170137830001791</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0500265760835912</v>
+        <v>0.05002657608359121</v>
       </c>
       <c r="I65" t="n">
         <v>0.04990936999895047</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0742086099293006</v>
+        <v>0.07420860992930059</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0785251274032603</v>
+        <v>0.07852512740326031</v>
       </c>
       <c r="L65" t="n">
-        <v>0.05596662903353462</v>
+        <v>0.05596662903353461</v>
       </c>
       <c r="M65" t="n">
         <v>0.02312274243601316</v>
@@ -12747,16 +12747,16 @@
         <v>0.02518858886305193</v>
       </c>
       <c r="O65" t="n">
-        <v>0.04025547236087761</v>
+        <v>0.04025547236087762</v>
       </c>
       <c r="P65" t="n">
         <v>0.03562594910190359</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.03073932767000941</v>
+        <v>0.03073932767000942</v>
       </c>
       <c r="R65" t="n">
-        <v>0.03233268407880429</v>
+        <v>0.0323326840788043</v>
       </c>
       <c r="S65" t="n">
         <v>0.03501913442555094</v>
@@ -12768,7 +12768,7 @@
         <v>0.03465525390804637</v>
       </c>
       <c r="V65" t="n">
-        <v>0.04695978357327492</v>
+        <v>0.04695978357327493</v>
       </c>
       <c r="W65" t="n">
         <v>0.04931579554091598</v>
@@ -12777,13 +12777,13 @@
         <v>0.04016349843668832</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.04845842479377027</v>
+        <v>0.04845842479377025</v>
       </c>
       <c r="Z65" t="n">
         <v>0.04388482647001481</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.04973407397122198</v>
+        <v>0.04973407397122197</v>
       </c>
       <c r="AB65" t="n">
         <v>0.1066117691065927</v>
@@ -12798,52 +12798,52 @@
         <v>0.1106305146656332</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.06594780172995288</v>
+        <v>0.06594780172995286</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.08251444336763203</v>
+        <v>0.08251444336763204</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.03903489208867673</v>
+        <v>0.03903489208867671</v>
       </c>
       <c r="AI65" t="n">
         <v>0.06175891131979479</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.05966806074272553</v>
+        <v>0.05966806074272552</v>
       </c>
       <c r="AK65" t="n">
-        <v>0.1241130671690336</v>
+        <v>0.1241130671690335</v>
       </c>
       <c r="AL65" t="n">
         <v>0.153624459893109</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.1322872232286914</v>
+        <v>0.1322872232286913</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.06082991081536737</v>
+        <v>0.06082991081536736</v>
       </c>
       <c r="AO65" t="n">
         <v>0.06711952285420555</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.0673370798312484</v>
+        <v>0.06733707983124841</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.07145627826288553</v>
+        <v>0.07145627826288556</v>
       </c>
       <c r="AR65" t="n">
-        <v>0.0913772904595575</v>
+        <v>0.09137729045955752</v>
       </c>
       <c r="AS65" t="n">
         <v>0.07495977913004929</v>
       </c>
       <c r="AT65" t="n">
-        <v>0.08075052665216724</v>
+        <v>0.08075052665216723</v>
       </c>
       <c r="AU65" t="n">
-        <v>0.07004748168599895</v>
+        <v>0.07004748168599893</v>
       </c>
       <c r="AV65" t="n">
         <v>0.06786668755119993</v>
@@ -12855,13 +12855,13 @@
         <v>0.05364441851859308</v>
       </c>
       <c r="AY65" t="n">
-        <v>0.04274701536159632</v>
+        <v>0.04274701536159631</v>
       </c>
       <c r="AZ65" t="n">
         <v>0.03994112861089982</v>
       </c>
       <c r="BA65" t="n">
-        <v>0.02792089367666457</v>
+        <v>0.02792089367666458</v>
       </c>
       <c r="BB65" t="n">
         <v>0.3892210605409299</v>
@@ -12870,10 +12870,10 @@
         <v>0.1213164698155713</v>
       </c>
       <c r="BD65" t="n">
-        <v>0.3526135908495049</v>
+        <v>0.3526135908495048</v>
       </c>
       <c r="BE65" t="n">
-        <v>0.08739938262206935</v>
+        <v>0.08739938262206938</v>
       </c>
       <c r="BF65" t="n">
         <v>0.1505873897706384</v>
@@ -12924,7 +12924,7 @@
         <v>0.2219146318644275</v>
       </c>
       <c r="BV65" t="n">
-        <v>0.1717551066299053</v>
+        <v>0.1717551066299052</v>
       </c>
       <c r="BW65" t="n">
         <v>0.1984956193045475</v>
@@ -12936,7 +12936,7 @@
         <v>0.138051472644998</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0.106376178314193</v>
+        <v>0.1063761783141931</v>
       </c>
     </row>
     <row r="66">
@@ -12964,7 +12964,7 @@
         <v>0.0001497502630347382</v>
       </c>
       <c r="H66" t="n">
-        <v>0.000137921063697281</v>
+        <v>0.0001379210636972809</v>
       </c>
       <c r="I66" t="n">
         <v>0.0001368493673421773</v>
@@ -12991,7 +12991,7 @@
         <v>0.0001439040424989819</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0001194635817396877</v>
+        <v>0.0001194635817396876</v>
       </c>
       <c r="R66" t="n">
         <v>0.0001315781595697579</v>
@@ -13000,7 +13000,7 @@
         <v>0.0001394420523405749</v>
       </c>
       <c r="T66" t="n">
-        <v>0.0001423035231080982</v>
+        <v>0.0001423035231080983</v>
       </c>
       <c r="U66" t="n">
         <v>0.0001416172411664461</v>
@@ -13063,7 +13063,7 @@
         <v>0.0002079235868888749</v>
       </c>
       <c r="AO66" t="n">
-        <v>0.0001940967634446398</v>
+        <v>0.0001940967634446399</v>
       </c>
       <c r="AP66" t="n">
         <v>0.0001890222643758548</v>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.009087140824320388</v>
+        <v>0.009087140824320387</v>
       </c>
       <c r="D72" t="n">
         <v>0.01251859297698672</v>
@@ -13971,10 +13971,10 @@
         <v>0.007998068903398341</v>
       </c>
       <c r="S72" t="n">
-        <v>0.009020747959087949</v>
+        <v>0.009020747959087951</v>
       </c>
       <c r="T72" t="n">
-        <v>0.008185358891388172</v>
+        <v>0.00818535889138817</v>
       </c>
       <c r="U72" t="n">
         <v>0.008100995639964598</v>
@@ -14028,7 +14028,7 @@
         <v>0.02403779680191368</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.02779060253046351</v>
+        <v>0.0277906025304635</v>
       </c>
       <c r="AM72" t="n">
         <v>0.02607193441660341</v>
@@ -14061,7 +14061,7 @@
         <v>0.01154640810743717</v>
       </c>
       <c r="AW72" t="n">
-        <v>0.01393129334400879</v>
+        <v>0.0139312933440088</v>
       </c>
       <c r="AX72" t="n">
         <v>0.01385268072923274</v>
@@ -14073,7 +14073,7 @@
         <v>0.01605139573786731</v>
       </c>
       <c r="BA72" t="n">
-        <v>0.02060081535049806</v>
+        <v>0.02060081535049807</v>
       </c>
       <c r="BB72" t="n">
         <v>0.01981137820924392</v>
@@ -14127,7 +14127,7 @@
         <v>0.01081473952606629</v>
       </c>
       <c r="BS72" t="n">
-        <v>0.01295645183598425</v>
+        <v>0.01295645183598424</v>
       </c>
       <c r="BT72" t="n">
         <v>0.01708767160943205</v>
@@ -14145,7 +14145,7 @@
         <v>0.02594927708998996</v>
       </c>
       <c r="BY72" t="n">
-        <v>0.02572220665589332</v>
+        <v>0.02572220665589333</v>
       </c>
       <c r="BZ72" t="n">
         <v>0.0206711430843869</v>
@@ -14161,7 +14161,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.006726408931911985</v>
+        <v>0.006726408931911986</v>
       </c>
       <c r="D73" t="n">
         <v>0.02168898557128442</v>
@@ -14173,7 +14173,7 @@
         <v>0.005574780283567483</v>
       </c>
       <c r="G73" t="n">
-        <v>0.003130974368622815</v>
+        <v>0.003130974368622814</v>
       </c>
       <c r="H73" t="n">
         <v>0.002884599558547111</v>
@@ -14185,7 +14185,7 @@
         <v>0.004112125887204915</v>
       </c>
       <c r="K73" t="n">
-        <v>0.004436769686470717</v>
+        <v>0.004436769686470716</v>
       </c>
       <c r="L73" t="n">
         <v>0.003933734314543328</v>
@@ -14206,13 +14206,13 @@
         <v>0.003190262298275581</v>
       </c>
       <c r="R73" t="n">
-        <v>0.003487882619623859</v>
+        <v>0.003487882619623858</v>
       </c>
       <c r="S73" t="n">
         <v>0.003814572635987122</v>
       </c>
       <c r="T73" t="n">
-        <v>0.003637591449838444</v>
+        <v>0.003637591449838445</v>
       </c>
       <c r="U73" t="n">
         <v>0.003543925001413677</v>
@@ -14221,34 +14221,34 @@
         <v>0.004398516705795909</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004842748263257204</v>
+        <v>0.004842748263257203</v>
       </c>
       <c r="X73" t="n">
-        <v>0.004182417334687124</v>
+        <v>0.004182417334687125</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.004735464506906969</v>
+        <v>0.004735464506906968</v>
       </c>
       <c r="Z73" t="n">
         <v>0.004659984354778196</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.005026008015953476</v>
+        <v>0.005026008015953477</v>
       </c>
       <c r="AB73" t="n">
         <v>0.00453989320688843</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.005589516477118626</v>
+        <v>0.005589516477118627</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.005917127652830012</v>
+        <v>0.00591712765283001</v>
       </c>
       <c r="AE73" t="n">
-        <v>0.005447988662127372</v>
+        <v>0.005447988662127371</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.003725939440519873</v>
+        <v>0.003725939440519874</v>
       </c>
       <c r="AG73" t="n">
         <v>0.004649041378502995</v>
@@ -14257,10 +14257,10 @@
         <v>0.003241735656690619</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.004926482326962801</v>
+        <v>0.0049264823269628</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.004711852708239145</v>
+        <v>0.004711852708239144</v>
       </c>
       <c r="AK73" t="n">
         <v>0.007710510293148668</v>
@@ -14275,7 +14275,7 @@
         <v>0.005300399640794567</v>
       </c>
       <c r="AO73" t="n">
-        <v>0.005038167973111076</v>
+        <v>0.005038167973111077</v>
       </c>
       <c r="AP73" t="n">
         <v>0.004911782552587758</v>
@@ -14284,7 +14284,7 @@
         <v>0.003915730459478279</v>
       </c>
       <c r="AR73" t="n">
-        <v>0.004334815392134625</v>
+        <v>0.004334815392134624</v>
       </c>
       <c r="AS73" t="n">
         <v>0.004437924693919979</v>
@@ -14293,34 +14293,34 @@
         <v>0.006918140027478262</v>
       </c>
       <c r="AU73" t="n">
-        <v>0.00578993179976262</v>
+        <v>0.005789931799762619</v>
       </c>
       <c r="AV73" t="n">
-        <v>0.005912715387038571</v>
+        <v>0.005912715387038572</v>
       </c>
       <c r="AW73" t="n">
-        <v>0.04110804625843159</v>
+        <v>0.0411080462584316</v>
       </c>
       <c r="AX73" t="n">
-        <v>0.01010978224707708</v>
+        <v>0.01010978224707707</v>
       </c>
       <c r="AY73" t="n">
-        <v>0.01083357025525581</v>
+        <v>0.01083357025525582</v>
       </c>
       <c r="AZ73" t="n">
         <v>0.009426811235790715</v>
       </c>
       <c r="BA73" t="n">
-        <v>0.007769814387027879</v>
+        <v>0.00776981438702788</v>
       </c>
       <c r="BB73" t="n">
         <v>0.04524092453212106</v>
       </c>
       <c r="BC73" t="n">
-        <v>0.01754701888810764</v>
+        <v>0.01754701888810763</v>
       </c>
       <c r="BD73" t="n">
-        <v>0.03423101067165921</v>
+        <v>0.0342310106716592</v>
       </c>
       <c r="BE73" t="n">
         <v>0.01381311311501278</v>
@@ -14347,7 +14347,7 @@
         <v>0.007086846769314759</v>
       </c>
       <c r="BM73" t="n">
-        <v>0.007237700125478002</v>
+        <v>0.007237700125477999</v>
       </c>
       <c r="BN73" t="n">
         <v>0.008064647964001002</v>
@@ -14356,7 +14356,7 @@
         <v>0.027265087964853</v>
       </c>
       <c r="BP73" t="n">
-        <v>0.009652927419561374</v>
+        <v>0.009652927419561376</v>
       </c>
       <c r="BQ73" t="n">
         <v>0.007051608124001514</v>
@@ -14371,7 +14371,7 @@
         <v>0.02558191589347302</v>
       </c>
       <c r="BU73" t="n">
-        <v>0.02560942478958377</v>
+        <v>0.02560942478958378</v>
       </c>
       <c r="BV73" t="n">
         <v>0.01806211564476744</v>
@@ -14380,13 +14380,13 @@
         <v>0.01888536067481358</v>
       </c>
       <c r="BX73" t="n">
-        <v>0.01774628041512736</v>
+        <v>0.01774628041512737</v>
       </c>
       <c r="BY73" t="n">
-        <v>0.01240511807817384</v>
+        <v>0.01240511807817385</v>
       </c>
       <c r="BZ73" t="n">
-        <v>0.008913970373522939</v>
+        <v>0.00891397037352294</v>
       </c>
     </row>
     <row r="74">
@@ -14402,7 +14402,7 @@
         <v>0.001638667436450315</v>
       </c>
       <c r="D74" t="n">
-        <v>0.001628196745240048</v>
+        <v>0.001628196745240049</v>
       </c>
       <c r="E74" t="n">
         <v>0.001669187595527564</v>
@@ -14420,10 +14420,10 @@
         <v>0.0004835046554068998</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0007039730071337122</v>
+        <v>0.000703973007133712</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0008200322851981795</v>
+        <v>0.0008200322851981796</v>
       </c>
       <c r="L74" t="n">
         <v>0.0006542850564166986</v>
@@ -14435,10 +14435,10 @@
         <v>0.0004027164593101192</v>
       </c>
       <c r="O74" t="n">
-        <v>0.0008367645752545659</v>
+        <v>0.0008367645752545658</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0005822460772529573</v>
+        <v>0.0005822460772529572</v>
       </c>
       <c r="Q74" t="n">
         <v>0.0005307218407344319</v>
@@ -14447,10 +14447,10 @@
         <v>0.000496585698563225</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0005977835543318605</v>
+        <v>0.0005977835543318604</v>
       </c>
       <c r="T74" t="n">
-        <v>0.0006124011644704761</v>
+        <v>0.000612401164470476</v>
       </c>
       <c r="U74" t="n">
         <v>0.0006019414112822108</v>
@@ -14480,13 +14480,13 @@
         <v>0.001021307046669089</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.0008101764254734586</v>
+        <v>0.0008101764254734585</v>
       </c>
       <c r="AE74" t="n">
         <v>0.0007863539089071306</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.0006157563631969763</v>
+        <v>0.0006157563631969764</v>
       </c>
       <c r="AG74" t="n">
         <v>0.0007987521360091311</v>
@@ -14525,7 +14525,7 @@
         <v>0.0008454179196919258</v>
       </c>
       <c r="AS74" t="n">
-        <v>0.0007392168640989928</v>
+        <v>0.0007392168640989927</v>
       </c>
       <c r="AT74" t="n">
         <v>0.000927410723802845</v>
@@ -14594,10 +14594,10 @@
         <v>0.001846835283717</v>
       </c>
       <c r="BP74" t="n">
-        <v>0.0009887348119050462</v>
+        <v>0.0009887348119050465</v>
       </c>
       <c r="BQ74" t="n">
-        <v>0.0007984019621490948</v>
+        <v>0.0007984019621490949</v>
       </c>
       <c r="BR74" t="n">
         <v>0.000939912291709281</v>
@@ -15652,7 +15652,7 @@
         <v>0.01246047831770819</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01278405808400005</v>
+        <v>0.01278405808400004</v>
       </c>
       <c r="E83" t="n">
         <v>0.01039145190352012</v>
@@ -15673,16 +15673,16 @@
         <v>0.006351169448250528</v>
       </c>
       <c r="K83" t="n">
-        <v>0.007497014255141361</v>
+        <v>0.007497014255141362</v>
       </c>
       <c r="L83" t="n">
         <v>0.005840060941921106</v>
       </c>
       <c r="M83" t="n">
-        <v>0.006419813085077874</v>
+        <v>0.006419813085077873</v>
       </c>
       <c r="N83" t="n">
-        <v>0.006573794550004696</v>
+        <v>0.006573794550004697</v>
       </c>
       <c r="O83" t="n">
         <v>0.01064755210838122</v>
@@ -15718,10 +15718,10 @@
         <v>0.02070697275171125</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.02172872596939382</v>
+        <v>0.02172872596939381</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.0219485641186998</v>
+        <v>0.02194856411869979</v>
       </c>
       <c r="AB83" t="n">
         <v>0.008259055426881951</v>
@@ -15766,16 +15766,16 @@
         <v>0.01247806818776306</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.01251152322129318</v>
+        <v>0.01251152322129319</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.00703515792332549</v>
+        <v>0.007035157923325489</v>
       </c>
       <c r="AR83" t="n">
         <v>0.008807155916194081</v>
       </c>
       <c r="AS83" t="n">
-        <v>0.008365292898607614</v>
+        <v>0.008365292898607615</v>
       </c>
       <c r="AT83" t="n">
         <v>0.01846986441217739</v>
@@ -15787,7 +15787,7 @@
         <v>0.01556378083082924</v>
       </c>
       <c r="AW83" t="n">
-        <v>0.02041248576895353</v>
+        <v>0.02041248576895352</v>
       </c>
       <c r="AX83" t="n">
         <v>0.01827268886738232</v>
@@ -15802,7 +15802,7 @@
         <v>0.02911178608281101</v>
       </c>
       <c r="BB83" t="n">
-        <v>0.02636130266338144</v>
+        <v>0.02636130266338145</v>
       </c>
       <c r="BC83" t="n">
         <v>0.03184392680583885</v>
@@ -15829,7 +15829,7 @@
         <v>0.03970677054408001</v>
       </c>
       <c r="BK83" t="n">
-        <v>0.037573284700656</v>
+        <v>0.03757328470065599</v>
       </c>
       <c r="BL83" t="n">
         <v>0.01973157175705334</v>
@@ -15856,7 +15856,7 @@
         <v>0.01190402860628673</v>
       </c>
       <c r="BT83" t="n">
-        <v>0.01480979291233127</v>
+        <v>0.01480979291233126</v>
       </c>
       <c r="BU83" t="n">
         <v>0.01698023950743058</v>
@@ -15868,7 +15868,7 @@
         <v>0.01517680994821645</v>
       </c>
       <c r="BX83" t="n">
-        <v>0.01513343634495114</v>
+        <v>0.01513343634495115</v>
       </c>
       <c r="BY83" t="n">
         <v>0.01763719949151174</v>
@@ -15917,7 +15917,7 @@
         <v>0.00111252356176057</v>
       </c>
       <c r="M84" t="n">
-        <v>0.0009625613420407898</v>
+        <v>0.0009625613420407899</v>
       </c>
       <c r="N84" t="n">
         <v>0.001037956490142471</v>
@@ -15926,7 +15926,7 @@
         <v>0.001751676018663767</v>
       </c>
       <c r="P84" t="n">
-        <v>0.001816263337554271</v>
+        <v>0.00181626333755427</v>
       </c>
       <c r="Q84" t="n">
         <v>0.001644133657204061</v>
@@ -15944,7 +15944,7 @@
         <v>0.001755647550541468</v>
       </c>
       <c r="V84" t="n">
-        <v>0.003441593297105726</v>
+        <v>0.003441593297105725</v>
       </c>
       <c r="W84" t="n">
         <v>0.003357715017941895</v>
@@ -15965,7 +15965,7 @@
         <v>0.001749365833137703</v>
       </c>
       <c r="AC84" t="n">
-        <v>0.0030718923388279</v>
+        <v>0.003071892338827899</v>
       </c>
       <c r="AD84" t="n">
         <v>0.002109449845917563</v>
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.0006686976573730833</v>
+        <v>0.0006686976573730832</v>
       </c>
       <c r="D85" t="n">
         <v>0.0005580474794684376</v>
@@ -16301,7 +16301,7 @@
         <v>0.0003197319490266715</v>
       </c>
       <c r="BM85" t="n">
-        <v>0.0006312994315490001</v>
+        <v>0.000631299431549</v>
       </c>
       <c r="BN85" t="n">
         <v>7.6440917749e-05</v>
@@ -16310,7 +16310,7 @@
         <v>9.525957199200001e-05</v>
       </c>
       <c r="BP85" t="n">
-        <v>0.006771349338762581</v>
+        <v>0.00677134933876258</v>
       </c>
       <c r="BQ85" t="n">
         <v>0.001595441840280756</v>
@@ -16790,7 +16790,7 @@
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr"/>
       <c r="BJ89" t="n">
-        <v>0.0003483255657215999</v>
+        <v>0.0003483255657216</v>
       </c>
       <c r="BK89" t="n">
         <v>0.0002992152641098593</v>
@@ -16811,7 +16811,7 @@
         <v>0.0005200341206308082</v>
       </c>
       <c r="BQ89" t="n">
-        <v>0.0005599697942634885</v>
+        <v>0.0005599697942634884</v>
       </c>
       <c r="BR89" t="inlineStr"/>
       <c r="BS89" t="inlineStr"/>
@@ -16958,7 +16958,7 @@
         <v>6.382910320543652e-06</v>
       </c>
       <c r="P91" t="n">
-        <v>1.437150341308172e-05</v>
+        <v>1.437150341308173e-05</v>
       </c>
       <c r="Q91" t="n">
         <v>1.381386819745647e-05</v>
@@ -16979,7 +16979,7 @@
         <v>2.026718208789618e-05</v>
       </c>
       <c r="W91" t="n">
-        <v>2.043599918346715e-05</v>
+        <v>2.043599918346714e-05</v>
       </c>
       <c r="X91" t="n">
         <v>1.832758719535169e-05</v>
@@ -16988,7 +16988,7 @@
         <v>1.863018456856592e-05</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.855085340991577e-05</v>
+        <v>1.855085340991576e-05</v>
       </c>
       <c r="AA91" t="n">
         <v>2.404474790188187e-05</v>
@@ -16997,7 +16997,7 @@
         <v>5.25827153659509e-05</v>
       </c>
       <c r="AC91" t="n">
-        <v>4.697155782144579e-05</v>
+        <v>4.697155782144578e-05</v>
       </c>
       <c r="AD91" t="n">
         <v>5.581370789672539e-05</v>
@@ -17012,7 +17012,7 @@
         <v>2.05700301923901e-05</v>
       </c>
       <c r="AH91" t="n">
-        <v>7.621747417207826e-06</v>
+        <v>7.621747417207827e-06</v>
       </c>
       <c r="AI91" t="n">
         <v>1.616821837388e-05</v>
@@ -17042,7 +17042,7 @@
         <v>2.026280546864582e-05</v>
       </c>
       <c r="AR91" t="n">
-        <v>3.203559140708191e-05</v>
+        <v>3.20355914070819e-05</v>
       </c>
       <c r="AS91" t="n">
         <v>1.920829838334368e-05</v>
@@ -17711,7 +17711,7 @@
         <v>0.0006637057486405051</v>
       </c>
       <c r="G95" t="n">
-        <v>0.001705572837345035</v>
+        <v>0.001705572837345036</v>
       </c>
       <c r="H95" t="n">
         <v>0.001562768513562334</v>
@@ -17723,7 +17723,7 @@
         <v>0.002487645336073106</v>
       </c>
       <c r="K95" t="n">
-        <v>0.002640772987003888</v>
+        <v>0.002640772987003889</v>
       </c>
       <c r="L95" t="n">
         <v>0.002387749035094052</v>
@@ -17735,13 +17735,13 @@
         <v>0.001369118389338051</v>
       </c>
       <c r="O95" t="n">
-        <v>0.001728182760219121</v>
+        <v>0.001728182760219122</v>
       </c>
       <c r="P95" t="n">
-        <v>0.001750321908049883</v>
+        <v>0.001750321908049882</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.001510425323537354</v>
+        <v>0.001510425323537353</v>
       </c>
       <c r="R95" t="n">
         <v>0.001595313886552818</v>
@@ -17774,7 +17774,7 @@
         <v>0.001533843278866227</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.003661790321967184</v>
+        <v>0.003661790321967183</v>
       </c>
       <c r="AC95" t="n">
         <v>0.004542699036152238</v>
@@ -17798,7 +17798,7 @@
         <v>0.002753438672215532</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.002781015161703459</v>
+        <v>0.00278101516170346</v>
       </c>
       <c r="AK95" t="n">
         <v>0.004322945041903562</v>
@@ -17807,7 +17807,7 @@
         <v>0.004872922600514682</v>
       </c>
       <c r="AM95" t="n">
-        <v>0.004743700956020295</v>
+        <v>0.004743700956020294</v>
       </c>
       <c r="AN95" t="n">
         <v>0.003127387040266444</v>
@@ -17828,7 +17828,7 @@
         <v>0.001840328834169172</v>
       </c>
       <c r="AT95" t="n">
-        <v>0.003152610671525026</v>
+        <v>0.003152610671525025</v>
       </c>
       <c r="AU95" t="n">
         <v>0.002672917154051957</v>
@@ -17855,22 +17855,22 @@
         <v>0.02186315756770723</v>
       </c>
       <c r="BC95" t="n">
-        <v>0.003944810752093875</v>
+        <v>0.003944810752093874</v>
       </c>
       <c r="BD95" t="n">
         <v>0.01192487461072182</v>
       </c>
       <c r="BE95" t="n">
-        <v>0.002933007662454921</v>
+        <v>0.00293300766245492</v>
       </c>
       <c r="BF95" t="n">
-        <v>0.003061722512511509</v>
+        <v>0.00306172251251151</v>
       </c>
       <c r="BG95" t="n">
-        <v>0.002883638922539685</v>
+        <v>0.002883638922539686</v>
       </c>
       <c r="BH95" t="n">
-        <v>0.003794487286034799</v>
+        <v>0.003794487286034798</v>
       </c>
       <c r="BI95" t="n">
         <v>0.003313493919714886</v>
@@ -17879,7 +17879,7 @@
         <v>0.00282419253044176</v>
       </c>
       <c r="BK95" t="n">
-        <v>0.0009342689785565877</v>
+        <v>0.0009342689785565876</v>
       </c>
       <c r="BL95" t="n">
         <v>0.001452250867609204</v>
@@ -17897,7 +17897,7 @@
         <v>0.002521481598783394</v>
       </c>
       <c r="BQ95" t="n">
-        <v>0.00209734308769272</v>
+        <v>0.002097343087692719</v>
       </c>
       <c r="BR95" t="n">
         <v>0.0139774013234821</v>
@@ -17915,13 +17915,13 @@
         <v>0.01015954679528478</v>
       </c>
       <c r="BW95" t="n">
-        <v>0.0108249814779468</v>
+        <v>0.01082498147794681</v>
       </c>
       <c r="BX95" t="n">
         <v>0.009993584000463455</v>
       </c>
       <c r="BY95" t="n">
-        <v>0.005561701024296139</v>
+        <v>0.00556170102429614</v>
       </c>
       <c r="BZ95" t="n">
         <v>0.003338290952490097</v>
@@ -18418,7 +18418,7 @@
         <v>0.0001018944803612778</v>
       </c>
       <c r="F98" t="n">
-        <v>7.215558334980977e-05</v>
+        <v>7.215558334980976e-05</v>
       </c>
       <c r="G98" t="n">
         <v>2.558860751453315e-05</v>
@@ -18505,13 +18505,13 @@
         <v>1.788618419693222e-05</v>
       </c>
       <c r="AI98" t="n">
-        <v>3.550822760389927e-05</v>
+        <v>3.550822760389926e-05</v>
       </c>
       <c r="AJ98" t="n">
-        <v>3.782778380294793e-05</v>
+        <v>3.782778380294792e-05</v>
       </c>
       <c r="AK98" t="n">
-        <v>5.343378273732738e-05</v>
+        <v>5.343378273732739e-05</v>
       </c>
       <c r="AL98" t="n">
         <v>7.067388997057134e-05</v>
@@ -18596,16 +18596,16 @@
         <v>0.000152081360465</v>
       </c>
       <c r="BN98" t="n">
-        <v>8.3386979928e-05</v>
+        <v>8.338697992799998e-05</v>
       </c>
       <c r="BO98" t="n">
         <v>0.000126892222419</v>
       </c>
       <c r="BP98" t="n">
-        <v>0.0005175735176056662</v>
+        <v>0.0005175735176056663</v>
       </c>
       <c r="BQ98" t="n">
-        <v>0.0004382197854091894</v>
+        <v>0.0004382197854091893</v>
       </c>
       <c r="BR98" t="n">
         <v>0.0001019859766941122</v>
@@ -19918,7 +19918,7 @@
         <v>0.0004801342329667882</v>
       </c>
       <c r="L110" t="n">
-        <v>0.0004020246359164168</v>
+        <v>0.0004020246359164169</v>
       </c>
       <c r="M110" t="n">
         <v>0.0004994564682699115</v>
@@ -19936,10 +19936,10 @@
         <v>0.0006668307876846532</v>
       </c>
       <c r="R110" t="n">
-        <v>0.0006904996719005619</v>
+        <v>0.0006904996719005618</v>
       </c>
       <c r="S110" t="n">
-        <v>0.0007168048535943013</v>
+        <v>0.0007168048535943012</v>
       </c>
       <c r="T110" t="n">
         <v>0.000691379209106993</v>
@@ -19966,10 +19966,10 @@
         <v>0.0011382403773992</v>
       </c>
       <c r="AB110" t="n">
-        <v>0.0005880848719870575</v>
+        <v>0.0005880848719870576</v>
       </c>
       <c r="AC110" t="n">
-        <v>0.0007853314875153462</v>
+        <v>0.0007853314875153461</v>
       </c>
       <c r="AD110" t="n">
         <v>0.0006582350282825715</v>
@@ -19978,10 +19978,10 @@
         <v>0.0007159694809132266</v>
       </c>
       <c r="AF110" t="n">
-        <v>0.0004190133500373945</v>
+        <v>0.0004190133500373946</v>
       </c>
       <c r="AG110" t="n">
-        <v>0.0005976944373176848</v>
+        <v>0.0005976944373176847</v>
       </c>
       <c r="AH110" t="n">
         <v>0.0005213659620774511</v>
@@ -19996,7 +19996,7 @@
         <v>0.000510436086101687</v>
       </c>
       <c r="AL110" t="n">
-        <v>0.0005944507030367121</v>
+        <v>0.0005944507030367122</v>
       </c>
       <c r="AM110" t="n">
         <v>0.0005006681759467027</v>
@@ -20005,7 +20005,7 @@
         <v>0.001060126552388265</v>
       </c>
       <c r="AO110" t="n">
-        <v>0.0009420685665781238</v>
+        <v>0.0009420685665781237</v>
       </c>
       <c r="AP110" t="n">
         <v>0.0009389400538897013</v>
@@ -20014,13 +20014,13 @@
         <v>0.0005520399009031443</v>
       </c>
       <c r="AR110" t="n">
-        <v>0.0006734879363981906</v>
+        <v>0.0006734879363981905</v>
       </c>
       <c r="AS110" t="n">
         <v>0.0005514490852979692</v>
       </c>
       <c r="AT110" t="n">
-        <v>0.00130151057240713</v>
+        <v>0.001301510572407131</v>
       </c>
       <c r="AU110" t="n">
         <v>0.001250762036023213</v>
@@ -20035,16 +20035,16 @@
         <v>0.003457693085035614</v>
       </c>
       <c r="AY110" t="n">
-        <v>0.003521711169552216</v>
+        <v>0.003521711169552215</v>
       </c>
       <c r="AZ110" t="n">
         <v>0.006497198629602104</v>
       </c>
       <c r="BA110" t="n">
-        <v>0.006282882406783113</v>
+        <v>0.006282882406783112</v>
       </c>
       <c r="BB110" t="n">
-        <v>0.001841328517187072</v>
+        <v>0.001841328517187071</v>
       </c>
       <c r="BC110" t="n">
         <v>0.004103174247983767</v>
@@ -20062,13 +20062,13 @@
         <v>0.001421166575559538</v>
       </c>
       <c r="BH110" t="n">
-        <v>0.001406828077442943</v>
+        <v>0.001406828077442944</v>
       </c>
       <c r="BI110" t="n">
         <v>0.001654783283981308</v>
       </c>
       <c r="BJ110" t="n">
-        <v>0.006488985077977999</v>
+        <v>0.006488985077978</v>
       </c>
       <c r="BK110" t="n">
         <v>0.006081659193312114</v>
@@ -20077,7 +20077,7 @@
         <v>0.001729764740965773</v>
       </c>
       <c r="BM110" t="n">
-        <v>0.002390942663031001</v>
+        <v>0.002390942663031</v>
       </c>
       <c r="BN110" t="n">
         <v>0.001318854357339</v>
@@ -20089,7 +20089,7 @@
         <v>0.004626792386700709</v>
       </c>
       <c r="BQ110" t="n">
-        <v>0.003358275565327552</v>
+        <v>0.003358275565327551</v>
       </c>
       <c r="BR110" t="n">
         <v>0.001453025788720055</v>

--- a/data/proteomics/ecGEM_volume_size_across_compartment.xlsx
+++ b/data/proteomics/ecGEM_volume_size_across_compartment.xlsx
@@ -828,172 +828,172 @@
         <v>1.049987227663292</v>
       </c>
       <c r="D2" t="n">
-        <v>1.256144698163695</v>
+        <v>1.256144698163693</v>
       </c>
       <c r="E2" t="n">
         <v>1.126161559236469</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8591535621148844</v>
+        <v>0.859153562114885</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5177522722082551</v>
+        <v>0.5177522722082555</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4666819413577978</v>
+        <v>0.4666819413577977</v>
       </c>
       <c r="I2" t="n">
         <v>0.477786040685783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6330785040863716</v>
+        <v>0.6330785040863718</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6613640442646163</v>
+        <v>0.6613640442646157</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5660421895011404</v>
+        <v>0.56604218950114</v>
       </c>
       <c r="M2" t="n">
         <v>0.360263035528362</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3749143332130898</v>
+        <v>0.3749143332130894</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5276593890769891</v>
+        <v>0.5276593890769892</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5202648195530772</v>
+        <v>0.5202648195530774</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4498247096478478</v>
+        <v>0.4498247096478482</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4554912368158401</v>
+        <v>0.4554912368158404</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4539163384409709</v>
+        <v>0.4539163384409713</v>
       </c>
       <c r="T2" t="n">
         <v>0.4538914170691597</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4675886634707169</v>
+        <v>0.467588663470717</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6834746554681825</v>
+        <v>0.6834746554681822</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6922160338100314</v>
+        <v>0.6922160338100313</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6425355055851452</v>
+        <v>0.6425355055851448</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7890243023013782</v>
+        <v>0.7890243023013779</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8378464312370537</v>
+        <v>0.8378464312370538</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8377193499862392</v>
+        <v>0.8377193499862391</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8231267106010238</v>
+        <v>0.8231267106010242</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9476955356448307</v>
+        <v>0.9476955356448303</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9728897876467884</v>
+        <v>0.9728897876467881</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9139430839228608</v>
+        <v>0.9139430839228609</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5829530587726548</v>
+        <v>0.5829530587726549</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.7268751833027058</v>
+        <v>0.7268751833027056</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3935434142391808</v>
+        <v>0.3935434142391811</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6515758008392198</v>
+        <v>0.6515758008392197</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.6242473643339939</v>
+        <v>0.6242473643339935</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7431975111596303</v>
+        <v>0.7431975111596301</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9145002333868393</v>
+        <v>0.9145002333868395</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.7826390134633697</v>
+        <v>0.7826390134633695</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.710959504014204</v>
+        <v>0.7109595040142034</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6721743395151187</v>
+        <v>0.6721743395151185</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6932823629116796</v>
+        <v>0.693282362911679</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6040513471139125</v>
+        <v>0.6040513471139126</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7408238220066246</v>
+        <v>0.7408238220066252</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6954901855513763</v>
+        <v>0.6954901855513761</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.9365220890647193</v>
+        <v>0.9365220890647181</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.8595203523287716</v>
+        <v>0.859520352328772</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8717060833677142</v>
+        <v>0.8717060833677145</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9743975669753336</v>
+        <v>0.9743975669753341</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.8412655522800151</v>
+        <v>0.8412655522800149</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.8231790574142378</v>
+        <v>0.823179057414238</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.092944924043125</v>
+        <v>1.092944924043126</v>
       </c>
       <c r="BA2" t="n">
         <v>1.048336875220488</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.844646275235932</v>
+        <v>1.844646275235933</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.032373365445709</v>
+        <v>1.032373365445708</v>
       </c>
       <c r="BD2" t="n">
         <v>1.82723526101249</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.8126665509427405</v>
+        <v>0.8126665509427401</v>
       </c>
       <c r="BF2" t="n">
         <v>1.040625959103209</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.000141129523174</v>
+        <v>1.000141129523175</v>
       </c>
       <c r="BH2" t="n">
         <v>1.119381185529753</v>
@@ -1005,52 +1005,52 @@
         <v>0.9734894186343692</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5501383651094054</v>
+        <v>0.5501383651094048</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.4870335389535334</v>
+        <v>0.4870335389535335</v>
       </c>
       <c r="BM2" t="n">
         <v>0.5608789831753038</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.5394131063841405</v>
+        <v>0.5394131063841406</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.775656923541114</v>
+        <v>0.775656923541115</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.6802600342673161</v>
+        <v>0.6802600342673157</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.4241860246430975</v>
+        <v>0.4241860246430973</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.9775864692441003</v>
+        <v>0.9775864692441001</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.040537443180722</v>
+        <v>1.040537443180723</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.082974163833796</v>
+        <v>1.082974163833795</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.152478924546474</v>
+        <v>1.152478924546475</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.8246314982360731</v>
+        <v>0.8246314982360721</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.9228255200030694</v>
+        <v>0.9228255200030693</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9289614786933184</v>
+        <v>0.9289614786933189</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.8682631427090874</v>
+        <v>0.8682631427090877</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.7340393413746037</v>
+        <v>0.7340393413746046</v>
       </c>
     </row>
     <row r="3">
@@ -1284,7 +1284,7 @@
         <v>0.0003322398597394922</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003772259410490469</v>
+        <v>0.000377225941049047</v>
       </c>
       <c r="E4" t="n">
         <v>0.0003583614413244079</v>
@@ -1308,7 +1308,7 @@
         <v>0.0001589428251550112</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001513537277061899</v>
+        <v>0.0001513537277061898</v>
       </c>
       <c r="M4" t="n">
         <v>0.0001160343239901041</v>
@@ -1326,13 +1326,13 @@
         <v>0.0001571374688951673</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000158748551935655</v>
+        <v>0.0001587485519356551</v>
       </c>
       <c r="S4" t="n">
         <v>0.0001663830337042046</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0001627185802885622</v>
+        <v>0.0001627185802885623</v>
       </c>
       <c r="U4" t="n">
         <v>0.0001727746616229145</v>
@@ -1344,7 +1344,7 @@
         <v>0.0001966598234159971</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0002023831851075061</v>
+        <v>0.0002023831851075062</v>
       </c>
       <c r="Y4" t="n">
         <v>0.0002142485712977009</v>
@@ -1368,10 +1368,10 @@
         <v>0.0001774014398450595</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0001323986378824871</v>
+        <v>0.000132398637882487</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.000155584009051211</v>
+        <v>0.0001555840090512109</v>
       </c>
       <c r="AH4" t="n">
         <v>0.000123808698491444</v>
@@ -1437,13 +1437,13 @@
         <v>0.001325319950023928</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001255572885887421</v>
+        <v>0.00125557288588742</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.002162014369514075</v>
+        <v>0.002162014369514076</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001095364362484891</v>
+        <v>0.00109536436248489</v>
       </c>
       <c r="BF4" t="n">
         <v>0.0009090216311288476</v>
@@ -1461,7 +1461,7 @@
         <v>0.0027146145554712</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002191342156808938</v>
+        <v>0.002191342156808939</v>
       </c>
       <c r="BL4" t="n">
         <v>0.0004860406399360256</v>
@@ -1479,7 +1479,7 @@
         <v>0.002714725365014473</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.002569892358410915</v>
+        <v>0.002569892358410914</v>
       </c>
       <c r="BR4" t="n">
         <v>0.0005900622026359213</v>
@@ -1488,13 +1488,13 @@
         <v>0.0006457381892774908</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0008656412027750573</v>
+        <v>0.0008656412027750572</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0009501970979753655</v>
+        <v>0.0009501970979753656</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0008203778733645753</v>
+        <v>0.0008203778733645755</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0008128982079587995</v>
@@ -1503,10 +1503,10 @@
         <v>0.0008208661226804844</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0008323106787265849</v>
+        <v>0.0008323106787265848</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0007116146950101079</v>
+        <v>0.000711614695010108</v>
       </c>
     </row>
     <row r="5">
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5143080793185156</v>
+        <v>0.5143080793185157</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3103516766423366</v>
+        <v>0.3103516766423367</v>
       </c>
       <c r="E6" t="n">
         <v>0.2750735048448869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3810908453460468</v>
+        <v>0.381090845346047</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1861148882390055</v>
+        <v>0.1861148882390054</v>
       </c>
       <c r="H6" t="n">
-        <v>0.164877731447555</v>
+        <v>0.1648777314475549</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1749548708358681</v>
+        <v>0.1749548708358682</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2094000186918242</v>
+        <v>0.2094000186918243</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2292392539856247</v>
+        <v>0.2292392539856248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1875375972021855</v>
+        <v>0.1875375972021854</v>
       </c>
       <c r="M6" t="n">
         <v>0.1412399583958422</v>
@@ -1793,16 +1793,16 @@
         <v>0.1451808310036761</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1824883645118466</v>
+        <v>0.1824883645118465</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1997833623260609</v>
+        <v>0.1997833623260608</v>
       </c>
       <c r="Q6" t="n">
         <v>0.178256221927974</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1729613283317465</v>
+        <v>0.1729613283317464</v>
       </c>
       <c r="S6" t="n">
         <v>0.1669621900372411</v>
@@ -1820,13 +1820,13 @@
         <v>0.2594294011896115</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2514658596404651</v>
+        <v>0.251465859640465</v>
       </c>
       <c r="Y6" t="n">
         <v>0.3197577467601339</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3520426017975076</v>
+        <v>0.3520426017975074</v>
       </c>
       <c r="AA6" t="n">
         <v>0.3206257421465145</v>
@@ -1835,10 +1835,10 @@
         <v>0.2583891258671711</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3272905187455606</v>
+        <v>0.3272905187455604</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3457428317054132</v>
+        <v>0.3457428317054134</v>
       </c>
       <c r="AE6" t="n">
         <v>0.3333422184760381</v>
@@ -1850,34 +1850,34 @@
         <v>0.2277272586538105</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1332400412292828</v>
+        <v>0.1332400412292829</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2267851652768534</v>
+        <v>0.2267851652768532</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2227594304593763</v>
+        <v>0.2227594304593762</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2535153256863985</v>
+        <v>0.2535153256863986</v>
       </c>
       <c r="AL6" t="n">
         <v>0.3218798731255537</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2559670972823109</v>
+        <v>0.255967097282311</v>
       </c>
       <c r="AN6" t="n">
         <v>0.2664625562288911</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2320396131717255</v>
+        <v>0.2320396131717256</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.2343507032601449</v>
+        <v>0.2343507032601447</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.1819395718445251</v>
+        <v>0.181939571844525</v>
       </c>
       <c r="AR6" t="n">
         <v>0.2550896352623452</v>
@@ -1889,16 +1889,16 @@
         <v>0.3024855845165623</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2839890668609882</v>
+        <v>0.2839890668609884</v>
       </c>
       <c r="AV6" t="n">
         <v>0.2905573828441335</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.3707407690831376</v>
+        <v>0.3707407690831379</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.213810083192056</v>
+        <v>0.2138100831920559</v>
       </c>
       <c r="AY6" t="n">
         <v>0.1877759087827729</v>
@@ -1910,28 +1910,28 @@
         <v>0.2170785297149514</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.5144229908985453</v>
+        <v>0.5144229908985455</v>
       </c>
       <c r="BC6" t="n">
         <v>0.42265632896176</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.6190479563544694</v>
+        <v>0.6190479563544693</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.36594371610543</v>
+        <v>0.3659437161054302</v>
       </c>
       <c r="BF6" t="n">
         <v>0.3878414958836536</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.3852939404380494</v>
+        <v>0.3852939404380497</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.3902524848553712</v>
+        <v>0.390252484855371</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.3823566278171409</v>
+        <v>0.382356627817141</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.3971948382237463</v>
@@ -1946,13 +1946,13 @@
         <v>0.2196026808143791</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1516482497677021</v>
+        <v>0.151648249767702</v>
       </c>
       <c r="BO6" t="n">
         <v>0.1836149940633889</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.3147745456503823</v>
+        <v>0.3147745456503825</v>
       </c>
       <c r="BQ6" t="n">
         <v>0.1785599988289098</v>
@@ -1961,28 +1961,28 @@
         <v>0.2785013426686078</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.285156449029961</v>
+        <v>0.2851564490299612</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.3020976186530686</v>
+        <v>0.3020976186530687</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.3216982265184689</v>
+        <v>0.321698226518469</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2305155942339972</v>
+        <v>0.2305155942339974</v>
       </c>
       <c r="BW6" t="n">
         <v>0.2554124485781185</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.2684452580795441</v>
+        <v>0.2684452580795439</v>
       </c>
       <c r="BY6" t="n">
         <v>0.27637629607699</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.2569175824963994</v>
+        <v>0.2569175824963995</v>
       </c>
     </row>
     <row r="7">
@@ -1998,10 +1998,10 @@
         <v>1.227702900574952</v>
       </c>
       <c r="D7" t="n">
-        <v>1.107817742152018</v>
+        <v>1.107817742152019</v>
       </c>
       <c r="E7" t="n">
-        <v>1.166235345688813</v>
+        <v>1.166235345688814</v>
       </c>
       <c r="F7" t="n">
         <v>1.288541085963575</v>
@@ -2010,64 +2010,64 @@
         <v>0.4493567617922103</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4038511183931698</v>
+        <v>0.4038511183931699</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4158391074185478</v>
+        <v>0.4158391074185479</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7506920834617156</v>
+        <v>0.750692083461716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7827808561125238</v>
+        <v>0.7827808561125242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6761619508185628</v>
+        <v>0.6761619508185622</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3274162882041731</v>
+        <v>0.327416288204173</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3454188670451778</v>
+        <v>0.3454188670451776</v>
       </c>
       <c r="O7" t="n">
-        <v>0.467549748723216</v>
+        <v>0.4675497487232156</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4652831266977556</v>
+        <v>0.4652831266977558</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3950000762617641</v>
+        <v>0.395000076261764</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4048519269576955</v>
+        <v>0.4048519269576953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4339307388466827</v>
+        <v>0.433930738846683</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4220583719045811</v>
+        <v>0.4220583719045813</v>
       </c>
       <c r="U7" t="n">
-        <v>0.426144659236355</v>
+        <v>0.4261446592363546</v>
       </c>
       <c r="V7" t="n">
         <v>0.674187322684403</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6815970976960154</v>
+        <v>0.681597097696016</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6646391909939912</v>
+        <v>0.6646391909939915</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8213980908423483</v>
+        <v>0.8213980908423479</v>
       </c>
       <c r="Z7" t="n">
         <v>0.8441529395581465</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.8582885339151144</v>
+        <v>0.8582885339151139</v>
       </c>
       <c r="AB7" t="n">
         <v>1.076929476043778</v>
@@ -2076,97 +2076,97 @@
         <v>1.299972964871672</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.289230897111436</v>
+        <v>1.289230897111437</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9815952440526076</v>
+        <v>0.9815952440526069</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5366674650241221</v>
+        <v>0.5366674650241223</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.6464002313312951</v>
+        <v>0.6464002313312948</v>
       </c>
       <c r="AH7" t="n">
         <v>0.3152085494247798</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5465774667708021</v>
+        <v>0.5465774667708025</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.5493768416962733</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.687397361952594</v>
+        <v>0.6873973619525929</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.861485790262135</v>
+        <v>0.8614857902621352</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.7182248758041915</v>
+        <v>0.7182248758041918</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.6236792409363762</v>
+        <v>0.6236792409363757</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5552088172173946</v>
+        <v>0.555208817217395</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.5958182796999952</v>
+        <v>0.5958182796999951</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.5818973228351779</v>
+        <v>0.5818973228351776</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.8080113656938166</v>
+        <v>0.8080113656938167</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.6279434500586174</v>
+        <v>0.6279434500586168</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.814667150983021</v>
+        <v>0.8146671509830208</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.7295714607737496</v>
+        <v>0.7295714607737497</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.7288609611279501</v>
+        <v>0.7288609611279503</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.9015501718970115</v>
+        <v>0.9015501718970108</v>
       </c>
       <c r="AX7" t="n">
         <v>1.155577028741131</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.8933718282368677</v>
+        <v>0.8933718282368679</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.495515052882004</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.261379992237812</v>
+        <v>1.26137999223781</v>
       </c>
       <c r="BB7" t="n">
         <v>1.56437021790089</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.081264416173102</v>
+        <v>1.081264416173101</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.634685651839967</v>
+        <v>1.634685651839968</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.9198683368265115</v>
+        <v>0.9198683368265123</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.097489586968306</v>
+        <v>1.097489586968307</v>
       </c>
       <c r="BG7" t="n">
         <v>1.080850846096522</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.1146951940471</v>
+        <v>1.114695194047101</v>
       </c>
       <c r="BI7" t="n">
         <v>1.113360493497043</v>
@@ -2175,52 +2175,52 @@
         <v>1.118596374007212</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5141265167424507</v>
+        <v>0.5141265167424512</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5848631786052085</v>
+        <v>0.5848631786052089</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6879163558332755</v>
+        <v>0.6879163558332745</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.4993418889399707</v>
+        <v>0.4993418889399709</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.6235051106462602</v>
+        <v>0.6235051106462599</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.7908840580962712</v>
+        <v>0.7908840580962715</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.4817974991180228</v>
+        <v>0.481797499118023</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.7694632132794637</v>
+        <v>0.7694632132794633</v>
       </c>
       <c r="BS7" t="n">
         <v>0.7986595779968452</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.8497655618256694</v>
+        <v>0.8497655618256693</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.9129961750019356</v>
+        <v>0.9129961750019355</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.6495737684084248</v>
+        <v>0.6495737684084243</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7344637977690033</v>
+        <v>0.7344637977690034</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.7637157314283928</v>
+        <v>0.763715731428393</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.7684553469714386</v>
+        <v>0.7684553469714389</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.7054232521858324</v>
+        <v>0.7054232521858319</v>
       </c>
     </row>
     <row r="8">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7982390795516946</v>
+        <v>0.7982390795516952</v>
       </c>
       <c r="D8" t="n">
         <v>0.7393193884560378</v>
       </c>
       <c r="E8" t="n">
-        <v>0.619345291258979</v>
+        <v>0.6193452912589791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6492396050707752</v>
+        <v>0.649239605070775</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2737602284041801</v>
+        <v>0.2737602284041799</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2339410648605333</v>
+        <v>0.2339410648605334</v>
       </c>
       <c r="I8" t="n">
         <v>0.2375708946283366</v>
@@ -2257,19 +2257,19 @@
         <v>0.3004151312184635</v>
       </c>
       <c r="K8" t="n">
-        <v>0.315345590719653</v>
+        <v>0.3153455907196531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.267092117313193</v>
+        <v>0.2670921173131931</v>
       </c>
       <c r="M8" t="n">
         <v>0.1924005285432476</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1951699541240396</v>
+        <v>0.1951699541240397</v>
       </c>
       <c r="O8" t="n">
-        <v>0.31324633991422</v>
+        <v>0.3132463399142199</v>
       </c>
       <c r="P8" t="n">
         <v>0.2920746868538087</v>
@@ -2287,25 +2287,25 @@
         <v>0.2384137940499195</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2405395568922333</v>
+        <v>0.2405395568922334</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3807334814021336</v>
+        <v>0.3807334814021335</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3825101421392363</v>
+        <v>0.3825101421392366</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3690861992735719</v>
+        <v>0.3690861992735717</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4872452010036449</v>
+        <v>0.487245201003645</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5450115984420971</v>
+        <v>0.5450115984420969</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5080470018680144</v>
+        <v>0.5080470018680143</v>
       </c>
       <c r="AB8" t="n">
         <v>0.3730032996525984</v>
@@ -2317,16 +2317,16 @@
         <v>0.4554396717984956</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4081776155867542</v>
+        <v>0.4081776155867541</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2965613066312803</v>
+        <v>0.2965613066312802</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3777935023335459</v>
+        <v>0.377793502333546</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2164781838518626</v>
+        <v>0.2164781838518625</v>
       </c>
       <c r="AI8" t="n">
         <v>0.3416887363714</v>
@@ -2335,7 +2335,7 @@
         <v>0.3123780421662213</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.2999350908331839</v>
+        <v>0.2999350908331838</v>
       </c>
       <c r="AL8" t="n">
         <v>0.3601947066162626</v>
@@ -2344,82 +2344,82 @@
         <v>0.3101394654783234</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.3658831692751931</v>
+        <v>0.3658831692751932</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.337982878961406</v>
+        <v>0.3379828789614061</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.3374959607947395</v>
+        <v>0.3374959607947397</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.2793935115354628</v>
+        <v>0.2793935115354629</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.3208014193879415</v>
+        <v>0.3208014193879416</v>
       </c>
       <c r="AS8" t="n">
         <v>0.3656109492187782</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5445909124963613</v>
+        <v>0.5445909124963614</v>
       </c>
       <c r="AU8" t="n">
         <v>0.4720523219880313</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.5054987189717977</v>
+        <v>0.5054987189717978</v>
       </c>
       <c r="AW8" t="n">
         <v>0.5508335816571837</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.4219282797917098</v>
+        <v>0.4219282797917099</v>
       </c>
       <c r="AY8" t="n">
         <v>0.4239808901691192</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.5598553049354346</v>
+        <v>0.5598553049354345</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.5413711884785151</v>
+        <v>0.5413711884785152</v>
       </c>
       <c r="BB8" t="n">
         <v>1.011244370521978</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.6964196231699886</v>
+        <v>0.6964196231699883</v>
       </c>
       <c r="BD8" t="n">
         <v>1.076919298804062</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.5778488099953577</v>
+        <v>0.5778488099953575</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.6151288257897005</v>
+        <v>0.6151288257897004</v>
       </c>
       <c r="BG8" t="n">
         <v>0.5998841874225795</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.6446558572924046</v>
+        <v>0.6446558572924049</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.6338407708263952</v>
+        <v>0.6338407708263951</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7077017395046326</v>
+        <v>0.7077017395046327</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.3646051222595128</v>
+        <v>0.3646051222595129</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.3815704345047605</v>
+        <v>0.3815704345047606</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.4144117842042941</v>
+        <v>0.4144117842042939</v>
       </c>
       <c r="BN8" t="n">
         <v>0.3114400057037329</v>
@@ -2431,31 +2431,31 @@
         <v>0.53761507544952</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.3081988538513361</v>
+        <v>0.308198853851336</v>
       </c>
       <c r="BR8" t="n">
         <v>0.5707863453682297</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.6093192567295522</v>
+        <v>0.609319256729552</v>
       </c>
       <c r="BT8" t="n">
         <v>0.6015885015292085</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.6165239432800269</v>
+        <v>0.6165239432800271</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.4083067263904818</v>
+        <v>0.4083067263904819</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.4385310140322546</v>
+        <v>0.4385310140322549</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.4662428397181792</v>
+        <v>0.4662428397181791</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.4582802526142648</v>
+        <v>0.4582802526142649</v>
       </c>
       <c r="BZ8" t="n">
         <v>0.4104237161057965</v>
@@ -2807,7 +2807,7 @@
         <v>0.1118711000126846</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06892571715862086</v>
+        <v>0.06892571715862088</v>
       </c>
       <c r="H11" t="n">
         <v>0.05487323214914212</v>
@@ -2834,16 +2834,16 @@
         <v>0.09974204941993269</v>
       </c>
       <c r="P11" t="n">
-        <v>0.07339573305615052</v>
+        <v>0.07339573305615051</v>
       </c>
       <c r="Q11" t="n">
         <v>0.06157716676391219</v>
       </c>
       <c r="R11" t="n">
-        <v>0.05771475927931041</v>
+        <v>0.0577147592793104</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04871636611428785</v>
+        <v>0.04871636611428786</v>
       </c>
       <c r="T11" t="n">
         <v>0.05527794592593267</v>
@@ -2855,7 +2855,7 @@
         <v>0.09543170810372335</v>
       </c>
       <c r="W11" t="n">
-        <v>0.09881859519773913</v>
+        <v>0.09881859519773911</v>
       </c>
       <c r="X11" t="n">
         <v>0.09364582980886042</v>
@@ -2873,10 +2873,10 @@
         <v>0.05190112496279513</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.06894696635695824</v>
+        <v>0.06894696635695825</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.07620633859554164</v>
+        <v>0.07620633859554166</v>
       </c>
       <c r="AE11" t="n">
         <v>0.08412395254498452</v>
@@ -2885,31 +2885,31 @@
         <v>0.07531449536145353</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.09156616234601626</v>
+        <v>0.09156616234601625</v>
       </c>
       <c r="AH11" t="n">
         <v>0.0629342456578984</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.09546658570361644</v>
+        <v>0.09546658570361642</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.07764318858642995</v>
+        <v>0.07764318858642996</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.05572766770626596</v>
+        <v>0.05572766770626595</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.05976905213957599</v>
+        <v>0.059769052139576</v>
       </c>
       <c r="AM11" t="n">
         <v>0.05571853850209376</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.08247918168038001</v>
+        <v>0.08247918168038003</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.08534858842759588</v>
+        <v>0.08534858842759589</v>
       </c>
       <c r="AP11" t="n">
         <v>0.08805876923953554</v>
@@ -2921,7 +2921,7 @@
         <v>0.06679790067919512</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.09338243358301306</v>
+        <v>0.09338243358301304</v>
       </c>
       <c r="AT11" t="n">
         <v>0.1714279720076306</v>
@@ -2933,7 +2933,7 @@
         <v>0.1471682092617092</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1393609109815633</v>
+        <v>0.1393609109815632</v>
       </c>
       <c r="AX11" t="n">
         <v>0.01001596512491797</v>
@@ -2945,7 +2945,7 @@
         <v>0.02798295840196091</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.02561427886906426</v>
+        <v>0.02561427886906425</v>
       </c>
       <c r="BB11" t="n">
         <v>0.1558207086678432</v>
@@ -2966,7 +2966,7 @@
         <v>0.08501895718879579</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.09192784981593212</v>
+        <v>0.09192784981593213</v>
       </c>
       <c r="BI11" t="n">
         <v>0.08779764787329428</v>
@@ -2981,7 +2981,7 @@
         <v>0.07730229704604426</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.020574585230125</v>
+        <v>0.02057458523012499</v>
       </c>
       <c r="BN11" t="n">
         <v>0.01125310403415</v>
@@ -2990,13 +2990,13 @@
         <v>0.022162660041695</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.07639364114680339</v>
+        <v>0.07639364114680341</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04238247931725552</v>
+        <v>0.04238247931725551</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.09644484929134946</v>
+        <v>0.09644484929134947</v>
       </c>
       <c r="BS11" t="n">
         <v>0.09541030931478837</v>
@@ -3005,7 +3005,7 @@
         <v>0.07585307604587255</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0696862829730249</v>
+        <v>0.06968628297302491</v>
       </c>
       <c r="BV11" t="n">
         <v>0.03996831038593669</v>
@@ -3014,10 +3014,10 @@
         <v>0.04209263817317187</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.04549972156230022</v>
+        <v>0.04549972156230023</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04888253032247341</v>
+        <v>0.0488825303224734</v>
       </c>
       <c r="BZ11" t="n">
         <v>0.0451101180288321</v>
@@ -3036,7 +3036,7 @@
         <v>0.02217893542236355</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02344663608176972</v>
+        <v>0.02344663608176973</v>
       </c>
       <c r="E12" t="n">
         <v>0.0257486870304725</v>
@@ -3045,22 +3045,22 @@
         <v>0.05069265433597803</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01995989614079386</v>
+        <v>0.01995989614079387</v>
       </c>
       <c r="H12" t="n">
         <v>0.01782330660639849</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0186634861483982</v>
+        <v>0.01866348614839821</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02309432970726709</v>
+        <v>0.02309432970726708</v>
       </c>
       <c r="K12" t="n">
         <v>0.02497715567570374</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02080467048728496</v>
+        <v>0.02080467048728495</v>
       </c>
       <c r="M12" t="n">
         <v>0.01558937166865422</v>
@@ -3072,10 +3072,10 @@
         <v>0.01840606919011975</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02689027045874541</v>
+        <v>0.02689027045874543</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02296376585644248</v>
+        <v>0.02296376585644247</v>
       </c>
       <c r="R12" t="n">
         <v>0.0233472714720706</v>
@@ -3084,10 +3084,10 @@
         <v>0.02587139832910626</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02368345547736158</v>
+        <v>0.02368345547736157</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02572533352043707</v>
+        <v>0.02572533352043708</v>
       </c>
       <c r="V12" t="n">
         <v>0.0313206049997131</v>
@@ -3099,25 +3099,25 @@
         <v>0.03171876961288196</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03288511794383801</v>
+        <v>0.032885117943838</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.03399075750222566</v>
+        <v>0.03399075750222565</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03588400297912371</v>
+        <v>0.0358840029791237</v>
       </c>
       <c r="AB12" t="n">
         <v>0.02950446607677986</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03808332616233212</v>
+        <v>0.03808332616233209</v>
       </c>
       <c r="AD12" t="n">
         <v>0.03406270465241797</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.02854469534692618</v>
+        <v>0.02854469534692619</v>
       </c>
       <c r="AF12" t="n">
         <v>0.01740077907179848</v>
@@ -3132,40 +3132,40 @@
         <v>0.0303858054517678</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.03057261998519871</v>
+        <v>0.0305726199851987</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.02647517203616514</v>
+        <v>0.02647517203616515</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02807863178441878</v>
+        <v>0.02807863178441877</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.02445647431249599</v>
+        <v>0.024456474312496</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.03563125512395165</v>
+        <v>0.03563125512395163</v>
       </c>
       <c r="AO12" t="n">
         <v>0.03248034163721467</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.03486475110574932</v>
+        <v>0.03486475110574931</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.01848322500797087</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.02695778819819575</v>
+        <v>0.02695778819819574</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.01997099923935498</v>
+        <v>0.01997099923935496</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.03250913189512489</v>
+        <v>0.03250913189512488</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.03111070355504049</v>
+        <v>0.03111070355504048</v>
       </c>
       <c r="AV12" t="n">
         <v>0.03272613865220685</v>
@@ -3174,25 +3174,25 @@
         <v>0.02977312935865722</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.038102974181191</v>
+        <v>0.03810297418119101</v>
       </c>
       <c r="AY12" t="n">
         <v>0.05264942286469058</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.03744019642051501</v>
+        <v>0.037440196420515</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.04004923612835318</v>
+        <v>0.04004923612835316</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.06073519467565329</v>
+        <v>0.06073519467565326</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.05875149224500057</v>
+        <v>0.05875149224500056</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.09125275566043056</v>
+        <v>0.09125275566043059</v>
       </c>
       <c r="BE12" t="n">
         <v>0.04779410468314452</v>
@@ -3201,61 +3201,61 @@
         <v>0.0321825679654386</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.03063281704566328</v>
+        <v>0.03063281704566329</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.03643799999227415</v>
+        <v>0.03643799999227416</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.04054942679106745</v>
+        <v>0.04054942679106746</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.08540144975993237</v>
+        <v>0.08540144975993236</v>
       </c>
       <c r="BK12" t="n">
         <v>0.07530277780062522</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.02391613228651358</v>
+        <v>0.02391613228651357</v>
       </c>
       <c r="BM12" t="n">
         <v>0.03366601921925902</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.022851172477024</v>
+        <v>0.02285117247702399</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.028088550008779</v>
+        <v>0.02808855000877899</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.06374698490179787</v>
+        <v>0.06374698490179785</v>
       </c>
       <c r="BQ12" t="n">
         <v>0.04717947072476981</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.02738103477203083</v>
+        <v>0.02738103477203082</v>
       </c>
       <c r="BS12" t="n">
         <v>0.03365105264998251</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.04915377444081242</v>
+        <v>0.04915377444081243</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.05232710193669216</v>
+        <v>0.05232710193669213</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.03455020299482121</v>
+        <v>0.03455020299482119</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.03297990757152342</v>
+        <v>0.03297990757152343</v>
       </c>
       <c r="BX12" t="n">
         <v>0.02867831836361502</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02688058534524348</v>
+        <v>0.02688058534524349</v>
       </c>
       <c r="BZ12" t="n">
         <v>0.02335473576866817</v>
@@ -3485,13 +3485,13 @@
         <v>0.01152972927726868</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0181645781850966</v>
+        <v>0.01816457818509659</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009039985626760323</v>
+        <v>0.009039985626760326</v>
       </c>
       <c r="G14" t="n">
-        <v>0.008849888610613548</v>
+        <v>0.008849888610613546</v>
       </c>
       <c r="H14" t="n">
         <v>0.008143144863982729</v>
@@ -3506,22 +3506,22 @@
         <v>0.01418015712387644</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01211468273141171</v>
+        <v>0.01211468273141172</v>
       </c>
       <c r="M14" t="n">
         <v>0.005664886637643952</v>
       </c>
       <c r="N14" t="n">
-        <v>0.006371476798339921</v>
+        <v>0.006371476798339919</v>
       </c>
       <c r="O14" t="n">
-        <v>0.008057841190896831</v>
+        <v>0.008057841190896829</v>
       </c>
       <c r="P14" t="n">
         <v>0.009598145047686506</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007903687573520562</v>
+        <v>0.00790368757352056</v>
       </c>
       <c r="R14" t="n">
         <v>0.00827676131353856</v>
@@ -3530,16 +3530,16 @@
         <v>0.00899804286679429</v>
       </c>
       <c r="T14" t="n">
-        <v>0.008896080946413852</v>
+        <v>0.008896080946413854</v>
       </c>
       <c r="U14" t="n">
-        <v>0.008952079256406321</v>
+        <v>0.00895207925640632</v>
       </c>
       <c r="V14" t="n">
         <v>0.01155991986586699</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01180826333695914</v>
+        <v>0.01180826333695913</v>
       </c>
       <c r="X14" t="n">
         <v>0.01012377605117148</v>
@@ -3569,10 +3569,10 @@
         <v>0.009689784133443647</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01150420343091633</v>
+        <v>0.01150420343091632</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.006822422829576734</v>
+        <v>0.006822422829576733</v>
       </c>
       <c r="AI14" t="n">
         <v>0.01155994513074424</v>
@@ -3587,13 +3587,13 @@
         <v>0.02063305439972827</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.01863683620436578</v>
+        <v>0.01863683620436579</v>
       </c>
       <c r="AN14" t="n">
         <v>0.01302123278754891</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.01212092176337464</v>
+        <v>0.01212092176337463</v>
       </c>
       <c r="AP14" t="n">
         <v>0.01201232559268637</v>
@@ -3605,7 +3605,7 @@
         <v>0.01321350647877024</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.01100453066871732</v>
+        <v>0.01100453066871731</v>
       </c>
       <c r="AT14" t="n">
         <v>0.01402912361937925</v>
@@ -3638,7 +3638,7 @@
         <v>0.02974563798119256</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0510478902493688</v>
+        <v>0.05104789024936879</v>
       </c>
       <c r="BE14" t="n">
         <v>0.02509616272718705</v>
@@ -3659,7 +3659,7 @@
         <v>0.0203025774801292</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.01475217002920228</v>
+        <v>0.01475217002920229</v>
       </c>
       <c r="BL14" t="n">
         <v>0.01224283383017588</v>
@@ -3674,7 +3674,7 @@
         <v>0.01932621244695</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01478509281969277</v>
+        <v>0.01478509281969276</v>
       </c>
       <c r="BQ14" t="n">
         <v>0.01152011254863777</v>
@@ -3689,19 +3689,19 @@
         <v>0.03407933714016372</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.03653309637381602</v>
+        <v>0.03653309637381603</v>
       </c>
       <c r="BV14" t="n">
         <v>0.02584852485115112</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.02675647249178734</v>
+        <v>0.02675647249178733</v>
       </c>
       <c r="BX14" t="n">
         <v>0.02318878861811598</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.01898939651890568</v>
+        <v>0.01898939651890569</v>
       </c>
       <c r="BZ14" t="n">
         <v>0.01553410251685018</v>
@@ -3723,10 +3723,10 @@
         <v>0.001553017163584355</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002789251802392839</v>
+        <v>0.00278925180239284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001424053347866576</v>
+        <v>0.001424053347866577</v>
       </c>
       <c r="G15" t="n">
         <v>0.001287688428877839</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01405326009579804</v>
+        <v>0.01405326009579805</v>
       </c>
       <c r="D16" t="n">
         <v>0.01305972168248062</v>
@@ -3967,7 +3967,7 @@
         <v>0.020397354990239</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003622539197324586</v>
+        <v>0.003622539197324587</v>
       </c>
       <c r="H16" t="n">
         <v>0.003183351670729165</v>
@@ -3979,7 +3979,7 @@
         <v>0.004413980511379809</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004369696862489717</v>
+        <v>0.004369696862489716</v>
       </c>
       <c r="L16" t="n">
         <v>0.00424270997631654</v>
@@ -3988,7 +3988,7 @@
         <v>0.003247820223645693</v>
       </c>
       <c r="N16" t="n">
-        <v>0.003354895189327942</v>
+        <v>0.003354895189327943</v>
       </c>
       <c r="O16" t="n">
         <v>0.003338003396389623</v>
@@ -4000,16 +4000,16 @@
         <v>0.004496117447621103</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0044904353840833</v>
+        <v>0.004490435384083299</v>
       </c>
       <c r="S16" t="n">
         <v>0.005346889227240285</v>
       </c>
       <c r="T16" t="n">
-        <v>0.005247856527636872</v>
+        <v>0.005247856527636873</v>
       </c>
       <c r="U16" t="n">
-        <v>0.005416735100837084</v>
+        <v>0.005416735100837085</v>
       </c>
       <c r="V16" t="n">
         <v>0.007611885369904682</v>
@@ -4021,25 +4021,25 @@
         <v>0.007203536429031572</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.00893869610602115</v>
+        <v>0.008938696106021153</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.009146993071343677</v>
+        <v>0.009146993071343678</v>
       </c>
       <c r="AA16" t="n">
         <v>0.008968994337012584</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.005422962468700086</v>
+        <v>0.005422962468700085</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.006224276987326405</v>
+        <v>0.006224276987326404</v>
       </c>
       <c r="AD16" t="n">
         <v>0.007084959998804936</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.008734823645602926</v>
+        <v>0.008734823645602924</v>
       </c>
       <c r="AF16" t="n">
         <v>0.006023085120096326</v>
@@ -4051,7 +4051,7 @@
         <v>0.003291075379759835</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.005622767331508697</v>
+        <v>0.005622767331508696</v>
       </c>
       <c r="AJ16" t="n">
         <v>0.005624115577661517</v>
@@ -4063,10 +4063,10 @@
         <v>0.006283614619449401</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.005694958801448964</v>
+        <v>0.005694958801448963</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.006453204476343259</v>
+        <v>0.006453204476343261</v>
       </c>
       <c r="AO16" t="n">
         <v>0.005759135321769804</v>
@@ -4075,7 +4075,7 @@
         <v>0.00640020983916839</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.005656731966255236</v>
+        <v>0.005656731966255238</v>
       </c>
       <c r="AR16" t="n">
         <v>0.006344586382157897</v>
@@ -4084,7 +4084,7 @@
         <v>0.007092283504571139</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.005541470214676141</v>
+        <v>0.005541470214676142</v>
       </c>
       <c r="AU16" t="n">
         <v>0.00581319971224802</v>
@@ -4147,7 +4147,7 @@
         <v>0.012923685294614</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.008981272065838</v>
+        <v>0.008981272065838002</v>
       </c>
       <c r="BP16" t="n">
         <v>0.01509962325085998</v>
@@ -4193,13 +4193,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008159739594521924</v>
+        <v>0.0008159739594521925</v>
       </c>
       <c r="D17" t="n">
         <v>0.0008634171827324289</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001510176025986872</v>
+        <v>0.001510176025986871</v>
       </c>
       <c r="F17" t="n">
         <v>0.001346944083880183</v>
@@ -4211,13 +4211,13 @@
         <v>0.004868841633299267</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005029862057562127</v>
+        <v>0.005029862057562129</v>
       </c>
       <c r="J17" t="n">
         <v>0.00198585124022714</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002299335444733257</v>
+        <v>0.002299335444733258</v>
       </c>
       <c r="L17" t="n">
         <v>0.001609632062591708</v>
@@ -4226,7 +4226,7 @@
         <v>0.004645613469944895</v>
       </c>
       <c r="N17" t="n">
-        <v>0.005578596670677017</v>
+        <v>0.005578596670677016</v>
       </c>
       <c r="O17" t="n">
         <v>0.004101773396949581</v>
@@ -4247,7 +4247,7 @@
         <v>0.006326666646888125</v>
       </c>
       <c r="U17" t="n">
-        <v>0.007661562401461951</v>
+        <v>0.00766156240146195</v>
       </c>
       <c r="V17" t="n">
         <v>0.007586346370382098</v>
@@ -4256,13 +4256,13 @@
         <v>0.007123166912644055</v>
       </c>
       <c r="X17" t="n">
-        <v>0.007111428002245543</v>
+        <v>0.007111428002245542</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.005926124171595333</v>
+        <v>0.005926124171595334</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.005612990712043483</v>
+        <v>0.005612990712043481</v>
       </c>
       <c r="AA17" t="n">
         <v>0.007157702640699005</v>
@@ -4292,13 +4292,13 @@
         <v>0.008887229845363756</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.009070580538792434</v>
+        <v>0.009070580538792438</v>
       </c>
       <c r="AK17" t="n">
         <v>0.00234256046621462</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.002389897295855254</v>
+        <v>0.002389897295855255</v>
       </c>
       <c r="AM17" t="n">
         <v>0.002160865971431755</v>
@@ -4307,22 +4307,22 @@
         <v>0.01056114244917232</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.009796613677345089</v>
+        <v>0.009796613677345087</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.01062433590079605</v>
+        <v>0.01062433590079606</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.002014962215701793</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.003183303781061957</v>
+        <v>0.003183303781061956</v>
       </c>
       <c r="AS17" t="n">
         <v>0.001363905449632131</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.004988485999488719</v>
+        <v>0.004988485999488721</v>
       </c>
       <c r="AU17" t="n">
         <v>0.006018855337782866</v>
@@ -4334,16 +4334,16 @@
         <v>0.001220480129089584</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0007371045464355394</v>
+        <v>0.0007371045464355392</v>
       </c>
       <c r="AY17" t="n">
         <v>0.0005177653413473382</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0007108715591008039</v>
+        <v>0.000710871559100804</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0006227901185917689</v>
+        <v>0.0006227901185917688</v>
       </c>
       <c r="BB17" t="n">
         <v>0.0009791253014351526</v>
@@ -4355,7 +4355,7 @@
         <v>0.01128635018459437</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.004470396099516055</v>
+        <v>0.004470396099516054</v>
       </c>
       <c r="BF17" t="n">
         <v>0.0002176435358098873</v>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00389974950425464</v>
+        <v>0.003899749504254641</v>
       </c>
       <c r="D19" t="n">
         <v>0.002337438432466823</v>
@@ -4733,7 +4733,7 @@
         <v>0.003602868936733618</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.003922596157999895</v>
+        <v>0.003922596157999896</v>
       </c>
       <c r="Z19" t="n">
         <v>0.004067111040977135</v>
@@ -4745,7 +4745,7 @@
         <v>0.003702272872665472</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.004375406429050402</v>
+        <v>0.004375406429050403</v>
       </c>
       <c r="AD19" t="n">
         <v>0.00487402524061248</v>
@@ -4787,7 +4787,7 @@
         <v>0.003047425970347553</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.002132792450222453</v>
+        <v>0.002132792450222454</v>
       </c>
       <c r="AR19" t="n">
         <v>0.003217690965632633</v>
@@ -4856,13 +4856,13 @@
         <v>0.00142917498414</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.0008474442649570002</v>
+        <v>0.0008474442649570001</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.00066217543239</v>
+        <v>0.0006621754323900001</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.006947340629672557</v>
+        <v>0.006947340629672556</v>
       </c>
       <c r="BQ19" t="n">
         <v>0.005837088053100736</v>
@@ -4914,10 +4914,10 @@
         <v>0.03579470333287686</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02750835969606835</v>
+        <v>0.02750835969606834</v>
       </c>
       <c r="G20" t="n">
-        <v>0.009592529616299212</v>
+        <v>0.00959252961629921</v>
       </c>
       <c r="H20" t="n">
         <v>0.008196138357415799</v>
@@ -4938,7 +4938,7 @@
         <v>0.008344910767565366</v>
       </c>
       <c r="N20" t="n">
-        <v>0.009052359334029663</v>
+        <v>0.009052359334029664</v>
       </c>
       <c r="O20" t="n">
         <v>0.01143643912669375</v>
@@ -5040,7 +5040,7 @@
         <v>0.0182214903840155</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.0209498634893285</v>
+        <v>0.02094986348932849</v>
       </c>
       <c r="AW20" t="n">
         <v>0.008208228949104274</v>
@@ -5049,10 +5049,10 @@
         <v>0.06610325335706266</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.03843695614588642</v>
+        <v>0.03843695614588643</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.08662798091984827</v>
+        <v>0.08662798091984829</v>
       </c>
       <c r="BA20" t="n">
         <v>0.06719698283182396</v>
@@ -5100,7 +5100,7 @@
         <v>0.00371669683987</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.005957948645162398</v>
+        <v>0.005957948645162399</v>
       </c>
       <c r="BQ20" t="n">
         <v>0.004017432388160269</v>
@@ -5462,13 +5462,13 @@
         <v>0.320844356500576</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2154134196059691</v>
+        <v>0.215413419605969</v>
       </c>
       <c r="E23" t="n">
         <v>0.1172059667990647</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1240586287985128</v>
+        <v>0.1240586287985129</v>
       </c>
       <c r="G23" t="n">
         <v>0.08033604112801793</v>
@@ -5477,7 +5477,7 @@
         <v>0.06447305360520757</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0564346993908549</v>
+        <v>0.05643469939085491</v>
       </c>
       <c r="J23" t="n">
         <v>0.06833077096710122</v>
@@ -5489,7 +5489,7 @@
         <v>0.06230820651610022</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0465709245766762</v>
+        <v>0.04657092457667621</v>
       </c>
       <c r="N23" t="n">
         <v>0.04459532642804678</v>
@@ -5498,22 +5498,22 @@
         <v>0.1129252539909291</v>
       </c>
       <c r="P23" t="n">
-        <v>0.08759610263059395</v>
+        <v>0.08759610263059397</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.07362879711331709</v>
+        <v>0.0736287971133171</v>
       </c>
       <c r="R23" t="n">
-        <v>0.06978160240857775</v>
+        <v>0.06978160240857774</v>
       </c>
       <c r="S23" t="n">
         <v>0.06042675313456905</v>
       </c>
       <c r="T23" t="n">
-        <v>0.06686733958958141</v>
+        <v>0.0668673395895814</v>
       </c>
       <c r="U23" t="n">
-        <v>0.05977704310946918</v>
+        <v>0.05977704310946919</v>
       </c>
       <c r="V23" t="n">
         <v>0.109385414784206</v>
@@ -5525,7 +5525,7 @@
         <v>0.1070315867905702</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.141191859177361</v>
+        <v>0.1411918591773611</v>
       </c>
       <c r="Z23" t="n">
         <v>0.182078861526926</v>
@@ -5534,7 +5534,7 @@
         <v>0.1515535902351397</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.06144006758554661</v>
+        <v>0.06144006758554659</v>
       </c>
       <c r="AC23" t="n">
         <v>0.08069804681241308</v>
@@ -5543,13 +5543,13 @@
         <v>0.0941132247783687</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.09860842451415357</v>
+        <v>0.09860842451415358</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.08630253927132216</v>
+        <v>0.08630253927132214</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1035806789266617</v>
+        <v>0.1035806789266618</v>
       </c>
       <c r="AH23" t="n">
         <v>0.0741275078855847</v>
@@ -5558,10 +5558,10 @@
         <v>0.1120454278327464</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.09292284668962843</v>
+        <v>0.09292284668962845</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.07270384745513231</v>
+        <v>0.07270384745513229</v>
       </c>
       <c r="AL23" t="n">
         <v>0.0779724888470256</v>
@@ -5579,7 +5579,7 @@
         <v>0.105704253334346</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.07033708006300014</v>
+        <v>0.07033708006300016</v>
       </c>
       <c r="AR23" t="n">
         <v>0.08142261483391736</v>
@@ -5588,16 +5588,16 @@
         <v>0.1069155275501203</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.1909554274358722</v>
+        <v>0.1909554274358723</v>
       </c>
       <c r="AU23" t="n">
         <v>0.1460380544540667</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.1635543759349876</v>
+        <v>0.1635543759349877</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.1814993039898483</v>
+        <v>0.1814993039898484</v>
       </c>
       <c r="AX23" t="n">
         <v>0.0324367975315425</v>
@@ -5612,7 +5612,7 @@
         <v>0.05844035338240644</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.2160020461209927</v>
+        <v>0.2160020461209928</v>
       </c>
       <c r="BC23" t="n">
         <v>0.157975497267448</v>
@@ -5621,13 +5621,13 @@
         <v>0.2525535527142941</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.1264089654789043</v>
+        <v>0.1264089654789042</v>
       </c>
       <c r="BF23" t="n">
         <v>0.1109962392514576</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.1070317337930671</v>
+        <v>0.1070317337930672</v>
       </c>
       <c r="BH23" t="n">
         <v>0.119752938236844</v>
@@ -5639,19 +5639,19 @@
         <v>0.1237277784287432</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.05559217365756217</v>
+        <v>0.05559217365756215</v>
       </c>
       <c r="BL23" t="n">
         <v>0.09400224249534254</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.047893945336409</v>
+        <v>0.04789394533640901</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.037330012613686</v>
+        <v>0.03733001261368599</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.05254259205315603</v>
+        <v>0.05254259205315601</v>
       </c>
       <c r="BP23" t="n">
         <v>0.1103461544049839</v>
@@ -5672,7 +5672,7 @@
         <v>0.1232200346835067</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.07333342537727428</v>
+        <v>0.07333342537727426</v>
       </c>
       <c r="BW23" t="n">
         <v>0.07130783250283872</v>
@@ -5681,7 +5681,7 @@
         <v>0.07185162988965116</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.07219776544156691</v>
+        <v>0.07219776544156689</v>
       </c>
       <c r="BZ23" t="n">
         <v>0.06478227947930569</v>
@@ -5980,16 +5980,16 @@
         <v>0.0005974609550989999</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.0003861431920079999</v>
+        <v>0.000386143192008</v>
       </c>
       <c r="BO25" t="n">
         <v>0.001428537332036</v>
       </c>
       <c r="BP25" t="n">
-        <v>0.0005168459556694665</v>
+        <v>0.0005168459556694666</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0.0002135653240629081</v>
+        <v>0.0002135653240629082</v>
       </c>
       <c r="BR25" t="n">
         <v>0.0006827299461645387</v>
@@ -6512,7 +6512,7 @@
         <v>0.0001424154180331318</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0003973274949688903</v>
+        <v>0.0003973274949688904</v>
       </c>
       <c r="G28" t="n">
         <v>7.635726773272987e-05</v>
@@ -6524,7 +6524,7 @@
         <v>7.373327542965274e-05</v>
       </c>
       <c r="J28" t="n">
-        <v>8.881127008107037e-05</v>
+        <v>8.881127008107038e-05</v>
       </c>
       <c r="K28" t="n">
         <v>0.0001046082256921506</v>
@@ -6536,7 +6536,7 @@
         <v>5.618634889925427e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>6.414504086288747e-05</v>
+        <v>6.414504086288746e-05</v>
       </c>
       <c r="O28" t="n">
         <v>5.633089106026419e-05</v>
@@ -6557,7 +6557,7 @@
         <v>7.125894810714698e-05</v>
       </c>
       <c r="U28" t="n">
-        <v>7.634154197983184e-05</v>
+        <v>7.634154197983183e-05</v>
       </c>
       <c r="V28" t="n">
         <v>9.859975614865237e-05</v>
@@ -6593,13 +6593,13 @@
         <v>6.872431815464377e-05</v>
       </c>
       <c r="AG28" t="n">
-        <v>8.404978525415752e-05</v>
+        <v>8.404978525415754e-05</v>
       </c>
       <c r="AH28" t="n">
         <v>4.954890279870984e-05</v>
       </c>
       <c r="AI28" t="n">
-        <v>8.890916871926854e-05</v>
+        <v>8.890916871926852e-05</v>
       </c>
       <c r="AJ28" t="n">
         <v>8.966587227678817e-05</v>
@@ -6680,7 +6680,7 @@
         <v>7.31432357530239e-05</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.0009805322026335999</v>
+        <v>0.0009805322026336001</v>
       </c>
       <c r="BK28" t="n">
         <v>0.0003385776726410014</v>
@@ -6729,10 +6729,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.05161323425854674</v>
+        <v>0.05161323425854673</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1937396268530673</v>
+        <v>0.1937396268530672</v>
       </c>
       <c r="E29" t="n">
         <v>0.1091358629200857</v>
@@ -6747,13 +6747,13 @@
         <v>0.02255584114044652</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02216740808002086</v>
+        <v>0.02216740808002087</v>
       </c>
       <c r="J29" t="n">
         <v>0.02140377716829229</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02194534480352572</v>
+        <v>0.02194534480352573</v>
       </c>
       <c r="L29" t="n">
         <v>0.02016602863400447</v>
@@ -6762,40 +6762,40 @@
         <v>0.020717999077648</v>
       </c>
       <c r="N29" t="n">
-        <v>0.02415465741828729</v>
+        <v>0.02415465741828728</v>
       </c>
       <c r="O29" t="n">
-        <v>0.01781502684277084</v>
+        <v>0.01781502684277085</v>
       </c>
       <c r="P29" t="n">
         <v>0.02378676560736187</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.02093822293370288</v>
+        <v>0.02093822293370289</v>
       </c>
       <c r="R29" t="n">
         <v>0.02396754530429277</v>
       </c>
       <c r="S29" t="n">
-        <v>0.02540862232349336</v>
+        <v>0.02540862232349337</v>
       </c>
       <c r="T29" t="n">
-        <v>0.02397932275204743</v>
+        <v>0.02397932275204744</v>
       </c>
       <c r="U29" t="n">
         <v>0.02515250984944163</v>
       </c>
       <c r="V29" t="n">
-        <v>0.03345971988071913</v>
+        <v>0.03345971988071912</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03438158862292283</v>
+        <v>0.03438158862292282</v>
       </c>
       <c r="X29" t="n">
         <v>0.03425123722408251</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.0372706662398604</v>
+        <v>0.03727066623986038</v>
       </c>
       <c r="Z29" t="n">
         <v>0.03240772667304067</v>
@@ -6807,10 +6807,10 @@
         <v>0.03448207072675304</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.04320495019843536</v>
+        <v>0.04320495019843538</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.04162821690534637</v>
+        <v>0.04162821690534636</v>
       </c>
       <c r="AE29" t="n">
         <v>0.0243468380180186</v>
@@ -6822,13 +6822,13 @@
         <v>0.01661928393980317</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.01258984338776577</v>
+        <v>0.01258984338776578</v>
       </c>
       <c r="AI29" t="n">
         <v>0.02239471283984712</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.02440473527492702</v>
+        <v>0.02440473527492701</v>
       </c>
       <c r="AK29" t="n">
         <v>0.02783720424625108</v>
@@ -6843,13 +6843,13 @@
         <v>0.03293595070665115</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.02967388856815083</v>
+        <v>0.02967388856815082</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.0309028841759808</v>
+        <v>0.03090288417598081</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.0161257951332207</v>
+        <v>0.01612579513322069</v>
       </c>
       <c r="AR29" t="n">
         <v>0.02206534539118389</v>
@@ -6858,19 +6858,19 @@
         <v>0.01526390963082038</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.02683934551725007</v>
+        <v>0.02683934551725006</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.03298613030227198</v>
+        <v>0.03298613030227199</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.03240068340601739</v>
+        <v>0.0324006834060174</v>
       </c>
       <c r="AW29" t="n">
         <v>0.03063182322043375</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.03267220736981639</v>
+        <v>0.0326722073698164</v>
       </c>
       <c r="AY29" t="n">
         <v>0.02791484395844429</v>
@@ -6882,31 +6882,31 @@
         <v>0.02721354355892404</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.03653610696846721</v>
+        <v>0.0365361069684672</v>
       </c>
       <c r="BC29" t="n">
-        <v>0.02324129773551014</v>
+        <v>0.02324129773551015</v>
       </c>
       <c r="BD29" t="n">
-        <v>0.04092063236908518</v>
+        <v>0.04092063236908517</v>
       </c>
       <c r="BE29" t="n">
         <v>0.01868147422090424</v>
       </c>
       <c r="BF29" t="n">
-        <v>0.03801720547165045</v>
+        <v>0.03801720547165044</v>
       </c>
       <c r="BG29" t="n">
         <v>0.03409570703078039</v>
       </c>
       <c r="BH29" t="n">
-        <v>0.03680645187094169</v>
+        <v>0.03680645187094168</v>
       </c>
       <c r="BI29" t="n">
         <v>0.04349267920170254</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.04801036281513624</v>
+        <v>0.04801036281513622</v>
       </c>
       <c r="BK29" t="n">
         <v>0.01538440339292617</v>
@@ -6924,10 +6924,10 @@
         <v>0.010499729625048</v>
       </c>
       <c r="BP29" t="n">
-        <v>0.04420767907804683</v>
+        <v>0.04420767907804681</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0.03123757337228382</v>
+        <v>0.03123757337228381</v>
       </c>
       <c r="BR29" t="n">
         <v>0.01637024842820569</v>
@@ -6942,16 +6942,16 @@
         <v>0.02299219260713465</v>
       </c>
       <c r="BV29" t="n">
-        <v>0.01788163400250088</v>
+        <v>0.01788163400250087</v>
       </c>
       <c r="BW29" t="n">
-        <v>0.02061711381252878</v>
+        <v>0.02061711381252879</v>
       </c>
       <c r="BX29" t="n">
         <v>0.02161097345913124</v>
       </c>
       <c r="BY29" t="n">
-        <v>0.02152030137081878</v>
+        <v>0.02152030137081877</v>
       </c>
       <c r="BZ29" t="n">
         <v>0.01991878073985019</v>
@@ -7151,10 +7151,10 @@
         <v>0.07818868369134903</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02708367543860904</v>
+        <v>0.02708367543860905</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02483430944492417</v>
+        <v>0.02483430944492418</v>
       </c>
       <c r="I32" t="n">
         <v>0.0287397415751385</v>
@@ -7163,16 +7163,16 @@
         <v>0.04679776255671784</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05566713871239079</v>
+        <v>0.0556671387123908</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04469200901876304</v>
+        <v>0.04469200901876303</v>
       </c>
       <c r="M32" t="n">
-        <v>0.02398989770695373</v>
+        <v>0.02398989770695372</v>
       </c>
       <c r="N32" t="n">
-        <v>0.02663936832914213</v>
+        <v>0.02663936832914214</v>
       </c>
       <c r="O32" t="n">
         <v>0.031472793471658</v>
@@ -7181,13 +7181,13 @@
         <v>0.03284324049720026</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.02834317017862426</v>
+        <v>0.02834317017862427</v>
       </c>
       <c r="R32" t="n">
         <v>0.02853228207235741</v>
       </c>
       <c r="S32" t="n">
-        <v>0.03160296600545336</v>
+        <v>0.03160296600545337</v>
       </c>
       <c r="T32" t="n">
         <v>0.0324982281224343</v>
@@ -7196,16 +7196,16 @@
         <v>0.03244257526840126</v>
       </c>
       <c r="V32" t="n">
-        <v>0.05292336557912806</v>
+        <v>0.05292336557912808</v>
       </c>
       <c r="W32" t="n">
-        <v>0.05344823099832626</v>
+        <v>0.05344823099832625</v>
       </c>
       <c r="X32" t="n">
-        <v>0.05058714268957816</v>
+        <v>0.05058714268957815</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.06303303006753991</v>
+        <v>0.06303303006753989</v>
       </c>
       <c r="Z32" t="n">
         <v>0.07193984764387817</v>
@@ -7214,7 +7214,7 @@
         <v>0.0647765568757276</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.09467621544861475</v>
+        <v>0.09467621544861478</v>
       </c>
       <c r="AC32" t="n">
         <v>0.1138394648529392</v>
@@ -7223,7 +7223,7 @@
         <v>0.122297606979586</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.07469786113848792</v>
+        <v>0.07469786113848791</v>
       </c>
       <c r="AF32" t="n">
         <v>0.03466042981410483</v>
@@ -7232,22 +7232,22 @@
         <v>0.04389141545237906</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.02383243706744505</v>
+        <v>0.02383243706744504</v>
       </c>
       <c r="AI32" t="n">
         <v>0.04244746430668317</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.04362588052895775</v>
+        <v>0.04362588052895774</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.05180939639024791</v>
+        <v>0.0518093963902479</v>
       </c>
       <c r="AL32" t="n">
         <v>0.06855816054235099</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.05311053098252221</v>
+        <v>0.05311053098252219</v>
       </c>
       <c r="AN32" t="n">
         <v>0.05462487752569137</v>
@@ -7256,22 +7256,22 @@
         <v>0.04594706306382935</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.05045294725558195</v>
+        <v>0.05045294725558197</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.03865157369949904</v>
+        <v>0.03865157369949906</v>
       </c>
       <c r="AR32" t="n">
         <v>0.0556336887579765</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.03590754810357977</v>
+        <v>0.03590754810357976</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.05747159825095003</v>
+        <v>0.05747159825095004</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.05453921005105521</v>
+        <v>0.0545392100510552</v>
       </c>
       <c r="AV32" t="n">
         <v>0.05210259347751038</v>
@@ -7280,13 +7280,13 @@
         <v>0.08833676256473276</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.05356196039346009</v>
+        <v>0.05356196039346011</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.03899530468943128</v>
+        <v>0.03899530468943127</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.05403604247833305</v>
+        <v>0.05403604247833304</v>
       </c>
       <c r="BA32" t="n">
         <v>0.0416655884621779</v>
@@ -7301,7 +7301,7 @@
         <v>0.1187487819921036</v>
       </c>
       <c r="BE32" t="n">
-        <v>0.07596562812882994</v>
+        <v>0.07596562812882993</v>
       </c>
       <c r="BF32" t="n">
         <v>0.1103215622073923</v>
@@ -7313,16 +7313,16 @@
         <v>0.1133944924508619</v>
       </c>
       <c r="BI32" t="n">
-        <v>0.1122283732574564</v>
+        <v>0.1122283732574563</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.09167672850950241</v>
+        <v>0.0916767285095024</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.04708331886506311</v>
+        <v>0.0470833188650631</v>
       </c>
       <c r="BL32" t="n">
-        <v>0.04561000418221187</v>
+        <v>0.04561000418221186</v>
       </c>
       <c r="BM32" t="n">
         <v>0.04989081382694399</v>
@@ -7334,22 +7334,22 @@
         <v>0.03563583985321801</v>
       </c>
       <c r="BP32" t="n">
-        <v>0.04706036281811712</v>
+        <v>0.04706036281811713</v>
       </c>
       <c r="BQ32" t="n">
         <v>0.03711303484457459</v>
       </c>
       <c r="BR32" t="n">
-        <v>0.04433766819588677</v>
+        <v>0.04433766819588676</v>
       </c>
       <c r="BS32" t="n">
-        <v>0.04855434551309767</v>
+        <v>0.04855434551309768</v>
       </c>
       <c r="BT32" t="n">
         <v>0.06267701914681131</v>
       </c>
       <c r="BU32" t="n">
-        <v>0.07737756939173787</v>
+        <v>0.0773775693917379</v>
       </c>
       <c r="BV32" t="n">
         <v>0.06478428738358505</v>
@@ -7364,7 +7364,7 @@
         <v>0.09064716467558576</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0.08169141273813736</v>
+        <v>0.08169141273813735</v>
       </c>
     </row>
     <row r="33">
@@ -7377,28 +7377,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.04089209820732146</v>
+        <v>0.04089209820732145</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04869644744851479</v>
+        <v>0.04869644744851478</v>
       </c>
       <c r="E33" t="n">
-        <v>0.04284633029455417</v>
+        <v>0.04284633029455416</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04293598422744917</v>
+        <v>0.04293598422744919</v>
       </c>
       <c r="G33" t="n">
         <v>0.04243411313614217</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03702500226432194</v>
+        <v>0.03702500226432195</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04558721617390476</v>
+        <v>0.04558721617390475</v>
       </c>
       <c r="J33" t="n">
-        <v>0.06084112248586104</v>
+        <v>0.06084112248586105</v>
       </c>
       <c r="K33" t="n">
         <v>0.07057969914834493</v>
@@ -7413,49 +7413,49 @@
         <v>0.03779317612174047</v>
       </c>
       <c r="O33" t="n">
-        <v>0.04020759417432643</v>
+        <v>0.04020759417432644</v>
       </c>
       <c r="P33" t="n">
         <v>0.04659274640204927</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04496333527704749</v>
+        <v>0.04496333527704748</v>
       </c>
       <c r="R33" t="n">
         <v>0.04134974583883249</v>
       </c>
       <c r="S33" t="n">
-        <v>0.03538658865396831</v>
+        <v>0.03538658865396829</v>
       </c>
       <c r="T33" t="n">
         <v>0.03728105972073707</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04433349865891824</v>
+        <v>0.04433349865891823</v>
       </c>
       <c r="V33" t="n">
         <v>0.05858704368361432</v>
       </c>
       <c r="W33" t="n">
-        <v>0.06063091485073744</v>
+        <v>0.06063091485073745</v>
       </c>
       <c r="X33" t="n">
         <v>0.05248980962080967</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.06081124025759335</v>
+        <v>0.06081124025759334</v>
       </c>
       <c r="Z33" t="n">
         <v>0.05874705741032876</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.06018735986350698</v>
+        <v>0.06018735986350697</v>
       </c>
       <c r="AB33" t="n">
         <v>0.1014547865175048</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.1165242403119343</v>
+        <v>0.1165242403119344</v>
       </c>
       <c r="AD33" t="n">
         <v>0.1214756625213475</v>
@@ -7467,28 +7467,28 @@
         <v>0.04226519334357057</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.06031999047012187</v>
+        <v>0.06031999047012186</v>
       </c>
       <c r="AH33" t="n">
         <v>0.0288317979652771</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.04671167800472804</v>
+        <v>0.04671167800472806</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.04874171946891495</v>
+        <v>0.04874171946891494</v>
       </c>
       <c r="AK33" t="n">
         <v>0.05688212275661492</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.08205635108287228</v>
+        <v>0.08205635108287231</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.05915471133627643</v>
+        <v>0.05915471133627642</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.07104464472032312</v>
+        <v>0.07104464472032311</v>
       </c>
       <c r="AO33" t="n">
         <v>0.0555752390623201</v>
@@ -7497,7 +7497,7 @@
         <v>0.05030053932858595</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.04181736931071485</v>
+        <v>0.04181736931071484</v>
       </c>
       <c r="AR33" t="n">
         <v>0.05524950659870086</v>
@@ -7506,13 +7506,13 @@
         <v>0.04394923845949144</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.06021951537336686</v>
+        <v>0.06021951537336685</v>
       </c>
       <c r="AU33" t="n">
         <v>0.07346421660992236</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.06582061040767601</v>
+        <v>0.06582061040767602</v>
       </c>
       <c r="AW33" t="n">
         <v>0.02896148326506329</v>
@@ -7524,10 +7524,10 @@
         <v>0.06252495392090344</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.08284761505678424</v>
+        <v>0.08284761505678423</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.08202339666101434</v>
+        <v>0.08202339666101433</v>
       </c>
       <c r="BB33" t="n">
         <v>0.09451494580100035</v>
@@ -7536,7 +7536,7 @@
         <v>0.06043341082748839</v>
       </c>
       <c r="BD33" t="n">
-        <v>0.09736226080242619</v>
+        <v>0.0973622608024262</v>
       </c>
       <c r="BE33" t="n">
         <v>0.04996964347830896</v>
@@ -7545,13 +7545,13 @@
         <v>0.0515362867302027</v>
       </c>
       <c r="BG33" t="n">
-        <v>0.05007890426394854</v>
+        <v>0.05007890426394855</v>
       </c>
       <c r="BH33" t="n">
         <v>0.05632238108095818</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.05189771094910962</v>
+        <v>0.05189771094910963</v>
       </c>
       <c r="BJ33" t="n">
         <v>0.0401982399864888</v>
@@ -7560,16 +7560,16 @@
         <v>0.02985399441560724</v>
       </c>
       <c r="BL33" t="n">
-        <v>0.03145374251808076</v>
+        <v>0.03145374251808077</v>
       </c>
       <c r="BM33" t="n">
-        <v>0.04303102293794</v>
+        <v>0.04303102293794002</v>
       </c>
       <c r="BN33" t="n">
         <v>0.031790479109665</v>
       </c>
       <c r="BO33" t="n">
-        <v>0.044955349275633</v>
+        <v>0.04495534927563299</v>
       </c>
       <c r="BP33" t="n">
         <v>0.0222370933549469</v>
@@ -7578,22 +7578,22 @@
         <v>0.01368654628570525</v>
       </c>
       <c r="BR33" t="n">
-        <v>0.05784118532753057</v>
+        <v>0.05784118532753058</v>
       </c>
       <c r="BS33" t="n">
-        <v>0.06142019140693977</v>
+        <v>0.06142019140693978</v>
       </c>
       <c r="BT33" t="n">
-        <v>0.05581740568900411</v>
+        <v>0.05581740568900413</v>
       </c>
       <c r="BU33" t="n">
-        <v>0.05604399904367947</v>
+        <v>0.05604399904367949</v>
       </c>
       <c r="BV33" t="n">
-        <v>0.03784011924159795</v>
+        <v>0.03784011924159796</v>
       </c>
       <c r="BW33" t="n">
-        <v>0.04224395451994687</v>
+        <v>0.04224395451994686</v>
       </c>
       <c r="BX33" t="n">
         <v>0.04607442704742617</v>
@@ -7971,22 +7971,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0008708763748411175</v>
+        <v>0.0008708763748411174</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0006426361269979653</v>
+        <v>0.0006426361269979655</v>
       </c>
       <c r="E36" t="n">
         <v>0.0006883312668076958</v>
       </c>
       <c r="F36" t="n">
-        <v>0.001869818550166176</v>
+        <v>0.001869818550166177</v>
       </c>
       <c r="G36" t="n">
         <v>0.0001106098665233601</v>
       </c>
       <c r="H36" t="n">
-        <v>9.254065795979336e-05</v>
+        <v>9.254065795979337e-05</v>
       </c>
       <c r="I36" t="n">
         <v>0.0001251323354108479</v>
@@ -8031,7 +8031,7 @@
         <v>0.0002206645068579077</v>
       </c>
       <c r="W36" t="n">
-        <v>0.0002186046756592321</v>
+        <v>0.0002186046756592322</v>
       </c>
       <c r="X36" t="n">
         <v>0.0002433823741195338</v>
@@ -8043,31 +8043,31 @@
         <v>0.0002988978181169974</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.0002779223686611942</v>
+        <v>0.0002779223686611941</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.0003052112361814046</v>
+        <v>0.0003052112361814047</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.0003683190789044037</v>
+        <v>0.0003683190789044036</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.0004446422269929933</v>
+        <v>0.0004446422269929932</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0003296000848543017</v>
+        <v>0.0003296000848543016</v>
       </c>
       <c r="AF36" t="n">
         <v>0.0001440898028391932</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.0001732108415616983</v>
+        <v>0.0001732108415616984</v>
       </c>
       <c r="AH36" t="n">
-        <v>9.765879293583726e-05</v>
+        <v>9.765879293583725e-05</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.0001732311734174351</v>
+        <v>0.0001732311734174352</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.0001771685696752035</v>
@@ -8082,10 +8082,10 @@
         <v>0.0002211071104535168</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.0002105813372908991</v>
+        <v>0.0002105813372908992</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.0001911422558714876</v>
+        <v>0.0001911422558714877</v>
       </c>
       <c r="AP36" t="n">
         <v>0.0002089516211224321</v>
@@ -8100,13 +8100,13 @@
         <v>0.0001508589053250189</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.0002056242648457089</v>
+        <v>0.000205624264845709</v>
       </c>
       <c r="AU36" t="n">
         <v>0.0002293602579536671</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.0002111462161482677</v>
+        <v>0.0002111462161482678</v>
       </c>
       <c r="AW36" t="n">
         <v>0.001015356009300522</v>
@@ -8151,7 +8151,7 @@
         <v>0.00471302696141008</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.00448709439092937</v>
+        <v>0.004487094390929372</v>
       </c>
       <c r="BL36" t="n">
         <v>0.001057737081655551</v>
@@ -8166,7 +8166,7 @@
         <v>0.0008602351945660001</v>
       </c>
       <c r="BP36" t="n">
-        <v>0.002963040577218874</v>
+        <v>0.002963040577218875</v>
       </c>
       <c r="BQ36" t="n">
         <v>0.002494693142525696</v>
@@ -8212,16 +8212,16 @@
         <v>0.02934521426469704</v>
       </c>
       <c r="D37" t="n">
-        <v>0.04343818644612287</v>
+        <v>0.04343818644612284</v>
       </c>
       <c r="E37" t="n">
         <v>0.07297885831143226</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02635010312095915</v>
+        <v>0.02635010312095916</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02047196481739983</v>
+        <v>0.02047196481739982</v>
       </c>
       <c r="H37" t="n">
         <v>0.01683919621050627</v>
@@ -8233,10 +8233,10 @@
         <v>0.0328644308579968</v>
       </c>
       <c r="K37" t="n">
-        <v>0.03726538659635743</v>
+        <v>0.03726538659635744</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02949412060044297</v>
+        <v>0.02949412060044298</v>
       </c>
       <c r="M37" t="n">
         <v>0.01559721797243444</v>
@@ -8245,34 +8245,34 @@
         <v>0.0162822100584973</v>
       </c>
       <c r="O37" t="n">
-        <v>0.02622883664725227</v>
+        <v>0.02622883664725226</v>
       </c>
       <c r="P37" t="n">
         <v>0.0278793476619497</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.02476757353196357</v>
+        <v>0.02476757353196356</v>
       </c>
       <c r="R37" t="n">
         <v>0.02519416158484606</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02636640082250943</v>
+        <v>0.02636640082250944</v>
       </c>
       <c r="T37" t="n">
         <v>0.02560750285425682</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02516793213286804</v>
+        <v>0.02516793213286805</v>
       </c>
       <c r="V37" t="n">
-        <v>0.03239108414581089</v>
+        <v>0.03239108414581088</v>
       </c>
       <c r="W37" t="n">
-        <v>0.03409211359631</v>
+        <v>0.03409211359631001</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02931941689248586</v>
+        <v>0.02931941689248587</v>
       </c>
       <c r="Y37" t="n">
         <v>0.03398600246477875</v>
@@ -8281,28 +8281,28 @@
         <v>0.03074976640514909</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.03585340637327934</v>
+        <v>0.03585340637327932</v>
       </c>
       <c r="AB37" t="n">
         <v>0.04039701160416453</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.05847134603605858</v>
+        <v>0.05847134603605857</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.05704842507347341</v>
+        <v>0.05704842507347339</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.04000306438492565</v>
+        <v>0.04000306438492566</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.02211591439329737</v>
+        <v>0.02211591439329738</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.02686116755048146</v>
+        <v>0.02686116755048145</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.0211727293195388</v>
+        <v>0.02117272931953879</v>
       </c>
       <c r="AI37" t="n">
         <v>0.03294369766672366</v>
@@ -8311,16 +8311,16 @@
         <v>0.03274660982749929</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.0449642589455135</v>
+        <v>0.04496425894551351</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.05403739661488217</v>
+        <v>0.05403739661488216</v>
       </c>
       <c r="AM37" t="n">
         <v>0.04786718509221028</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.03679094726826666</v>
+        <v>0.03679094726826665</v>
       </c>
       <c r="AO37" t="n">
         <v>0.03342043480887056</v>
@@ -8338,13 +8338,13 @@
         <v>0.02412704330925889</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.04779499643609249</v>
+        <v>0.04779499643609251</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.04124543242418705</v>
+        <v>0.04124543242418706</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.0418845579523915</v>
+        <v>0.04188455795239152</v>
       </c>
       <c r="AW37" t="n">
         <v>0.07367890065650859</v>
@@ -8356,40 +8356,40 @@
         <v>0.02687748456241815</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.03481863917339705</v>
+        <v>0.03481863917339706</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.01581704935022682</v>
+        <v>0.01581704935022681</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.09622095526240426</v>
+        <v>0.09622095526240428</v>
       </c>
       <c r="BC37" t="n">
         <v>0.06930708318250663</v>
       </c>
       <c r="BD37" t="n">
-        <v>0.09379006199189097</v>
+        <v>0.09379006199189098</v>
       </c>
       <c r="BE37" t="n">
-        <v>0.04842426997584363</v>
+        <v>0.04842426997584362</v>
       </c>
       <c r="BF37" t="n">
         <v>0.08992084610598554</v>
       </c>
       <c r="BG37" t="n">
-        <v>0.08536591983287185</v>
+        <v>0.08536591983287183</v>
       </c>
       <c r="BH37" t="n">
         <v>0.1032704525868096</v>
       </c>
       <c r="BI37" t="n">
-        <v>0.09606870729184853</v>
+        <v>0.09606870729184852</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.0425119185698856</v>
+        <v>0.04251191856988561</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.02246844458742795</v>
+        <v>0.02246844458742796</v>
       </c>
       <c r="BL37" t="n">
         <v>0.0165730908491464</v>
@@ -8404,37 +8404,37 @@
         <v>0.056057411931915</v>
       </c>
       <c r="BP37" t="n">
-        <v>0.02723644291398003</v>
+        <v>0.02723644291398002</v>
       </c>
       <c r="BQ37" t="n">
         <v>0.01662809308079342</v>
       </c>
       <c r="BR37" t="n">
-        <v>0.04695853858380743</v>
+        <v>0.04695853858380741</v>
       </c>
       <c r="BS37" t="n">
-        <v>0.05351020914787204</v>
+        <v>0.05351020914787205</v>
       </c>
       <c r="BT37" t="n">
-        <v>0.06920118763140928</v>
+        <v>0.06920118763140927</v>
       </c>
       <c r="BU37" t="n">
-        <v>0.08080280687936596</v>
+        <v>0.08080280687936595</v>
       </c>
       <c r="BV37" t="n">
         <v>0.06648571959135273</v>
       </c>
       <c r="BW37" t="n">
-        <v>0.08197961675108624</v>
+        <v>0.08197961675108627</v>
       </c>
       <c r="BX37" t="n">
-        <v>0.09371738611923568</v>
+        <v>0.09371738611923569</v>
       </c>
       <c r="BY37" t="n">
         <v>0.09175604787608491</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0.07093717299439814</v>
+        <v>0.07093717299439817</v>
       </c>
     </row>
     <row r="38">
@@ -8947,7 +8947,7 @@
         <v>0.001086030447019943</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0003246304775855303</v>
+        <v>0.0003246304775855304</v>
       </c>
       <c r="H43" t="n">
         <v>0.0003070454294159379</v>
@@ -8956,10 +8956,10 @@
         <v>0.0003138630477138006</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0008548853813608759</v>
+        <v>0.000854885381360876</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0008830292125006882</v>
+        <v>0.0008830292125006881</v>
       </c>
       <c r="L43" t="n">
         <v>0.0008522387629117746</v>
@@ -8968,7 +8968,7 @@
         <v>0.000315222017287659</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0003430135426206136</v>
+        <v>0.0003430135426206135</v>
       </c>
       <c r="O43" t="n">
         <v>0.0003394245248854531</v>
@@ -8980,7 +8980,7 @@
         <v>0.0003643446644562527</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0004065343051817429</v>
+        <v>0.000406534305181743</v>
       </c>
       <c r="S43" t="n">
         <v>0.0004040290312356395</v>
@@ -9019,7 +9019,7 @@
         <v>0.001359014848965865</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.000856059125495353</v>
+        <v>0.0008560591254953531</v>
       </c>
       <c r="AF43" t="n">
         <v>0.0004945251523247239</v>
@@ -9040,7 +9040,7 @@
         <v>0.0005787094350507029</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.0006938382035583439</v>
+        <v>0.0006938382035583438</v>
       </c>
       <c r="AM43" t="n">
         <v>0.0006518831904764678</v>
@@ -9067,10 +9067,10 @@
         <v>0.0005696189588042548</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.0007277503389309488</v>
+        <v>0.0007277503389309486</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.0005857404319289293</v>
+        <v>0.0005857404319289292</v>
       </c>
       <c r="AW43" t="n">
         <v>0.00141349246934526</v>
@@ -9079,7 +9079,7 @@
         <v>0.0008454862839038287</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.0008558868396113489</v>
+        <v>0.0008558868396113488</v>
       </c>
       <c r="AZ43" t="n">
         <v>0.0003875413742759901</v>
@@ -9094,16 +9094,16 @@
         <v>0.001413849464824968</v>
       </c>
       <c r="BD43" t="n">
-        <v>0.002211244934986091</v>
+        <v>0.002211244934986092</v>
       </c>
       <c r="BE43" t="n">
         <v>0.001180751148836009</v>
       </c>
       <c r="BF43" t="n">
-        <v>0.0009423304235904469</v>
+        <v>0.0009423304235904468</v>
       </c>
       <c r="BG43" t="n">
-        <v>0.0009079313824777999</v>
+        <v>0.0009079313824777998</v>
       </c>
       <c r="BH43" t="n">
         <v>0.001203771918090037</v>
@@ -9121,7 +9121,7 @@
         <v>0.0004770302895941812</v>
       </c>
       <c r="BM43" t="n">
-        <v>0.00066019119141</v>
+        <v>0.0006601911914100001</v>
       </c>
       <c r="BN43" t="n">
         <v>0.0004438039759190001</v>
@@ -9136,7 +9136,7 @@
         <v>0.001533612951909356</v>
       </c>
       <c r="BR43" t="n">
-        <v>0.001129722994709994</v>
+        <v>0.001129722994709995</v>
       </c>
       <c r="BS43" t="n">
         <v>0.001421394006658139</v>
@@ -9157,7 +9157,7 @@
         <v>0.0008783809125692923</v>
       </c>
       <c r="BY43" t="n">
-        <v>0.0007529297692763498</v>
+        <v>0.0007529297692763499</v>
       </c>
       <c r="BZ43" t="n">
         <v>0.0006612427727831727</v>
@@ -9176,10 +9176,10 @@
         <v>0.0006906517668779341</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007345179282229171</v>
+        <v>0.0007345179282229173</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0007286813554939124</v>
+        <v>0.0007286813554939126</v>
       </c>
       <c r="F44" t="n">
         <v>0.002379482114004293</v>
@@ -9194,25 +9194,25 @@
         <v>0.0002519653090286769</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0003538989382279474</v>
+        <v>0.0003538989382279473</v>
       </c>
       <c r="K44" t="n">
         <v>0.0004041036214240926</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0003495284171693682</v>
+        <v>0.0003495284171693681</v>
       </c>
       <c r="M44" t="n">
         <v>0.0002280000290082293</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0002393808770803761</v>
+        <v>0.000239380877080376</v>
       </c>
       <c r="O44" t="n">
         <v>0.0002368320178932056</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0003399769539449599</v>
+        <v>0.0003399769539449598</v>
       </c>
       <c r="Q44" t="n">
         <v>0.0002922773131445313</v>
@@ -9221,37 +9221,37 @@
         <v>0.0003070358410380349</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0003581127573367405</v>
+        <v>0.0003581127573367404</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0003352451191144074</v>
+        <v>0.0003352451191144075</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0003475492910157886</v>
+        <v>0.0003475492910157887</v>
       </c>
       <c r="V44" t="n">
         <v>0.0004919386222872489</v>
       </c>
       <c r="W44" t="n">
-        <v>0.0005157558600707861</v>
+        <v>0.0005157558600707862</v>
       </c>
       <c r="X44" t="n">
-        <v>0.0005167573614099408</v>
+        <v>0.0005167573614099407</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.0005908863926914122</v>
+        <v>0.000590886392691412</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0005942913913028623</v>
+        <v>0.0005942913913028622</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0006267347194173036</v>
+        <v>0.0006267347194173037</v>
       </c>
       <c r="AB44" t="n">
         <v>0.0005890309195216571</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.0007305339073841656</v>
+        <v>0.0007305339073841655</v>
       </c>
       <c r="AD44" t="n">
         <v>0.0007376936958756999</v>
@@ -9260,10 +9260,10 @@
         <v>0.0005726945388758923</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0003229679957901761</v>
+        <v>0.0003229679957901762</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.0003611304658216216</v>
+        <v>0.0003611304658216215</v>
       </c>
       <c r="AH44" t="n">
         <v>0.0002132367680783868</v>
@@ -9278,13 +9278,13 @@
         <v>0.0004480992691228183</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.0005374784804561732</v>
+        <v>0.0005374784804561731</v>
       </c>
       <c r="AM44" t="n">
         <v>0.0004786566148071366</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.0004615607869486244</v>
+        <v>0.0004615607869486243</v>
       </c>
       <c r="AO44" t="n">
         <v>0.0004252867320855558</v>
@@ -9293,13 +9293,13 @@
         <v>0.0004651055058316485</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.0003384842221802779</v>
+        <v>0.000338484222180278</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.0004951571500580522</v>
+        <v>0.0004951571500580524</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.0003777417139028418</v>
+        <v>0.0003777417139028417</v>
       </c>
       <c r="AT44" t="n">
         <v>0.0004714341830339178</v>
@@ -9326,19 +9326,19 @@
         <v>0.00157920013175412</v>
       </c>
       <c r="BB44" t="n">
-        <v>0.0009443297037733912</v>
+        <v>0.0009443297037733911</v>
       </c>
       <c r="BC44" t="n">
         <v>0.001314854107271866</v>
       </c>
       <c r="BD44" t="n">
-        <v>0.001693196789087674</v>
+        <v>0.001693196789087673</v>
       </c>
       <c r="BE44" t="n">
         <v>0.0009937183701310334</v>
       </c>
       <c r="BF44" t="n">
-        <v>0.0006548256674536439</v>
+        <v>0.0006548256674536438</v>
       </c>
       <c r="BG44" t="n">
         <v>0.0008201042193322674</v>
@@ -9347,13 +9347,13 @@
         <v>0.0006893138320887157</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.0007275797199780114</v>
+        <v>0.0007275797199780115</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.0072245397220944</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.00440553236045924</v>
+        <v>0.004405532360459242</v>
       </c>
       <c r="BL44" t="n">
         <v>0.001428661253412902</v>
@@ -9362,22 +9362,22 @@
         <v>0.001182919180961</v>
       </c>
       <c r="BN44" t="n">
-        <v>0.0006694964919540001</v>
+        <v>0.000669496491954</v>
       </c>
       <c r="BO44" t="n">
         <v>0.0007115188128589999</v>
       </c>
       <c r="BP44" t="n">
-        <v>0.004724845716358263</v>
+        <v>0.004724845716358261</v>
       </c>
       <c r="BQ44" t="n">
-        <v>0.004336316512052163</v>
+        <v>0.004336316512052164</v>
       </c>
       <c r="BR44" t="n">
         <v>0.0004835828294780274</v>
       </c>
       <c r="BS44" t="n">
-        <v>0.0005373041672076551</v>
+        <v>0.000537304167207655</v>
       </c>
       <c r="BT44" t="n">
         <v>0.0007084056617775744</v>
@@ -9392,10 +9392,10 @@
         <v>0.0005998931523395383</v>
       </c>
       <c r="BX44" t="n">
-        <v>0.0006473970413813714</v>
+        <v>0.0006473970413813716</v>
       </c>
       <c r="BY44" t="n">
-        <v>0.0006417251121315134</v>
+        <v>0.0006417251121315133</v>
       </c>
       <c r="BZ44" t="n">
         <v>0.0006026146934179852</v>
@@ -9846,7 +9846,7 @@
         <v>0.0004446083939889183</v>
       </c>
       <c r="T48" t="n">
-        <v>0.0004166316851689865</v>
+        <v>0.0004166316851689866</v>
       </c>
       <c r="U48" t="n">
         <v>0.0004098688069242123</v>
@@ -9975,7 +9975,7 @@
         <v>0.00231110502760416</v>
       </c>
       <c r="BK48" t="n">
-        <v>0.0008824134723302295</v>
+        <v>0.0008824134723302294</v>
       </c>
       <c r="BL48" t="n">
         <v>0.000614891800478267</v>
@@ -10591,22 +10591,22 @@
         <v>0.1898655784976916</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0596382326981627</v>
+        <v>0.05963823269816269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.05423711469210915</v>
+        <v>0.05423711469210914</v>
       </c>
       <c r="I54" t="n">
-        <v>0.05143403927058116</v>
+        <v>0.05143403927058115</v>
       </c>
       <c r="J54" t="n">
         <v>0.08861473051631437</v>
       </c>
       <c r="K54" t="n">
-        <v>0.08769148706878988</v>
+        <v>0.08769148706878983</v>
       </c>
       <c r="L54" t="n">
-        <v>0.07506259669369787</v>
+        <v>0.07506259669369784</v>
       </c>
       <c r="M54" t="n">
         <v>0.03471172123205261</v>
@@ -10624,7 +10624,7 @@
         <v>0.03780440914502887</v>
       </c>
       <c r="R54" t="n">
-        <v>0.03777021782216378</v>
+        <v>0.0377702178221638</v>
       </c>
       <c r="S54" t="n">
         <v>0.03605587487352713</v>
@@ -10663,7 +10663,7 @@
         <v>0.1143107063543565</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.09654706807146193</v>
+        <v>0.09654706807146195</v>
       </c>
       <c r="AF54" t="n">
         <v>0.07353994020113497</v>
@@ -10681,16 +10681,16 @@
         <v>0.04924378088719029</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.04272843111430607</v>
+        <v>0.04272843111430608</v>
       </c>
       <c r="AL54" t="n">
         <v>0.05085816043419402</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.04604362386664201</v>
+        <v>0.046043623866642</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.05730555382432563</v>
+        <v>0.05730555382432564</v>
       </c>
       <c r="AO54" t="n">
         <v>0.05010150926536122</v>
@@ -10702,13 +10702,13 @@
         <v>0.06772861854584572</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.07085209812095618</v>
+        <v>0.07085209812095619</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.09910904869469508</v>
+        <v>0.09910904869469507</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.09955425678155341</v>
+        <v>0.09955425678155343</v>
       </c>
       <c r="AU54" t="n">
         <v>0.08926911643136358</v>
@@ -10717,7 +10717,7 @@
         <v>0.09369546929625121</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.04099871512080958</v>
+        <v>0.04099871512080957</v>
       </c>
       <c r="AX54" t="n">
         <v>0.110014217788939</v>
@@ -10726,10 +10726,10 @@
         <v>0.1033021970510136</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0.1438794386472141</v>
+        <v>0.143879438647214</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.1359816777724765</v>
+        <v>0.1359816777724766</v>
       </c>
       <c r="BB54" t="n">
         <v>0.2045911924521313</v>
@@ -10759,13 +10759,13 @@
         <v>0.1315240313754536</v>
       </c>
       <c r="BK54" t="n">
-        <v>0.04518994484349141</v>
+        <v>0.0451899448434914</v>
       </c>
       <c r="BL54" t="n">
-        <v>0.06710901670523277</v>
+        <v>0.06710901670523278</v>
       </c>
       <c r="BM54" t="n">
-        <v>0.06831464925758098</v>
+        <v>0.06831464925758099</v>
       </c>
       <c r="BN54" t="n">
         <v>0.03407159117696099</v>
@@ -10774,7 +10774,7 @@
         <v>0.05660769668922399</v>
       </c>
       <c r="BP54" t="n">
-        <v>0.1229658241254421</v>
+        <v>0.1229658241254422</v>
       </c>
       <c r="BQ54" t="n">
         <v>0.06302358751104499</v>
@@ -10789,10 +10789,10 @@
         <v>0.09739698835396821</v>
       </c>
       <c r="BU54" t="n">
-        <v>0.09069491182603888</v>
+        <v>0.09069491182603887</v>
       </c>
       <c r="BV54" t="n">
-        <v>0.05000832036309062</v>
+        <v>0.0500083203630906</v>
       </c>
       <c r="BW54" t="n">
         <v>0.05287604464728281</v>
@@ -10801,10 +10801,10 @@
         <v>0.05759318504522874</v>
       </c>
       <c r="BY54" t="n">
-        <v>0.06339911879974638</v>
+        <v>0.0633991187997464</v>
       </c>
       <c r="BZ54" t="n">
-        <v>0.06229786134273684</v>
+        <v>0.06229786134273685</v>
       </c>
     </row>
     <row r="55">
@@ -10823,13 +10823,13 @@
         <v>0.01081454757929513</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01303629366939747</v>
+        <v>0.01303629366939746</v>
       </c>
       <c r="F55" t="n">
         <v>0.01360351201504055</v>
       </c>
       <c r="G55" t="n">
-        <v>0.005360424324383288</v>
+        <v>0.005360424324383287</v>
       </c>
       <c r="H55" t="n">
         <v>0.004783724941028616</v>
@@ -10844,7 +10844,7 @@
         <v>0.007457180080699568</v>
       </c>
       <c r="L55" t="n">
-        <v>0.006516095643963008</v>
+        <v>0.006516095643963009</v>
       </c>
       <c r="M55" t="n">
         <v>0.004855855585870098</v>
@@ -10856,10 +10856,10 @@
         <v>0.006253634020039597</v>
       </c>
       <c r="P55" t="n">
-        <v>0.007090215170729595</v>
+        <v>0.007090215170729596</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.006232395903747292</v>
+        <v>0.006232395903747293</v>
       </c>
       <c r="R55" t="n">
         <v>0.00616788113007639</v>
@@ -10877,43 +10877,43 @@
         <v>0.007146787951147837</v>
       </c>
       <c r="W55" t="n">
-        <v>0.007059463625383834</v>
+        <v>0.007059463625383835</v>
       </c>
       <c r="X55" t="n">
         <v>0.007067113781883744</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.008239441873919534</v>
+        <v>0.008239441873919536</v>
       </c>
       <c r="Z55" t="n">
         <v>0.008610745951254982</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.008649727747567499</v>
+        <v>0.008649727747567497</v>
       </c>
       <c r="AB55" t="n">
         <v>0.008371258037462088</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.008970740126326903</v>
+        <v>0.008970740126326905</v>
       </c>
       <c r="AD55" t="n">
         <v>0.009602932346261925</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.009828621292482192</v>
+        <v>0.009828621292482194</v>
       </c>
       <c r="AF55" t="n">
         <v>0.006887409785626681</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.008413094378923156</v>
+        <v>0.008413094378923158</v>
       </c>
       <c r="AH55" t="n">
         <v>0.004792819511346456</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.007712396841239953</v>
+        <v>0.007712396841239952</v>
       </c>
       <c r="AJ55" t="n">
         <v>0.007984239077775344</v>
@@ -10922,19 +10922,19 @@
         <v>0.007744541766948131</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.008803280989721005</v>
+        <v>0.008803280989721003</v>
       </c>
       <c r="AM55" t="n">
         <v>0.00785363183889881</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.009294941133990065</v>
+        <v>0.009294941133990067</v>
       </c>
       <c r="AO55" t="n">
         <v>0.008181841985693768</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.00855048071443624</v>
+        <v>0.008550480714436242</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.006809123503029726</v>
@@ -10943,13 +10943,13 @@
         <v>0.00814125550698422</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.007785504755174552</v>
+        <v>0.007785504755174551</v>
       </c>
       <c r="AT55" t="n">
         <v>0.008963274165000711</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.009271411238595864</v>
+        <v>0.009271411238595862</v>
       </c>
       <c r="AV55" t="n">
         <v>0.009916605387099429</v>
@@ -10964,13 +10964,13 @@
         <v>0.02157720635429981</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0.01716881102091137</v>
+        <v>0.01716881102091138</v>
       </c>
       <c r="BA55" t="n">
         <v>0.01941219761128539</v>
       </c>
       <c r="BB55" t="n">
-        <v>0.02210354675805214</v>
+        <v>0.02210354675805213</v>
       </c>
       <c r="BC55" t="n">
         <v>0.02018148766768143</v>
@@ -11058,10 +11058,10 @@
         <v>0.02445946242487982</v>
       </c>
       <c r="D56" t="n">
-        <v>0.04591343296125255</v>
+        <v>0.04591343296125253</v>
       </c>
       <c r="E56" t="n">
-        <v>0.06835196440235006</v>
+        <v>0.06835196440235003</v>
       </c>
       <c r="F56" t="n">
         <v>0.01630759095521601</v>
@@ -11073,10 +11073,10 @@
         <v>0.02716422965099677</v>
       </c>
       <c r="I56" t="n">
-        <v>0.02838142976457154</v>
+        <v>0.02838142976457153</v>
       </c>
       <c r="J56" t="n">
-        <v>0.04322255549696287</v>
+        <v>0.04322255549696288</v>
       </c>
       <c r="K56" t="n">
         <v>0.0431271440629354</v>
@@ -11091,31 +11091,31 @@
         <v>0.03116615445696052</v>
       </c>
       <c r="O56" t="n">
-        <v>0.03090427932153013</v>
+        <v>0.03090427932153012</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0481303493777258</v>
+        <v>0.04813034937772578</v>
       </c>
       <c r="Q56" t="n">
         <v>0.04071491673379893</v>
       </c>
       <c r="R56" t="n">
-        <v>0.04364996720761423</v>
+        <v>0.04364996720761422</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04870327175299428</v>
+        <v>0.0487032717529943</v>
       </c>
       <c r="T56" t="n">
-        <v>0.04655934913633557</v>
+        <v>0.04655934913633558</v>
       </c>
       <c r="U56" t="n">
-        <v>0.04999325036413325</v>
+        <v>0.04999325036413324</v>
       </c>
       <c r="V56" t="n">
         <v>0.06448379347575399</v>
       </c>
       <c r="W56" t="n">
-        <v>0.06158527827109765</v>
+        <v>0.06158527827109766</v>
       </c>
       <c r="X56" t="n">
         <v>0.05537270755326205</v>
@@ -11127,7 +11127,7 @@
         <v>0.06582734282117071</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.07167697759378799</v>
+        <v>0.07167697759378797</v>
       </c>
       <c r="AB56" t="n">
         <v>0.06501752004711467</v>
@@ -11136,16 +11136,16 @@
         <v>0.0724475201775201</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.07530707529535538</v>
+        <v>0.07530707529535539</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.07587328173838839</v>
+        <v>0.07587328173838837</v>
       </c>
       <c r="AF56" t="n">
         <v>0.03946071040200334</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.04711417263990938</v>
+        <v>0.04711417263990939</v>
       </c>
       <c r="AH56" t="n">
         <v>0.03173287119874686</v>
@@ -11160,19 +11160,19 @@
         <v>0.06178990670852413</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.07695179329973223</v>
+        <v>0.07695179329973226</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.06702473603587308</v>
+        <v>0.06702473603587307</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.06778832530265994</v>
+        <v>0.06778832530265991</v>
       </c>
       <c r="AO56" t="n">
         <v>0.06424328918390118</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.07278275968300488</v>
+        <v>0.07278275968300485</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.05200978641053879</v>
@@ -11187,7 +11187,7 @@
         <v>0.06431954771474285</v>
       </c>
       <c r="AU56" t="n">
-        <v>0.07135948344390257</v>
+        <v>0.07135948344390253</v>
       </c>
       <c r="AV56" t="n">
         <v>0.06365730817176012</v>
@@ -11205,16 +11205,16 @@
         <v>0.005985132258225338</v>
       </c>
       <c r="BA56" t="n">
-        <v>0.003903863431020502</v>
+        <v>0.003903863431020501</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.008568820750290666</v>
+        <v>0.008568820750290664</v>
       </c>
       <c r="BC56" t="n">
-        <v>0.003378906085344885</v>
+        <v>0.003378906085344884</v>
       </c>
       <c r="BD56" t="n">
-        <v>0.005165016903268299</v>
+        <v>0.0051650169032683</v>
       </c>
       <c r="BE56" t="n">
         <v>0.00319563864441662</v>
@@ -11223,16 +11223,16 @@
         <v>0.005748131008486537</v>
       </c>
       <c r="BG56" t="n">
-        <v>0.00551674710100437</v>
+        <v>0.005516747101004368</v>
       </c>
       <c r="BH56" t="n">
-        <v>0.007156683085491687</v>
+        <v>0.007156683085491688</v>
       </c>
       <c r="BI56" t="n">
-        <v>0.005459503637301601</v>
+        <v>0.005459503637301603</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.007666014618502558</v>
+        <v>0.00766601461850256</v>
       </c>
       <c r="BK56" t="n">
         <v>0.003496545827132832</v>
@@ -11241,7 +11241,7 @@
         <v>0.003781662807793282</v>
       </c>
       <c r="BM56" t="n">
-        <v>0.005640112044796002</v>
+        <v>0.005640112044795999</v>
       </c>
       <c r="BN56" t="n">
         <v>0.010211438888226</v>
@@ -11250,10 +11250,10 @@
         <v>0.01195859948303</v>
       </c>
       <c r="BP56" t="n">
-        <v>0.006929935827152902</v>
+        <v>0.006929935827152901</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0.005079851383037976</v>
+        <v>0.005079851383037974</v>
       </c>
       <c r="BR56" t="n">
         <v>0.01005309630287698</v>
@@ -11262,7 +11262,7 @@
         <v>0.01284990036110044</v>
       </c>
       <c r="BT56" t="n">
-        <v>0.01822980336708245</v>
+        <v>0.01822980336708246</v>
       </c>
       <c r="BU56" t="n">
         <v>0.02102460113097052</v>
@@ -11274,7 +11274,7 @@
         <v>0.019070155061954</v>
       </c>
       <c r="BX56" t="n">
-        <v>0.02095497457295137</v>
+        <v>0.02095497457295136</v>
       </c>
       <c r="BY56" t="n">
         <v>0.01886996370724664</v>
@@ -11476,7 +11476,7 @@
         <v>0.0007534617421709644</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0005645065914264417</v>
+        <v>0.0005645065914264416</v>
       </c>
       <c r="E59" t="n">
         <v>0.0004213929021846839</v>
@@ -11581,7 +11581,7 @@
         <v>8.762256239141321e-05</v>
       </c>
       <c r="AM59" t="n">
-        <v>9.469186338320944e-05</v>
+        <v>9.469186338320945e-05</v>
       </c>
       <c r="AN59" t="n">
         <v>7.41557695650366e-05</v>
@@ -11602,7 +11602,7 @@
         <v>6.386508318341714e-05</v>
       </c>
       <c r="AT59" t="n">
-        <v>7.750975295792609e-05</v>
+        <v>7.750975295792608e-05</v>
       </c>
       <c r="AU59" t="n">
         <v>8.546975738521603e-05</v>
@@ -11662,13 +11662,13 @@
         <v>0.002761247671184</v>
       </c>
       <c r="BN59" t="n">
-        <v>0.002631306979092</v>
+        <v>0.002631306979092001</v>
       </c>
       <c r="BO59" t="n">
         <v>0.00151526937906</v>
       </c>
       <c r="BP59" t="n">
-        <v>0.002441881969380743</v>
+        <v>0.002441881969380742</v>
       </c>
       <c r="BQ59" t="n">
         <v>0.001486610580064461</v>
@@ -11717,13 +11717,13 @@
         <v>0.05059057885521379</v>
       </c>
       <c r="E60" t="n">
-        <v>0.04128636135723639</v>
+        <v>0.04128636135723638</v>
       </c>
       <c r="F60" t="n">
         <v>0.04948523388856117</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01923450235223112</v>
+        <v>0.01923450235223113</v>
       </c>
       <c r="H60" t="n">
         <v>0.01653647501397063</v>
@@ -11756,7 +11756,7 @@
         <v>0.02814563363255421</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02804108539696286</v>
+        <v>0.02804108539696285</v>
       </c>
       <c r="S60" t="n">
         <v>0.02868018458426515</v>
@@ -11768,13 +11768,13 @@
         <v>0.03058381269343196</v>
       </c>
       <c r="V60" t="n">
-        <v>0.03543101953646079</v>
+        <v>0.0354310195364608</v>
       </c>
       <c r="W60" t="n">
-        <v>0.03451643422008279</v>
+        <v>0.0345164342200828</v>
       </c>
       <c r="X60" t="n">
-        <v>0.03692718769015445</v>
+        <v>0.03692718769015446</v>
       </c>
       <c r="Y60" t="n">
         <v>0.0416164647357115</v>
@@ -11789,13 +11789,13 @@
         <v>0.02164211481213933</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.02894114796002764</v>
+        <v>0.02894114796002765</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.03467690804097148</v>
+        <v>0.0346769080409715</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.03392698075829243</v>
+        <v>0.03392698075829242</v>
       </c>
       <c r="AF60" t="n">
         <v>0.0217668744673701</v>
@@ -11816,13 +11816,13 @@
         <v>0.01632518981369226</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.02220332635947453</v>
+        <v>0.02220332635947452</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.02052187710576137</v>
+        <v>0.02052187710576136</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.034758517360381</v>
+        <v>0.03475851736038101</v>
       </c>
       <c r="AO60" t="n">
         <v>0.03142183993159976</v>
@@ -11843,7 +11843,7 @@
         <v>0.04247473150939399</v>
       </c>
       <c r="AU60" t="n">
-        <v>0.04079026790250642</v>
+        <v>0.04079026790250641</v>
       </c>
       <c r="AV60" t="n">
         <v>0.04331008822523776</v>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.008471823497959208</v>
+        <v>0.00847182349795921</v>
       </c>
       <c r="D63" t="n">
         <v>0.01279448374917614</v>
@@ -12278,13 +12278,13 @@
         <v>0.02222583211886308</v>
       </c>
       <c r="F63" t="n">
-        <v>0.009699266579793364</v>
+        <v>0.009699266579793366</v>
       </c>
       <c r="G63" t="n">
         <v>0.01331718767020005</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01276479903903758</v>
+        <v>0.01276479903903757</v>
       </c>
       <c r="I63" t="n">
         <v>0.0143977278620904</v>
@@ -12296,7 +12296,7 @@
         <v>0.00687817216704303</v>
       </c>
       <c r="L63" t="n">
-        <v>0.005777465565244612</v>
+        <v>0.005777465565244611</v>
       </c>
       <c r="M63" t="n">
         <v>0.01059716192462796</v>
@@ -12311,10 +12311,10 @@
         <v>0.01482050348809692</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.01427792720100104</v>
+        <v>0.01427792720100105</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01347914591567789</v>
+        <v>0.0134791459156779</v>
       </c>
       <c r="S63" t="n">
         <v>0.0116560017532111</v>
@@ -12329,7 +12329,7 @@
         <v>0.01256270732208422</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0129668785521955</v>
+        <v>0.01296687855219551</v>
       </c>
       <c r="X63" t="n">
         <v>0.01093219401904202</v>
@@ -12374,13 +12374,13 @@
         <v>0.03534642402757376</v>
       </c>
       <c r="AL63" t="n">
-        <v>0.0494620321141796</v>
+        <v>0.04946203211417961</v>
       </c>
       <c r="AM63" t="n">
         <v>0.03931935007139734</v>
       </c>
       <c r="AN63" t="n">
-        <v>0.02511262690813035</v>
+        <v>0.02511262690813034</v>
       </c>
       <c r="AO63" t="n">
         <v>0.02076384457930367</v>
@@ -12410,7 +12410,7 @@
         <v>0.003596173743162529</v>
       </c>
       <c r="AX63" t="n">
-        <v>0.007850846041321854</v>
+        <v>0.007850846041321852</v>
       </c>
       <c r="AY63" t="n">
         <v>0.005774768069212781</v>
@@ -12425,10 +12425,10 @@
         <v>0.008081167614974703</v>
       </c>
       <c r="BC63" t="n">
-        <v>0.01030101705854174</v>
+        <v>0.01030101705854173</v>
       </c>
       <c r="BD63" t="n">
-        <v>0.0186980517326153</v>
+        <v>0.01869805173261529</v>
       </c>
       <c r="BE63" t="n">
         <v>0.008222561582154501</v>
@@ -12437,13 +12437,13 @@
         <v>0.005130062452075996</v>
       </c>
       <c r="BG63" t="n">
-        <v>0.00503810711077459</v>
+        <v>0.005038107110774591</v>
       </c>
       <c r="BH63" t="n">
         <v>0.005368022979285251</v>
       </c>
       <c r="BI63" t="n">
-        <v>0.005029524292469652</v>
+        <v>0.005029524292469653</v>
       </c>
       <c r="BJ63" t="n">
         <v>0.016140996405944</v>
@@ -12461,7 +12461,7 @@
         <v>0.002658611182841</v>
       </c>
       <c r="BO63" t="n">
-        <v>0.006199054538276999</v>
+        <v>0.006199054538277</v>
       </c>
       <c r="BP63" t="n">
         <v>0.008345442582701538</v>
@@ -12482,19 +12482,19 @@
         <v>0.006244368310440417</v>
       </c>
       <c r="BV63" t="n">
-        <v>0.00491008335984464</v>
+        <v>0.004910083359844641</v>
       </c>
       <c r="BW63" t="n">
         <v>0.005371868292407976</v>
       </c>
       <c r="BX63" t="n">
-        <v>0.005684500182179034</v>
+        <v>0.005684500182179035</v>
       </c>
       <c r="BY63" t="n">
         <v>0.005992729534612658</v>
       </c>
       <c r="BZ63" t="n">
-        <v>0.005180301225062908</v>
+        <v>0.005180301225062909</v>
       </c>
     </row>
     <row r="64">
@@ -12711,10 +12711,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.03811371040001067</v>
+        <v>0.03811371040001066</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0528489991071889</v>
+        <v>0.05284899910718889</v>
       </c>
       <c r="E65" t="n">
         <v>0.1091938922930419</v>
@@ -12726,10 +12726,10 @@
         <v>0.05170137830001791</v>
       </c>
       <c r="H65" t="n">
-        <v>0.05002657608359121</v>
+        <v>0.0500265760835912</v>
       </c>
       <c r="I65" t="n">
-        <v>0.04990936999895047</v>
+        <v>0.04990936999895048</v>
       </c>
       <c r="J65" t="n">
         <v>0.07420860992930059</v>
@@ -12738,7 +12738,7 @@
         <v>0.07852512740326031</v>
       </c>
       <c r="L65" t="n">
-        <v>0.05596662903353461</v>
+        <v>0.05596662903353462</v>
       </c>
       <c r="M65" t="n">
         <v>0.02312274243601316</v>
@@ -12747,16 +12747,16 @@
         <v>0.02518858886305193</v>
       </c>
       <c r="O65" t="n">
-        <v>0.04025547236087762</v>
+        <v>0.04025547236087761</v>
       </c>
       <c r="P65" t="n">
         <v>0.03562594910190359</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.03073932767000942</v>
+        <v>0.03073932767000941</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0323326840788043</v>
+        <v>0.03233268407880429</v>
       </c>
       <c r="S65" t="n">
         <v>0.03501913442555094</v>
@@ -12765,13 +12765,13 @@
         <v>0.0332717843685913</v>
       </c>
       <c r="U65" t="n">
-        <v>0.03465525390804637</v>
+        <v>0.03465525390804636</v>
       </c>
       <c r="V65" t="n">
         <v>0.04695978357327493</v>
       </c>
       <c r="W65" t="n">
-        <v>0.04931579554091598</v>
+        <v>0.04931579554091597</v>
       </c>
       <c r="X65" t="n">
         <v>0.04016349843668832</v>
@@ -12780,7 +12780,7 @@
         <v>0.04845842479377025</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.04388482647001481</v>
+        <v>0.0438848264700148</v>
       </c>
       <c r="AA65" t="n">
         <v>0.04973407397122197</v>
@@ -12798,22 +12798,22 @@
         <v>0.1106305146656332</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.06594780172995286</v>
+        <v>0.06594780172995288</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.08251444336763204</v>
+        <v>0.08251444336763203</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.03903489208867671</v>
+        <v>0.03903489208867672</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.06175891131979479</v>
+        <v>0.0617589113197948</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.05966806074272552</v>
+        <v>0.05966806074272554</v>
       </c>
       <c r="AK65" t="n">
-        <v>0.1241130671690335</v>
+        <v>0.1241130671690336</v>
       </c>
       <c r="AL65" t="n">
         <v>0.153624459893109</v>
@@ -12822,19 +12822,19 @@
         <v>0.1322872232286913</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.06082991081536736</v>
+        <v>0.06082991081536737</v>
       </c>
       <c r="AO65" t="n">
-        <v>0.06711952285420555</v>
+        <v>0.06711952285420558</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.06733707983124841</v>
+        <v>0.0673370798312484</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.07145627826288556</v>
+        <v>0.07145627826288554</v>
       </c>
       <c r="AR65" t="n">
-        <v>0.09137729045955752</v>
+        <v>0.0913772904595575</v>
       </c>
       <c r="AS65" t="n">
         <v>0.07495977913004929</v>
@@ -12843,25 +12843,25 @@
         <v>0.08075052665216723</v>
       </c>
       <c r="AU65" t="n">
-        <v>0.07004748168599893</v>
+        <v>0.07004748168599895</v>
       </c>
       <c r="AV65" t="n">
-        <v>0.06786668755119993</v>
+        <v>0.06786668755119991</v>
       </c>
       <c r="AW65" t="n">
         <v>0.1641120883021979</v>
       </c>
       <c r="AX65" t="n">
-        <v>0.05364441851859308</v>
+        <v>0.05364441851859307</v>
       </c>
       <c r="AY65" t="n">
-        <v>0.04274701536159631</v>
+        <v>0.04274701536159632</v>
       </c>
       <c r="AZ65" t="n">
         <v>0.03994112861089982</v>
       </c>
       <c r="BA65" t="n">
-        <v>0.02792089367666458</v>
+        <v>0.02792089367666457</v>
       </c>
       <c r="BB65" t="n">
         <v>0.3892210605409299</v>
@@ -12870,10 +12870,10 @@
         <v>0.1213164698155713</v>
       </c>
       <c r="BD65" t="n">
-        <v>0.3526135908495048</v>
+        <v>0.3526135908495049</v>
       </c>
       <c r="BE65" t="n">
-        <v>0.08739938262206938</v>
+        <v>0.08739938262206934</v>
       </c>
       <c r="BF65" t="n">
         <v>0.1505873897706384</v>
@@ -12891,7 +12891,7 @@
         <v>0.06534434610744</v>
       </c>
       <c r="BK65" t="n">
-        <v>0.06683898505884608</v>
+        <v>0.06683898505884607</v>
       </c>
       <c r="BL65" t="n">
         <v>0.02289563740083265</v>
@@ -13009,7 +13009,7 @@
         <v>0.0001757005513195305</v>
       </c>
       <c r="W66" t="n">
-        <v>0.0001800598447747712</v>
+        <v>0.0001800598447747713</v>
       </c>
       <c r="X66" t="n">
         <v>0.0001915453620613842</v>
@@ -13066,7 +13066,7 @@
         <v>0.0001940967634446399</v>
       </c>
       <c r="AP66" t="n">
-        <v>0.0001890222643758548</v>
+        <v>0.0001890222643758549</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.0001708457444233777</v>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.009087140824320387</v>
+        <v>0.009087140824320388</v>
       </c>
       <c r="D72" t="n">
         <v>0.01251859297698672</v>
@@ -13959,7 +13959,7 @@
         <v>0.005894670527306001</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006452523554999388</v>
+        <v>0.006452523554999389</v>
       </c>
       <c r="P72" t="n">
         <v>0.008981859799223793</v>
@@ -13971,7 +13971,7 @@
         <v>0.007998068903398341</v>
       </c>
       <c r="S72" t="n">
-        <v>0.009020747959087951</v>
+        <v>0.009020747959087949</v>
       </c>
       <c r="T72" t="n">
         <v>0.00818535889138817</v>
@@ -14028,7 +14028,7 @@
         <v>0.02403779680191368</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.0277906025304635</v>
+        <v>0.02779060253046351</v>
       </c>
       <c r="AM72" t="n">
         <v>0.02607193441660341</v>
@@ -14061,7 +14061,7 @@
         <v>0.01154640810743717</v>
       </c>
       <c r="AW72" t="n">
-        <v>0.0139312933440088</v>
+        <v>0.01393129334400879</v>
       </c>
       <c r="AX72" t="n">
         <v>0.01385268072923274</v>
@@ -14073,7 +14073,7 @@
         <v>0.01605139573786731</v>
       </c>
       <c r="BA72" t="n">
-        <v>0.02060081535049807</v>
+        <v>0.02060081535049806</v>
       </c>
       <c r="BB72" t="n">
         <v>0.01981137820924392</v>
@@ -14109,7 +14109,7 @@
         <v>0.009792343821584426</v>
       </c>
       <c r="BM72" t="n">
-        <v>0.008812556678121001</v>
+        <v>0.008812556678120999</v>
       </c>
       <c r="BN72" t="n">
         <v>0.020978332678122</v>
@@ -14127,10 +14127,10 @@
         <v>0.01081473952606629</v>
       </c>
       <c r="BS72" t="n">
-        <v>0.01295645183598424</v>
+        <v>0.01295645183598425</v>
       </c>
       <c r="BT72" t="n">
-        <v>0.01708767160943205</v>
+        <v>0.01708767160943204</v>
       </c>
       <c r="BU72" t="n">
         <v>0.02082604172463947</v>
@@ -14145,7 +14145,7 @@
         <v>0.02594927708998996</v>
       </c>
       <c r="BY72" t="n">
-        <v>0.02572220665589333</v>
+        <v>0.02572220665589332</v>
       </c>
       <c r="BZ72" t="n">
         <v>0.0206711430843869</v>
@@ -14161,13 +14161,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.006726408931911986</v>
+        <v>0.006726408931911982</v>
       </c>
       <c r="D73" t="n">
-        <v>0.02168898557128442</v>
+        <v>0.02168898557128443</v>
       </c>
       <c r="E73" t="n">
-        <v>0.05207941763201959</v>
+        <v>0.05207941763201958</v>
       </c>
       <c r="F73" t="n">
         <v>0.005574780283567483</v>
@@ -14182,10 +14182,10 @@
         <v>0.002882132655553965</v>
       </c>
       <c r="J73" t="n">
-        <v>0.004112125887204915</v>
+        <v>0.004112125887204914</v>
       </c>
       <c r="K73" t="n">
-        <v>0.004436769686470716</v>
+        <v>0.004436769686470715</v>
       </c>
       <c r="L73" t="n">
         <v>0.003933734314543328</v>
@@ -14194,7 +14194,7 @@
         <v>0.002453180032958254</v>
       </c>
       <c r="N73" t="n">
-        <v>0.002538482941790804</v>
+        <v>0.002538482941790803</v>
       </c>
       <c r="O73" t="n">
         <v>0.003604767456450613</v>
@@ -14203,37 +14203,37 @@
         <v>0.003955347181064943</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.003190262298275581</v>
+        <v>0.00319026229827558</v>
       </c>
       <c r="R73" t="n">
-        <v>0.003487882619623858</v>
+        <v>0.003487882619623859</v>
       </c>
       <c r="S73" t="n">
         <v>0.003814572635987122</v>
       </c>
       <c r="T73" t="n">
-        <v>0.003637591449838445</v>
+        <v>0.003637591449838444</v>
       </c>
       <c r="U73" t="n">
-        <v>0.003543925001413677</v>
+        <v>0.003543925001413676</v>
       </c>
       <c r="V73" t="n">
         <v>0.004398516705795909</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004842748263257203</v>
+        <v>0.004842748263257204</v>
       </c>
       <c r="X73" t="n">
         <v>0.004182417334687125</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.004735464506906968</v>
+        <v>0.004735464506906969</v>
       </c>
       <c r="Z73" t="n">
         <v>0.004659984354778196</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.005026008015953477</v>
+        <v>0.005026008015953476</v>
       </c>
       <c r="AB73" t="n">
         <v>0.00453989320688843</v>
@@ -14248,28 +14248,28 @@
         <v>0.005447988662127371</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.003725939440519874</v>
+        <v>0.003725939440519873</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.004649041378502995</v>
+        <v>0.004649041378502996</v>
       </c>
       <c r="AH73" t="n">
         <v>0.003241735656690619</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.0049264823269628</v>
+        <v>0.004926482326962802</v>
       </c>
       <c r="AJ73" t="n">
         <v>0.004711852708239144</v>
       </c>
       <c r="AK73" t="n">
-        <v>0.007710510293148668</v>
+        <v>0.007710510293148666</v>
       </c>
       <c r="AL73" t="n">
         <v>0.008598330058908884</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.008131854639171139</v>
+        <v>0.00813185463917114</v>
       </c>
       <c r="AN73" t="n">
         <v>0.005300399640794567</v>
@@ -14284,7 +14284,7 @@
         <v>0.003915730459478279</v>
       </c>
       <c r="AR73" t="n">
-        <v>0.004334815392134624</v>
+        <v>0.004334815392134626</v>
       </c>
       <c r="AS73" t="n">
         <v>0.004437924693919979</v>
@@ -14293,34 +14293,34 @@
         <v>0.006918140027478262</v>
       </c>
       <c r="AU73" t="n">
-        <v>0.005789931799762619</v>
+        <v>0.00578993179976262</v>
       </c>
       <c r="AV73" t="n">
-        <v>0.005912715387038572</v>
+        <v>0.005912715387038571</v>
       </c>
       <c r="AW73" t="n">
-        <v>0.0411080462584316</v>
+        <v>0.04110804625843159</v>
       </c>
       <c r="AX73" t="n">
-        <v>0.01010978224707707</v>
+        <v>0.01010978224707708</v>
       </c>
       <c r="AY73" t="n">
         <v>0.01083357025525582</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0.009426811235790715</v>
+        <v>0.00942681123579071</v>
       </c>
       <c r="BA73" t="n">
         <v>0.00776981438702788</v>
       </c>
       <c r="BB73" t="n">
-        <v>0.04524092453212106</v>
+        <v>0.04524092453212105</v>
       </c>
       <c r="BC73" t="n">
         <v>0.01754701888810763</v>
       </c>
       <c r="BD73" t="n">
-        <v>0.0342310106716592</v>
+        <v>0.03423101067165921</v>
       </c>
       <c r="BE73" t="n">
         <v>0.01381311311501278</v>
@@ -14329,7 +14329,7 @@
         <v>0.01406064210883963</v>
       </c>
       <c r="BG73" t="n">
-        <v>0.01348676530379107</v>
+        <v>0.01348676530379108</v>
       </c>
       <c r="BH73" t="n">
         <v>0.01583616081928295</v>
@@ -14338,7 +14338,7 @@
         <v>0.01465772526636441</v>
       </c>
       <c r="BJ73" t="n">
-        <v>0.008814706839452801</v>
+        <v>0.008814706839452803</v>
       </c>
       <c r="BK73" t="n">
         <v>0.00347120026226882</v>
@@ -14350,7 +14350,7 @@
         <v>0.007237700125477999</v>
       </c>
       <c r="BN73" t="n">
-        <v>0.008064647964001002</v>
+        <v>0.008064647964001</v>
       </c>
       <c r="BO73" t="n">
         <v>0.027265087964853</v>
@@ -14359,7 +14359,7 @@
         <v>0.009652927419561376</v>
       </c>
       <c r="BQ73" t="n">
-        <v>0.007051608124001514</v>
+        <v>0.007051608124001516</v>
       </c>
       <c r="BR73" t="n">
         <v>0.02541801077365185</v>
@@ -14371,7 +14371,7 @@
         <v>0.02558191589347302</v>
       </c>
       <c r="BU73" t="n">
-        <v>0.02560942478958378</v>
+        <v>0.02560942478958377</v>
       </c>
       <c r="BV73" t="n">
         <v>0.01806211564476744</v>
@@ -14380,13 +14380,13 @@
         <v>0.01888536067481358</v>
       </c>
       <c r="BX73" t="n">
-        <v>0.01774628041512737</v>
+        <v>0.01774628041512736</v>
       </c>
       <c r="BY73" t="n">
-        <v>0.01240511807817385</v>
+        <v>0.01240511807817384</v>
       </c>
       <c r="BZ73" t="n">
-        <v>0.00891397037352294</v>
+        <v>0.008913970373522937</v>
       </c>
     </row>
     <row r="74">
@@ -14402,7 +14402,7 @@
         <v>0.001638667436450315</v>
       </c>
       <c r="D74" t="n">
-        <v>0.001628196745240049</v>
+        <v>0.001628196745240048</v>
       </c>
       <c r="E74" t="n">
         <v>0.001669187595527564</v>
@@ -14420,10 +14420,10 @@
         <v>0.0004835046554068998</v>
       </c>
       <c r="J74" t="n">
-        <v>0.000703973007133712</v>
+        <v>0.0007039730071337122</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0008200322851981796</v>
+        <v>0.0008200322851981795</v>
       </c>
       <c r="L74" t="n">
         <v>0.0006542850564166986</v>
@@ -14435,10 +14435,10 @@
         <v>0.0004027164593101192</v>
       </c>
       <c r="O74" t="n">
-        <v>0.0008367645752545658</v>
+        <v>0.0008367645752545659</v>
       </c>
       <c r="P74" t="n">
-        <v>0.0005822460772529572</v>
+        <v>0.0005822460772529573</v>
       </c>
       <c r="Q74" t="n">
         <v>0.0005307218407344319</v>
@@ -14447,10 +14447,10 @@
         <v>0.000496585698563225</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0005977835543318604</v>
+        <v>0.0005977835543318605</v>
       </c>
       <c r="T74" t="n">
-        <v>0.000612401164470476</v>
+        <v>0.0006124011644704761</v>
       </c>
       <c r="U74" t="n">
         <v>0.0006019414112822108</v>
@@ -14480,13 +14480,13 @@
         <v>0.001021307046669089</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.0008101764254734585</v>
+        <v>0.0008101764254734586</v>
       </c>
       <c r="AE74" t="n">
         <v>0.0007863539089071306</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.0006157563631969764</v>
+        <v>0.0006157563631969763</v>
       </c>
       <c r="AG74" t="n">
         <v>0.0007987521360091311</v>
@@ -14525,7 +14525,7 @@
         <v>0.0008454179196919258</v>
       </c>
       <c r="AS74" t="n">
-        <v>0.0007392168640989927</v>
+        <v>0.0007392168640989928</v>
       </c>
       <c r="AT74" t="n">
         <v>0.000927410723802845</v>
@@ -14576,7 +14576,7 @@
         <v>0.001494392191818649</v>
       </c>
       <c r="BJ74" t="n">
-        <v>0.0005892441104</v>
+        <v>0.0005892441103999998</v>
       </c>
       <c r="BK74" t="n">
         <v>7.162980912238799e-05</v>
@@ -14594,10 +14594,10 @@
         <v>0.001846835283717</v>
       </c>
       <c r="BP74" t="n">
-        <v>0.0009887348119050465</v>
+        <v>0.0009887348119050462</v>
       </c>
       <c r="BQ74" t="n">
-        <v>0.0007984019621490949</v>
+        <v>0.0007984019621490948</v>
       </c>
       <c r="BR74" t="n">
         <v>0.000939912291709281</v>
@@ -14729,7 +14729,7 @@
         <v>0.0004474194495425286</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0004243808596383562</v>
+        <v>0.0004243808596383563</v>
       </c>
       <c r="F76" t="n">
         <v>0.001104626875312271</v>
@@ -14741,7 +14741,7 @@
         <v>0.0003189636622280933</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0003154380533894004</v>
+        <v>0.0003154380533894005</v>
       </c>
       <c r="J76" t="n">
         <v>0.0004455840579672784</v>
@@ -14780,13 +14780,13 @@
         <v>0.0003650458175239881</v>
       </c>
       <c r="V76" t="n">
-        <v>0.0004624075648164765</v>
+        <v>0.0004624075648164766</v>
       </c>
       <c r="W76" t="n">
         <v>0.0004921089980554702</v>
       </c>
       <c r="X76" t="n">
-        <v>0.0004453038748220789</v>
+        <v>0.0004453038748220788</v>
       </c>
       <c r="Y76" t="n">
         <v>0.0005487996495709132</v>
@@ -14798,7 +14798,7 @@
         <v>0.0005341850552116788</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.0005904631636684608</v>
+        <v>0.0005904631636684609</v>
       </c>
       <c r="AC76" t="n">
         <v>0.0007587451189581207</v>
@@ -14825,7 +14825,7 @@
         <v>0.0005050085771579104</v>
       </c>
       <c r="AK76" t="n">
-        <v>0.0007669842869127099</v>
+        <v>0.0007669842869127098</v>
       </c>
       <c r="AL76" t="n">
         <v>0.0008679435941951233</v>
@@ -14864,7 +14864,7 @@
         <v>0.001143825029040527</v>
       </c>
       <c r="AX76" t="n">
-        <v>0.0005747492479542489</v>
+        <v>0.0005747492479542488</v>
       </c>
       <c r="AY76" t="n">
         <v>0.0006758510904385533</v>
@@ -14945,7 +14945,7 @@
         <v>0.0007430135348815087</v>
       </c>
       <c r="BY76" t="n">
-        <v>0.0006920869323669099</v>
+        <v>0.0006920869323669101</v>
       </c>
       <c r="BZ76" t="n">
         <v>0.0006367700465088281</v>
@@ -15655,7 +15655,7 @@
         <v>0.01278405808400004</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01039145190352012</v>
+        <v>0.01039145190352013</v>
       </c>
       <c r="F83" t="n">
         <v>0.01454774136972846</v>
@@ -15673,13 +15673,13 @@
         <v>0.006351169448250528</v>
       </c>
       <c r="K83" t="n">
-        <v>0.007497014255141362</v>
+        <v>0.007497014255141361</v>
       </c>
       <c r="L83" t="n">
         <v>0.005840060941921106</v>
       </c>
       <c r="M83" t="n">
-        <v>0.006419813085077873</v>
+        <v>0.006419813085077874</v>
       </c>
       <c r="N83" t="n">
         <v>0.006573794550004697</v>
@@ -15721,7 +15721,7 @@
         <v>0.02172872596939381</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.02194856411869979</v>
+        <v>0.0219485641186998</v>
       </c>
       <c r="AB83" t="n">
         <v>0.008259055426881951</v>
@@ -15763,13 +15763,13 @@
         <v>0.01384779792534649</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.01247806818776306</v>
+        <v>0.01247806818776307</v>
       </c>
       <c r="AP83" t="n">
         <v>0.01251152322129319</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.007035157923325489</v>
+        <v>0.00703515792332549</v>
       </c>
       <c r="AR83" t="n">
         <v>0.008807155916194081</v>
@@ -15796,16 +15796,16 @@
         <v>0.01827443751297628</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0.02805388616640226</v>
+        <v>0.02805388616640225</v>
       </c>
       <c r="BA83" t="n">
         <v>0.02911178608281101</v>
       </c>
       <c r="BB83" t="n">
-        <v>0.02636130266338145</v>
+        <v>0.02636130266338144</v>
       </c>
       <c r="BC83" t="n">
-        <v>0.03184392680583885</v>
+        <v>0.03184392680583884</v>
       </c>
       <c r="BD83" t="n">
         <v>0.03766884878259264</v>
@@ -15829,7 +15829,7 @@
         <v>0.03970677054408001</v>
       </c>
       <c r="BK83" t="n">
-        <v>0.03757328470065599</v>
+        <v>0.037573284700656</v>
       </c>
       <c r="BL83" t="n">
         <v>0.01973157175705334</v>
@@ -15917,7 +15917,7 @@
         <v>0.00111252356176057</v>
       </c>
       <c r="M84" t="n">
-        <v>0.0009625613420407899</v>
+        <v>0.0009625613420407898</v>
       </c>
       <c r="N84" t="n">
         <v>0.001037956490142471</v>
@@ -15926,7 +15926,7 @@
         <v>0.001751676018663767</v>
       </c>
       <c r="P84" t="n">
-        <v>0.00181626333755427</v>
+        <v>0.001816263337554271</v>
       </c>
       <c r="Q84" t="n">
         <v>0.001644133657204061</v>
@@ -15944,7 +15944,7 @@
         <v>0.001755647550541468</v>
       </c>
       <c r="V84" t="n">
-        <v>0.003441593297105725</v>
+        <v>0.003441593297105726</v>
       </c>
       <c r="W84" t="n">
         <v>0.003357715017941895</v>
@@ -15965,7 +15965,7 @@
         <v>0.001749365833137703</v>
       </c>
       <c r="AC84" t="n">
-        <v>0.003071892338827899</v>
+        <v>0.0030718923388279</v>
       </c>
       <c r="AD84" t="n">
         <v>0.002109449845917563</v>
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.0006686976573730832</v>
+        <v>0.0006686976573730833</v>
       </c>
       <c r="D85" t="n">
         <v>0.0005580474794684376</v>
@@ -16301,7 +16301,7 @@
         <v>0.0003197319490266715</v>
       </c>
       <c r="BM85" t="n">
-        <v>0.000631299431549</v>
+        <v>0.0006312994315490001</v>
       </c>
       <c r="BN85" t="n">
         <v>7.6440917749e-05</v>
@@ -16811,7 +16811,7 @@
         <v>0.0005200341206308082</v>
       </c>
       <c r="BQ89" t="n">
-        <v>0.0005599697942634884</v>
+        <v>0.0005599697942634885</v>
       </c>
       <c r="BR89" t="inlineStr"/>
       <c r="BS89" t="inlineStr"/>
@@ -16958,7 +16958,7 @@
         <v>6.382910320543652e-06</v>
       </c>
       <c r="P91" t="n">
-        <v>1.437150341308173e-05</v>
+        <v>1.437150341308172e-05</v>
       </c>
       <c r="Q91" t="n">
         <v>1.381386819745647e-05</v>
@@ -16979,7 +16979,7 @@
         <v>2.026718208789618e-05</v>
       </c>
       <c r="W91" t="n">
-        <v>2.043599918346714e-05</v>
+        <v>2.043599918346715e-05</v>
       </c>
       <c r="X91" t="n">
         <v>1.832758719535169e-05</v>
@@ -16988,7 +16988,7 @@
         <v>1.863018456856592e-05</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.855085340991576e-05</v>
+        <v>1.855085340991577e-05</v>
       </c>
       <c r="AA91" t="n">
         <v>2.404474790188187e-05</v>
@@ -16997,7 +16997,7 @@
         <v>5.25827153659509e-05</v>
       </c>
       <c r="AC91" t="n">
-        <v>4.697155782144578e-05</v>
+        <v>4.697155782144579e-05</v>
       </c>
       <c r="AD91" t="n">
         <v>5.581370789672539e-05</v>
@@ -17012,7 +17012,7 @@
         <v>2.05700301923901e-05</v>
       </c>
       <c r="AH91" t="n">
-        <v>7.621747417207827e-06</v>
+        <v>7.621747417207826e-06</v>
       </c>
       <c r="AI91" t="n">
         <v>1.616821837388e-05</v>
@@ -17042,7 +17042,7 @@
         <v>2.026280546864582e-05</v>
       </c>
       <c r="AR91" t="n">
-        <v>3.20355914070819e-05</v>
+        <v>3.203559140708191e-05</v>
       </c>
       <c r="AS91" t="n">
         <v>1.920829838334368e-05</v>
@@ -17711,7 +17711,7 @@
         <v>0.0006637057486405051</v>
       </c>
       <c r="G95" t="n">
-        <v>0.001705572837345036</v>
+        <v>0.001705572837345035</v>
       </c>
       <c r="H95" t="n">
         <v>0.001562768513562334</v>
@@ -17723,7 +17723,7 @@
         <v>0.002487645336073106</v>
       </c>
       <c r="K95" t="n">
-        <v>0.002640772987003889</v>
+        <v>0.002640772987003888</v>
       </c>
       <c r="L95" t="n">
         <v>0.002387749035094052</v>
@@ -17735,13 +17735,13 @@
         <v>0.001369118389338051</v>
       </c>
       <c r="O95" t="n">
-        <v>0.001728182760219122</v>
+        <v>0.001728182760219121</v>
       </c>
       <c r="P95" t="n">
-        <v>0.001750321908049882</v>
+        <v>0.001750321908049883</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.001510425323537353</v>
+        <v>0.001510425323537354</v>
       </c>
       <c r="R95" t="n">
         <v>0.001595313886552818</v>
@@ -17792,16 +17792,16 @@
         <v>0.002345563319705379</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.001810068162799993</v>
+        <v>0.001810068162799992</v>
       </c>
       <c r="AI95" t="n">
         <v>0.002753438672215532</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.00278101516170346</v>
+        <v>0.002781015161703459</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.004322945041903562</v>
+        <v>0.004322945041903563</v>
       </c>
       <c r="AL95" t="n">
         <v>0.004872922600514682</v>
@@ -17825,10 +17825,10 @@
         <v>0.002344096835057941</v>
       </c>
       <c r="AS95" t="n">
-        <v>0.001840328834169172</v>
+        <v>0.001840328834169173</v>
       </c>
       <c r="AT95" t="n">
-        <v>0.003152610671525025</v>
+        <v>0.003152610671525026</v>
       </c>
       <c r="AU95" t="n">
         <v>0.002672917154051957</v>
@@ -17843,7 +17843,7 @@
         <v>0.003395304544805187</v>
       </c>
       <c r="AY95" t="n">
-        <v>0.004518269890383349</v>
+        <v>0.00451826989038335</v>
       </c>
       <c r="AZ95" t="n">
         <v>0.002144921256278596</v>
@@ -17861,25 +17861,25 @@
         <v>0.01192487461072182</v>
       </c>
       <c r="BE95" t="n">
-        <v>0.00293300766245492</v>
+        <v>0.002933007662454921</v>
       </c>
       <c r="BF95" t="n">
-        <v>0.00306172251251151</v>
+        <v>0.003061722512511509</v>
       </c>
       <c r="BG95" t="n">
         <v>0.002883638922539686</v>
       </c>
       <c r="BH95" t="n">
-        <v>0.003794487286034798</v>
+        <v>0.003794487286034799</v>
       </c>
       <c r="BI95" t="n">
-        <v>0.003313493919714886</v>
+        <v>0.003313493919714887</v>
       </c>
       <c r="BJ95" t="n">
-        <v>0.00282419253044176</v>
+        <v>0.002824192530441761</v>
       </c>
       <c r="BK95" t="n">
-        <v>0.0009342689785565876</v>
+        <v>0.0009342689785565877</v>
       </c>
       <c r="BL95" t="n">
         <v>0.001452250867609204</v>
@@ -17897,7 +17897,7 @@
         <v>0.002521481598783394</v>
       </c>
       <c r="BQ95" t="n">
-        <v>0.002097343087692719</v>
+        <v>0.00209734308769272</v>
       </c>
       <c r="BR95" t="n">
         <v>0.0139774013234821</v>
@@ -17921,7 +17921,7 @@
         <v>0.009993584000463455</v>
       </c>
       <c r="BY95" t="n">
-        <v>0.00556170102429614</v>
+        <v>0.005561701024296139</v>
       </c>
       <c r="BZ95" t="n">
         <v>0.003338290952490097</v>
@@ -19924,7 +19924,7 @@
         <v>0.0004994564682699115</v>
       </c>
       <c r="N110" t="n">
-        <v>0.0005733339771369778</v>
+        <v>0.0005733339771369776</v>
       </c>
       <c r="O110" t="n">
         <v>0.0005234158227181642</v>
@@ -19936,16 +19936,16 @@
         <v>0.0006668307876846532</v>
       </c>
       <c r="R110" t="n">
-        <v>0.0006904996719005618</v>
+        <v>0.0006904996719005619</v>
       </c>
       <c r="S110" t="n">
-        <v>0.0007168048535943012</v>
+        <v>0.0007168048535943013</v>
       </c>
       <c r="T110" t="n">
-        <v>0.000691379209106993</v>
+        <v>0.0006913792091069929</v>
       </c>
       <c r="U110" t="n">
-        <v>0.0007157239690261801</v>
+        <v>0.00071572396902618</v>
       </c>
       <c r="V110" t="n">
         <v>0.0009527621396236465</v>
@@ -19954,7 +19954,7 @@
         <v>0.001048990468602881</v>
       </c>
       <c r="X110" t="n">
-        <v>0.0007806088835125493</v>
+        <v>0.0007806088835125494</v>
       </c>
       <c r="Y110" t="n">
         <v>0.001102993885928386</v>
@@ -19972,22 +19972,22 @@
         <v>0.0007853314875153461</v>
       </c>
       <c r="AD110" t="n">
-        <v>0.0006582350282825715</v>
+        <v>0.0006582350282825713</v>
       </c>
       <c r="AE110" t="n">
-        <v>0.0007159694809132266</v>
+        <v>0.0007159694809132268</v>
       </c>
       <c r="AF110" t="n">
-        <v>0.0004190133500373946</v>
+        <v>0.0004190133500373945</v>
       </c>
       <c r="AG110" t="n">
-        <v>0.0005976944373176847</v>
+        <v>0.0005976944373176848</v>
       </c>
       <c r="AH110" t="n">
         <v>0.0005213659620774511</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.0009085050347399607</v>
+        <v>0.0009085050347399606</v>
       </c>
       <c r="AJ110" t="n">
         <v>0.0009099881775113138</v>
@@ -19996,7 +19996,7 @@
         <v>0.000510436086101687</v>
       </c>
       <c r="AL110" t="n">
-        <v>0.0005944507030367122</v>
+        <v>0.0005944507030367121</v>
       </c>
       <c r="AM110" t="n">
         <v>0.0005006681759467027</v>
@@ -20014,7 +20014,7 @@
         <v>0.0005520399009031443</v>
       </c>
       <c r="AR110" t="n">
-        <v>0.0006734879363981905</v>
+        <v>0.0006734879363981906</v>
       </c>
       <c r="AS110" t="n">
         <v>0.0005514490852979692</v>
@@ -20032,7 +20032,7 @@
         <v>0.0008890703055824042</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.003457693085035614</v>
+        <v>0.003457693085035615</v>
       </c>
       <c r="AY110" t="n">
         <v>0.003521711169552215</v>
@@ -20041,19 +20041,19 @@
         <v>0.006497198629602104</v>
       </c>
       <c r="BA110" t="n">
-        <v>0.006282882406783112</v>
+        <v>0.006282882406783113</v>
       </c>
       <c r="BB110" t="n">
-        <v>0.001841328517187071</v>
+        <v>0.001841328517187072</v>
       </c>
       <c r="BC110" t="n">
         <v>0.004103174247983767</v>
       </c>
       <c r="BD110" t="n">
-        <v>0.00537532041225971</v>
+        <v>0.005375320412259709</v>
       </c>
       <c r="BE110" t="n">
-        <v>0.003564464728363349</v>
+        <v>0.003564464728363348</v>
       </c>
       <c r="BF110" t="n">
         <v>0.001351022935062274</v>
@@ -20062,13 +20062,13 @@
         <v>0.001421166575559538</v>
       </c>
       <c r="BH110" t="n">
-        <v>0.001406828077442944</v>
+        <v>0.001406828077442943</v>
       </c>
       <c r="BI110" t="n">
         <v>0.001654783283981308</v>
       </c>
       <c r="BJ110" t="n">
-        <v>0.006488985077978</v>
+        <v>0.006488985077977999</v>
       </c>
       <c r="BK110" t="n">
         <v>0.006081659193312114</v>
@@ -20086,10 +20086,10 @@
         <v>0.001725908991551</v>
       </c>
       <c r="BP110" t="n">
-        <v>0.004626792386700709</v>
+        <v>0.004626792386700708</v>
       </c>
       <c r="BQ110" t="n">
-        <v>0.003358275565327551</v>
+        <v>0.003358275565327552</v>
       </c>
       <c r="BR110" t="n">
         <v>0.001453025788720055</v>
@@ -21285,7 +21285,7 @@
         <v>0.003692352093916999</v>
       </c>
       <c r="BO119" t="n">
-        <v>0.003792075875264</v>
+        <v>0.003792075875263999</v>
       </c>
       <c r="BP119" t="n">
         <v>0.001834987588053294</v>
@@ -21315,7 +21315,7 @@
         <v>0.005092632450610418</v>
       </c>
       <c r="BY119" t="n">
-        <v>0.003960348208473712</v>
+        <v>0.003960348208473711</v>
       </c>
       <c r="BZ119" t="n">
         <v>0.003848155944086583</v>
@@ -22973,10 +22973,10 @@
         <v>0.000270892123756039</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0003322419792279049</v>
+        <v>0.0003322419792279048</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0005012905864609141</v>
+        <v>0.0005012905864609142</v>
       </c>
       <c r="G135" t="n">
         <v>0.0001285680097172467</v>
@@ -22985,10 +22985,10 @@
         <v>0.0001215943709610892</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0001168369094488223</v>
+        <v>0.0001168369094488224</v>
       </c>
       <c r="J135" t="n">
-        <v>0.0002000698447746118</v>
+        <v>0.0002000698447746119</v>
       </c>
       <c r="K135" t="n">
         <v>0.0001833654272562879</v>
@@ -23006,16 +23006,16 @@
         <v>7.356164823838308e-05</v>
       </c>
       <c r="P135" t="n">
-        <v>9.468166264885947e-05</v>
+        <v>9.468166264885946e-05</v>
       </c>
       <c r="Q135" t="n">
         <v>8.189532000935594e-05</v>
       </c>
       <c r="R135" t="n">
-        <v>8.212279538192174e-05</v>
+        <v>8.212279538192173e-05</v>
       </c>
       <c r="S135" t="n">
-        <v>0.0001006100954311027</v>
+        <v>0.0001006100954311026</v>
       </c>
       <c r="T135" t="n">
         <v>0.0001088293239808879</v>
@@ -23090,7 +23090,7 @@
         <v>0.0001794744043111782</v>
       </c>
       <c r="AR135" t="n">
-        <v>0.0002023798635626408</v>
+        <v>0.0002023798635626409</v>
       </c>
       <c r="AS135" t="n">
         <v>0.0001416750945288853</v>
@@ -23117,7 +23117,7 @@
         <v>0.000268638907664972</v>
       </c>
       <c r="BA135" t="n">
-        <v>0.0002226245998164807</v>
+        <v>0.0002226245998164808</v>
       </c>
       <c r="BB135" t="n">
         <v>0.0001901481235938387</v>
@@ -23162,7 +23162,7 @@
         <v>0.000237896994391</v>
       </c>
       <c r="BP135" t="n">
-        <v>0.0006558551062093423</v>
+        <v>0.0006558551062093422</v>
       </c>
       <c r="BQ135" t="n">
         <v>0.0006001545413622894</v>
